--- a/app/template_knowledge/sources/영상편집DB_원본구간.xlsx
+++ b/app/template_knowledge/sources/영상편집DB_원본구간.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="R7af833a9c5ff4b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="R16095117e46546a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="Rf7362879307e454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R712392988bd840ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R0030ee42eb864bcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R35b060a51f634948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R99535d8c1d4146ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R0d70a8f5d53940fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R6cc9df3b8d004a5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R9c473724b947435f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="Rbc49a21a67fe43e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="R6d0a22a284114921"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R23cdfeafd2bf47e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="Rf724c0532b10471e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="Rc209c255fcc84583"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="Rfb8ccf188f6a4154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="Rfc4c116a82fa4c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="Rd0501696557c4639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R4d353376ced846c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R3a2735aba24c4175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="Rafd7c9cb14c44b1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R356bef69aa3342e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R62d140c102664418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="Rddef04beeea44f27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="Rfeca9a9d91524650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R4fd58b2a37b745ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -630,7 +630,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="21" t="str">
-        <x:v>SARILS 영상편집 의사결정 템플릿 v5.1 · 실제 가이드 3종</x:v>
+        <x:v>SARILS 영상편집 의사결정 템플릿 v5.4 · 실제 가이드 3종</x:v>
       </x:c>
       <x:c r="B1" s="21"/>
       <x:c r="C1" s="21"/>
@@ -638,7 +638,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>주술회전·오츠카레 원문과 실제 장면 분석을 실행 템플릿에 연결하며, 삭제된 랭킹 데이터는 포함하지 않습니다.</x:v>
+        <x:v>주술회전·동그리오·오츠카레 원문과 실제 장면 분석을 실행 템플릿에 연결하며, 삭제된 카페 랭킹 데이터는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -932,16 +932,16 @@
     </x:row>
     <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="42" t="str">
-        <x:v>실제 가이드 2종</x:v>
+        <x:v>실제 가이드 3종</x:v>
       </x:c>
       <x:c r="B24" s="46" t="str">
-        <x:v>주술회전 트랜지션 · 오츠카레 썸머 챌린지를 실제 레코드로 등록</x:v>
+        <x:v>주술회전 트랜지션 · 동그리오 챌린지 · 오츠카레 썸머 챌린지를 실제 레코드로 등록</x:v>
       </x:c>
       <x:c r="C24" s="46" t="str">
         <x:v>02, 03, 12</x:v>
       </x:c>
       <x:c r="D24" s="46" t="str">
-        <x:v>두 가이드의 원문·분석 근거와 실행 구간만 보존</x:v>
+        <x:v>세 가이드의 원문·분석 근거와 실행 구간만 보존</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2380,7 +2380,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="56" t="str">
-        <x:v>원문 가이드는 수정 없이 보존하고, 카페 추천 영상과 이번 주술회전.mp4·썸머.mp4의 실제 영상 분석을 별도 VIDEO_ANALYSIS 레코드로 추가했습니다. 실행용 v2 구간은 03_GUIDE_TEMPLATES에서 이 근거를 참조합니다.</x:v>
+        <x:v>원문 가이드는 수정 없이 보존하고, 업로드 영상 분석은 VIDEO_ANALYSIS로 누적합니다. 5프레임 정밀 관측은 별도 시트/열을 만들지 않고 03_GUIDE_TEMPLATES의 action_pattern·timing_rule에 실행 구간별로 흡수하며, 원본 분석 근거는 이 시트에서 보존합니다.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -3860,7 +3860,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="G46" s="85" t="str">
-        <x:v>  동일 무드(임팩트형 타격 SFX + 저역 서브베이스)의 대체 트랙 3개를 반환한 뒤 사용자 확인을 요청한다.</x:v>
+        <x:v>동일 무드(임팩트형 타격 SFX + 저역 서브베이스)의 대체 트랙 3개를 반환한 뒤 사용자 확인을 요청한다.</x:v>
       </x:c>
       <x:c r="H46" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4000,7 +4000,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="G50" s="85" t="str">
-        <x:v>  모든 시각 효과(모션 블러·펀치 줌·플래시)는 이 창 안에서만 발생시킨다.</x:v>
+        <x:v>모든 시각 효과(모션 블러·펀치 줌·플래시)는 이 창 안에서만 발생시킨다.</x:v>
       </x:c>
       <x:c r="H50" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4138,7 +4138,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="G54" s="85" t="str">
-        <x:v>    VoL(f)  = variance(Laplacian(grayscale(f)))        # 낮을수록 흐림</x:v>
+        <x:v>VoL(f)  = variance(Laplacian(grayscale(f)))        # 낮을수록 흐림</x:v>
       </x:c>
       <x:c r="H54" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4173,7 +4173,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="G55" s="85" t="str">
-        <x:v>    Flow(f) = mean magnitude of Farnebäck dense optical flow</x:v>
+        <x:v>Flow(f) = mean magnitude of Farnebäck dense optical flow</x:v>
       </x:c>
       <x:c r="H55" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4208,7 +4208,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="G56" s="85" t="str">
-        <x:v>  ※ 블러 피크는 VoL '최솟값'이다. 최댓값이 아니다. 방향을 혼동하면 컷이 정반대로 잘린다.</x:v>
+        <x:v>※ 블러 피크는 VoL '최솟값'이다. 최댓값이 아니다. 방향을 혼동하면 컷이 정반대로 잘린다.</x:v>
       </x:c>
       <x:c r="H56" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4278,7 +4278,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G58" s="85" t="str">
-        <x:v>  후반 40% 구간에서 argmin(VoL) ∧ argmax(Flow) 인 프레임을 Peak_A → Out-point. 이후 프레임 폐기.</x:v>
+        <x:v>후반 40% 구간에서 argmin(VoL) ∧ argmax(Flow) 인 프레임을 Peak_A → Out-point. 이후 프레임 폐기.</x:v>
       </x:c>
       <x:c r="H58" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4348,7 +4348,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="G60" s="85" t="str">
-        <x:v>  전반 40% 구간에서 argmin(VoL) ∧ argmax(Flow) 인 프레임을 Peak_B → In-point. 이전 프레임 폐기.</x:v>
+        <x:v>전반 40% 구간에서 argmin(VoL) ∧ argmax(Flow) 인 프레임을 Peak_B → In-point. 이전 프레임 폐기.</x:v>
       </x:c>
       <x:c r="H60" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4453,7 +4453,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="G63" s="85" t="str">
-        <x:v>  편집을 중단, ③ 촬영 지시서를 반환한다.</x:v>
+        <x:v>편집을 중단, ③ 촬영 지시서를 반환한다.</x:v>
       </x:c>
       <x:c r="H63" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4591,7 +4591,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="G67" s="85" t="str">
-        <x:v>  로드한 BGM을 메인 트랙에 배치하고 -14 LUFS(True Peak ≤ -1.0 dBTP)로 정규화한다.</x:v>
+        <x:v>로드한 BGM을 메인 트랙에 배치하고 -14 LUFS(True Peak ≤ -1.0 dBTP)로 정규화한다.</x:v>
       </x:c>
       <x:c r="H67" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4661,7 +4661,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="G69" s="85" t="str">
-        <x:v>  정렬은 프레임 경계가 아니라 샘플 단위로 수행하고, 최종 오차 ±1프레임 이내를 보장한다.</x:v>
+        <x:v>정렬은 프레임 경계가 아니라 샘플 단위로 수행하고, 최종 오차 ±1프레임 이내를 보장한다.</x:v>
       </x:c>
       <x:c r="H69" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4731,7 +4731,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="G71" s="85" t="str">
-        <x:v>  미달 시 T_beat 를 차순위 온셋으로 교체하고 재정렬한다.</x:v>
+        <x:v>미달 시 T_beat 를 차순위 온셋으로 교체하고 재정렬한다.</x:v>
       </x:c>
       <x:c r="H71" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4869,7 +4869,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="G75" s="85" t="str">
-        <x:v>  MediaPipe Hands로 Peak_A 마지막 프레임과 Peak_B 첫 프레임의 손 랜드마크(#9 중지 MCP) 좌표를 추출.</x:v>
+        <x:v>MediaPipe Hands로 Peak_A 마지막 프레임과 Peak_B 첫 프레임의 손 랜드마크(#9 중지 MCP) 좌표를 추출.</x:v>
       </x:c>
       <x:c r="H75" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4904,7 +4904,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="G76" s="85" t="str">
-        <x:v>  델타(Δx, Δy)만큼 Clip B를 Pan 이동시키고, 여백은 스케일 108% 크롭으로 덮는다. 잔차 20px 이내.</x:v>
+        <x:v>델타(Δx, Δy)만큼 Clip B를 Pan 이동시키고, 여백은 스케일 108% 크롭으로 덮는다. 잔차 20px 이내.</x:v>
       </x:c>
       <x:c r="H76" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -4974,7 +4974,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="G78" s="85" t="str">
-        <x:v>  Clip A 마지막 30프레임과 Clip B 첫 30프레임의 LAB 채널 평균·표준편차를 계산해</x:v>
+        <x:v>Clip A 마지막 30프레임과 Clip B 첫 30프레임의 LAB 채널 평균·표준편차를 계산해</x:v>
       </x:c>
       <x:c r="H78" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5009,7 +5009,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="G79" s="85" t="str">
-        <x:v>  Clip B를 Clip A 기준으로 이동시킨다. 전환 순간 화면이 튀는 현상을 제거한다.</x:v>
+        <x:v>Clip B를 Clip A 기준으로 이동시킨다. 전환 순간 화면이 튀는 현상을 제거한다.</x:v>
       </x:c>
       <x:c r="H79" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5079,7 +5079,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="G81" s="85" t="str">
-        <x:v>    · Clip A 마지막 4프레임 : 방향성 모션 블러 (각도 = Flow 벡터 평균 방향, 강도 70%)</x:v>
+        <x:v>· Clip A 마지막 4프레임 : 방향성 모션 블러 (각도 = Flow 벡터 평균 방향, 강도 70%)</x:v>
       </x:c>
       <x:c r="H81" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5114,7 +5114,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="G82" s="85" t="str">
-        <x:v>    · T_beat 프레임         : 화이트 플래시 2프레임 (opacity 0→60→0)</x:v>
+        <x:v>· T_beat 프레임         : 화이트 플래시 2프레임 (opacity 0→60→0)</x:v>
       </x:c>
       <x:c r="H82" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5149,7 +5149,7 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="G83" s="85" t="str">
-        <x:v>    · Clip B 첫 4프레임     : 펀치 줌 scale 105% → 100%, easing cubic-out</x:v>
+        <x:v>· Clip B 첫 4프레임     : 펀치 줌 scale 105% → 100%, easing cubic-out</x:v>
       </x:c>
       <x:c r="H83" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5219,7 +5219,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="G85" s="85" t="str">
-        <x:v>    0.0초부터 훅 자막 "{{caption.hook}}" 표시 (페이드인 금지, pop 3프레임)</x:v>
+        <x:v>0.0초부터 훅 자막 "{{caption.hook}}" 표시 (페이드인 금지, pop 3프레임)</x:v>
       </x:c>
       <x:c r="H85" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5254,7 +5254,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="G86" s="85" t="str">
-        <x:v>    위치 (540, 1200) / 90px / Noto Sans KR Bold / 흰색 + 검정 외곽선 4px</x:v>
+        <x:v>위치 (540, 1200) / 90px / Noto Sans KR Bold / 흰색 + 검정 외곽선 4px</x:v>
       </x:c>
       <x:c r="H86" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5289,7 +5289,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="G87" s="85" t="str">
-        <x:v>    T_beat 이후 결과 자막 "{{caption.reveal}}" 로 교체</x:v>
+        <x:v>T_beat 이후 결과 자막 "{{caption.reveal}}" 로 교체</x:v>
       </x:c>
       <x:c r="H87" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5532,7 +5532,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="G94" s="85" t="str">
-        <x:v>  QA 필수 항목: sync_error_ms(≤33), spatial_residual_px(≤20), loudness_lufs, face_blur_count</x:v>
+        <x:v>QA 필수 항목: sync_error_ms(≤33), spatial_residual_px(≤20), loudness_lufs, face_blur_count</x:v>
       </x:c>
       <x:c r="H94" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5841,7 +5841,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="G103" s="85" t="str">
-        <x:v>  · 핸드폰 세로로, 가슴 높이</x:v>
+        <x:v>· 핸드폰 세로로, 가슴 높이</x:v>
       </x:c>
       <x:c r="H103" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5876,7 +5876,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="G104" s="85" t="str">
-        <x:v>  · 빈 접시(또는 빈 진열대)를 3초간 비추기</x:v>
+        <x:v>· 빈 접시(또는 빈 진열대)를 3초간 비추기</x:v>
       </x:c>
       <x:c r="H104" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5911,7 +5911,7 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="G105" s="85" t="str">
-        <x:v>  · ★ 마지막에 핸드폰을 오른쪽으로 "휙" 빠르게 돌리며 끝내기</x:v>
+        <x:v>· ★ 마지막에 핸드폰을 오른쪽으로 "휙" 빠르게 돌리며 끝내기</x:v>
       </x:c>
       <x:c r="H105" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -5946,7 +5946,7 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="G106" s="85" t="str">
-        <x:v>    → 이 흔들린 구간이 전환 재료입니다. 천천히 돌리면 안 됩니다.</x:v>
+        <x:v>→ 이 흔들린 구간이 전환 재료입니다. 천천히 돌리면 안 됩니다.</x:v>
       </x:c>
       <x:c r="H106" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6049,7 +6049,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="G109" s="85" t="str">
-        <x:v>  · ★ 핸드폰을 이미 오른쪽으로 돌려놓은 상태에서 녹화 시작</x:v>
+        <x:v>· ★ 핸드폰을 이미 오른쪽으로 돌려놓은 상태에서 녹화 시작</x:v>
       </x:c>
       <x:c r="H109" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6084,7 +6084,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="G110" s="85" t="str">
-        <x:v>  · 곧바로 왼쪽으로 "휙" 돌려 제자리로 돌아오기</x:v>
+        <x:v>· 곧바로 왼쪽으로 "휙" 돌려 제자리로 돌아오기</x:v>
       </x:c>
       <x:c r="H110" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6119,7 +6119,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="G111" s="85" t="str">
-        <x:v>  · 완성된 요리(또는 상품)를 3초간 비추기</x:v>
+        <x:v>· 완성된 요리(또는 상품)를 3초간 비추기</x:v>
       </x:c>
       <x:c r="H111" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6634,7 +6634,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="G126" s="85" t="str">
-        <x:v>  · 업로드된 2개 영상을 분석해</x:v>
+        <x:v>· 업로드된 2개 영상을 분석해</x:v>
       </x:c>
       <x:c r="H126" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6669,7 +6669,7 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="G127" s="85" t="str">
-        <x:v>      Clip A = 전 상태(빈 접시/빈 진열대/시술 전 등)</x:v>
+        <x:v>Clip A = 전 상태(빈 접시/빈 진열대/시술 전 등)</x:v>
       </x:c>
       <x:c r="H127" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6704,7 +6704,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="G128" s="85" t="str">
-        <x:v>      Clip B = 후 상태(완성 메뉴/상품/시술 후 등)</x:v>
+        <x:v>Clip B = 후 상태(완성 메뉴/상품/시술 후 등)</x:v>
       </x:c>
       <x:c r="H128" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6739,7 +6739,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="G129" s="85" t="str">
-        <x:v>    로 자동 분류합니다.</x:v>
+        <x:v>로 자동 분류합니다.</x:v>
       </x:c>
       <x:c r="H129" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6774,7 +6774,7 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="G130" s="85" t="str">
-        <x:v>  · 해상도, 세로 화면 여부, 촬영 길이, 흔들림 강도를 검사합니다.</x:v>
+        <x:v>· 해상도, 세로 화면 여부, 촬영 길이, 흔들림 강도를 검사합니다.</x:v>
       </x:c>
       <x:c r="H130" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6809,7 +6809,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="G131" s="85" t="str">
-        <x:v>  · 전환에 필요한 휘두름 동작이 부족하면 편집을 억지로 진행하지 않고</x:v>
+        <x:v>· 전환에 필요한 휘두름 동작이 부족하면 편집을 억지로 진행하지 않고</x:v>
       </x:c>
       <x:c r="H131" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6844,7 +6844,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="G132" s="85" t="str">
-        <x:v>    "1컷 마지막을 더 빠르게 오른쪽으로 휘둘러 다시 촬영해주세요"처럼</x:v>
+        <x:v>"1컷 마지막을 더 빠르게 오른쪽으로 휘둘러 다시 촬영해주세요"처럼</x:v>
       </x:c>
       <x:c r="H132" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6879,7 +6879,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="G133" s="85" t="str">
-        <x:v>    재촬영할 컷과 이유를 구체적으로 반환합니다.</x:v>
+        <x:v>재촬영할 컷과 이유를 구체적으로 반환합니다.</x:v>
       </x:c>
       <x:c r="H133" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -6982,7 +6982,7 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="G136" s="85" t="str">
-        <x:v>  · AI가 Optical Flow와 Blur Peak를 계산해</x:v>
+        <x:v>· AI가 Optical Flow와 Blur Peak를 계산해</x:v>
       </x:c>
       <x:c r="H136" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7017,7 +7017,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="G137" s="85" t="str">
-        <x:v>    Clip A의 가장 강한 휘두름 끝점과 Clip B의 가장 강한 복귀 시작점을 찾습니다.</x:v>
+        <x:v>Clip A의 가장 강한 휘두름 끝점과 Clip B의 가장 강한 복귀 시작점을 찾습니다.</x:v>
       </x:c>
       <x:c r="H137" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7052,7 +7052,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="G138" s="85" t="str">
-        <x:v>  · 사용자가 타임라인에서 직접 컷 포인트를 찾을 필요가 없습니다.</x:v>
+        <x:v>· 사용자가 타임라인에서 직접 컷 포인트를 찾을 필요가 없습니다.</x:v>
       </x:c>
       <x:c r="H138" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7087,7 +7087,7 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="G139" s="85" t="str">
-        <x:v>  · 두 컷의 방향이 맞지 않거나 전환 재료가 부족하면 자동 실패 판정을 내립니다.</x:v>
+        <x:v>· 두 컷의 방향이 맞지 않거나 전환 재료가 부족하면 자동 실패 판정을 내립니다.</x:v>
       </x:c>
       <x:c r="H139" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7190,7 +7190,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="G142" s="85" t="str">
-        <x:v>  · 템플릿에 지정된 상업 이용 가능 음원을 자동 로드합니다.</x:v>
+        <x:v>· 템플릿에 지정된 상업 이용 가능 음원을 자동 로드합니다.</x:v>
       </x:c>
       <x:c r="H142" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7225,7 +7225,7 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="G143" s="85" t="str">
-        <x:v>  · 가장 강한 타격음 T_beat를 탐지합니다.</x:v>
+        <x:v>· 가장 강한 타격음 T_beat를 탐지합니다.</x:v>
       </x:c>
       <x:c r="H143" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7260,7 +7260,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="G144" s="85" t="str">
-        <x:v>  · 영상 전환 프레임과 T_beat를 ±1프레임 이내로 자동 정렬합니다.</x:v>
+        <x:v>· 영상 전환 프레임과 T_beat를 ±1프레임 이내로 자동 정렬합니다.</x:v>
       </x:c>
       <x:c r="H144" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7295,7 +7295,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="G145" s="85" t="str">
-        <x:v>  · 원본 현장음은 자동 음소거하고 BGM의 라우드니스를 규격에 맞춥니다.</x:v>
+        <x:v>· 원본 현장음은 자동 음소거하고 BGM의 라우드니스를 규격에 맞춥니다.</x:v>
       </x:c>
       <x:c r="H145" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7398,7 +7398,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="G148" s="85" t="str">
-        <x:v>  · 전환 전후 손 위치와 화면 구도를 분석해 Clip B의 위치·크롭을 자동 보정합니다.</x:v>
+        <x:v>· 전환 전후 손 위치와 화면 구도를 분석해 Clip B의 위치·크롭을 자동 보정합니다.</x:v>
       </x:c>
       <x:c r="H148" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7433,7 +7433,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="G149" s="85" t="str">
-        <x:v>  · 두 영상의 밝기와 색감을 자동 매칭합니다.</x:v>
+        <x:v>· 두 영상의 밝기와 색감을 자동 매칭합니다.</x:v>
       </x:c>
       <x:c r="H149" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7468,7 +7468,7 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="G150" s="85" t="str">
-        <x:v>  · 전환 순간에만 모션 블러 → 화이트 플래시 → 펀치 줌을 순서대로 적용합니다.</x:v>
+        <x:v>· 전환 순간에만 모션 블러 → 화이트 플래시 → 펀치 줌을 순서대로 적용합니다.</x:v>
       </x:c>
       <x:c r="H150" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7503,7 +7503,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="G151" s="85" t="str">
-        <x:v>  · 효과 강도는 W_impact 안에서만 제한해 과편집을 방지합니다.</x:v>
+        <x:v>· 효과 강도는 W_impact 안에서만 제한해 과편집을 방지합니다.</x:v>
       </x:c>
       <x:c r="H151" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7606,7 +7606,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="G154" s="85" t="str">
-        <x:v>  · 온보딩 정보와 프로젝트의 홍보 목적을 바탕으로</x:v>
+        <x:v>· 온보딩 정보와 프로젝트의 홍보 목적을 바탕으로</x:v>
       </x:c>
       <x:c r="H154" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7641,7 +7641,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="G155" s="85" t="str">
-        <x:v>      시작: {{caption.hook}}</x:v>
+        <x:v>시작: {{caption.hook}}</x:v>
       </x:c>
       <x:c r="H155" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7676,7 +7676,7 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="G156" s="85" t="str">
-        <x:v>      전환 후: {{caption.reveal}}</x:v>
+        <x:v>전환 후: {{caption.reveal}}</x:v>
       </x:c>
       <x:c r="H156" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7711,7 +7711,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="G157" s="85" t="str">
-        <x:v>      마지막: {{store.name}} · {{store.location}} · {{cta.text}}</x:v>
+        <x:v>마지막: {{store.name}} · {{store.location}} · {{cta.text}}</x:v>
       </x:c>
       <x:c r="H157" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7746,7 +7746,7 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="G158" s="85" t="str">
-        <x:v>    를 자동 구성합니다.</x:v>
+        <x:v>를 자동 구성합니다.</x:v>
       </x:c>
       <x:c r="H158" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7781,7 +7781,7 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="G159" s="85" t="str">
-        <x:v>  · 템플릿 세이프존과 폰트 규칙에 맞춰 자동 배치합니다.</x:v>
+        <x:v>· 템플릿 세이프존과 폰트 규칙에 맞춰 자동 배치합니다.</x:v>
       </x:c>
       <x:c r="H159" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7884,7 +7884,7 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="G162" s="85" t="str">
-        <x:v>  · sync_error_ms ≤ 33</x:v>
+        <x:v>· sync_error_ms ≤ 33</x:v>
       </x:c>
       <x:c r="H162" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7919,7 +7919,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="G163" s="85" t="str">
-        <x:v>  · spatial_residual_px ≤ 20</x:v>
+        <x:v>· spatial_residual_px ≤ 20</x:v>
       </x:c>
       <x:c r="H163" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7954,7 +7954,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="G164" s="85" t="str">
-        <x:v>  · loudness 규격</x:v>
+        <x:v>· loudness 규격</x:v>
       </x:c>
       <x:c r="H164" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -7989,7 +7989,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="G165" s="85" t="str">
-        <x:v>  · 얼굴 정책</x:v>
+        <x:v>· 얼굴 정책</x:v>
       </x:c>
       <x:c r="H165" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -8024,7 +8024,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="G166" s="85" t="str">
-        <x:v>  · 전체 길이 6~12초</x:v>
+        <x:v>· 전체 길이 6~12초</x:v>
       </x:c>
       <x:c r="H166" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -8059,7 +8059,7 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="G167" s="85" t="str">
-        <x:v>    를 검사합니다.</x:v>
+        <x:v>를 검사합니다.</x:v>
       </x:c>
       <x:c r="H167" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -8094,7 +8094,7 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="G168" s="85" t="str">
-        <x:v>  · QA를 통과하면 1080x1920 / 30fps mp4로 자동 렌더링합니다.</x:v>
+        <x:v>· QA를 통과하면 1080x1920 / 30fps mp4로 자동 렌더링합니다.</x:v>
       </x:c>
       <x:c r="H168" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -8129,7 +8129,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="G169" s="85" t="str">
-        <x:v>  · QA 실패 시 임의로 품질을 낮춰 내보내지 않고,</x:v>
+        <x:v>· QA 실패 시 임의로 품질을 낮춰 내보내지 않고,</x:v>
       </x:c>
       <x:c r="H169" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -8164,7 +8164,7 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="G170" s="85" t="str">
-        <x:v>    실패 원인과 필요한 재촬영 지시를 반환합니다.</x:v>
+        <x:v>실패 원인과 필요한 재촬영 지시를 반환합니다.</x:v>
       </x:c>
       <x:c r="H170" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -9268,7 +9268,7 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="G202" s="85" t="str">
-        <x:v>**성공/실패를 가르는 핵심:** 홍보 컷이 춤을 멈추게 만드는 광고 삽입처럼 보이면 실패다.  </x:v>
+        <x:v>**성공/실패를 가르는 핵심:** 홍보 컷이 춤을 멈추게 만드는 광고 삽입처럼 보이면 실패다.</x:v>
       </x:c>
       <x:c r="H202" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -10273,7 +10273,7 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="G231" s="85" t="str">
-        <x:v>**중요:** 홍보 컷이 들어가도 음원은 절대 끊지 않는다.  </x:v>
+        <x:v>**중요:** 홍보 컷이 들어가도 음원은 절대 끊지 않는다.</x:v>
       </x:c>
       <x:c r="H231" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11000,7 +11000,7 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="G252" s="85" t="str">
-        <x:v>   '챌린지 안에 홍보가 박자처럼 끼어드는 영상'으로 보이게 한다.</x:v>
+        <x:v>'챌린지 안에 홍보가 박자처럼 끼어드는 영상'으로 보이게 한다.</x:v>
       </x:c>
       <x:c r="H252" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11173,7 +11173,7 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="G257" s="85" t="str">
-        <x:v>  license != commercial_safe 이면 원곡 사용을 중단하고:</x:v>
+        <x:v>license != commercial_safe 이면 원곡 사용을 중단하고:</x:v>
       </x:c>
       <x:c r="H257" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11208,7 +11208,7 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="G258" s="85" t="str">
-        <x:v>    (a) 플랫폼 내 사업자 계정 사용 가능 버전 탐색 안내</x:v>
+        <x:v>(a) 플랫폼 내 사업자 계정 사용 가능 버전 탐색 안내</x:v>
       </x:c>
       <x:c r="H258" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11243,7 +11243,7 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="G259" s="85" t="str">
-        <x:v>    (b) 동일 BPM ±6, 밝은 여름 챌린지 무드의 commercial_safe 대체 트랙 3종</x:v>
+        <x:v>(b) 동일 BPM ±6, 밝은 여름 챌린지 무드의 commercial_safe 대체 트랙 3종</x:v>
       </x:c>
       <x:c r="H259" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11278,7 +11278,7 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="G260" s="85" t="str">
-        <x:v>  을 반환한다.</x:v>
+        <x:v>을 반환한다.</x:v>
       </x:c>
       <x:c r="H260" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11418,7 +11418,7 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="G264" s="85" t="str">
-        <x:v>  phrase_start[i], phrase_end[i] 배열을 만든다.</x:v>
+        <x:v>phrase_start[i], phrase_end[i] 배열을 만든다.</x:v>
       </x:c>
       <x:c r="H264" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11523,7 +11523,7 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="G267" s="85" t="str">
-        <x:v>  연속 홍보 컷 간 최소 간격은 1.2초 이상을 권장한다.</x:v>
+        <x:v>연속 홍보 컷 간 최소 간격은 1.2초 이상을 권장한다.</x:v>
       </x:c>
       <x:c r="H267" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11696,7 +11696,7 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="G272" s="85" t="str">
-        <x:v>    · 전신 또는 상반신이 안정적으로 보임</x:v>
+        <x:v>· 전신 또는 상반신이 안정적으로 보임</x:v>
       </x:c>
       <x:c r="H272" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11731,7 +11731,7 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="G273" s="85" t="str">
-        <x:v>    · 인물이 프레임 밖으로 크게 이탈하지 않음</x:v>
+        <x:v>· 인물이 프레임 밖으로 크게 이탈하지 않음</x:v>
       </x:c>
       <x:c r="H273" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11766,7 +11766,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="G274" s="85" t="str">
-        <x:v>    · 후렴 전체 안무가 끊기지 않고 존재함</x:v>
+        <x:v>· 후렴 전체 안무가 끊기지 않고 존재함</x:v>
       </x:c>
       <x:c r="H274" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11801,7 +11801,7 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="G275" s="85" t="str">
-        <x:v>    · 심한 모션 블러/초점 이탈 구간이 전체의 20% 미만</x:v>
+        <x:v>· 심한 모션 블러/초점 이탈 구간이 전체의 20% 미만</x:v>
       </x:c>
       <x:c r="H275" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11871,7 +11871,7 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="G277" s="85" t="str">
-        <x:v>  pose_visibility + framing_stability + motion_completeness 점수로 최상위 테이크를 기본 베이스로 선택한다.</x:v>
+        <x:v>pose_visibility + framing_stability + motion_completeness 점수로 최상위 테이크를 기본 베이스로 선택한다.</x:v>
       </x:c>
       <x:c r="H277" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -11941,7 +11941,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="G279" s="85" t="str">
-        <x:v>  기본적으로 한 번도 시간축을 끊지 않는다.</x:v>
+        <x:v>기본적으로 한 번도 시간축을 끊지 않는다.</x:v>
       </x:c>
       <x:c r="H279" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12114,7 +12114,7 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="G284" s="85" t="str">
-        <x:v>    index_finger = extended</x:v>
+        <x:v>index_finger = extended</x:v>
       </x:c>
       <x:c r="H284" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12149,7 +12149,7 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="G285" s="85" t="str">
-        <x:v>    middle_finger = extended</x:v>
+        <x:v>middle_finger = extended</x:v>
       </x:c>
       <x:c r="H285" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12184,7 +12184,7 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="G286" s="85" t="str">
-        <x:v>    ring_finger = folded</x:v>
+        <x:v>ring_finger = folded</x:v>
       </x:c>
       <x:c r="H286" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12219,7 +12219,7 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="G287" s="85" t="str">
-        <x:v>    pinky_finger = folded</x:v>
+        <x:v>pinky_finger = folded</x:v>
       </x:c>
       <x:c r="H287" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12394,7 +12394,7 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="G292" s="85" t="str">
-        <x:v>  {{promo.primary}}의 가장 선명한 클로즈업 컷으로 교체한다.</x:v>
+        <x:v>{{promo.primary}}의 가장 선명한 클로즈업 컷으로 교체한다.</x:v>
       </x:c>
       <x:c r="H292" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12464,7 +12464,7 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="G294" s="85" t="str">
-        <x:v>  '브이를 하면서 상품을 보여주는 것'이 아니라</x:v>
+        <x:v>'브이를 하면서 상품을 보여주는 것'이 아니라</x:v>
       </x:c>
       <x:c r="H294" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12499,7 +12499,7 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="G295" s="85" t="str">
-        <x:v>  '브이가 나올 정확한 순간에 브이 대신 상품이 화면을 차지하는 것'이다.</x:v>
+        <x:v>'브이가 나올 정확한 순간에 브이 대신 상품이 화면을 차지하는 것'이다.</x:v>
       </x:c>
       <x:c r="H295" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12637,7 +12637,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="G299" s="85" t="str">
-        <x:v>    P1 = 대표 메뉴/상품 Hero Close-up</x:v>
+        <x:v>P1 = 대표 메뉴/상품 Hero Close-up</x:v>
       </x:c>
       <x:c r="H299" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12672,7 +12672,7 @@
         <x:v>296</x:v>
       </x:c>
       <x:c r="G300" s="85" t="str">
-        <x:v>    P2 = 메뉴명·가격 또는 핵심 혜택</x:v>
+        <x:v>P2 = 메뉴명·가격 또는 핵심 혜택</x:v>
       </x:c>
       <x:c r="H300" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12707,7 +12707,7 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="G301" s="85" t="str">
-        <x:v>    P3 = 만드는 장면/사용 장면/디테일</x:v>
+        <x:v>P3 = 만드는 장면/사용 장면/디테일</x:v>
       </x:c>
       <x:c r="H301" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12742,7 +12742,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="G302" s="85" t="str">
-        <x:v>    P4 = 기간·한정·CTA</x:v>
+        <x:v>P4 = 기간·한정·CTA</x:v>
       </x:c>
       <x:c r="H302" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12812,7 +12812,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="G304" s="85" t="str">
-        <x:v>    primary_v_event → P1</x:v>
+        <x:v>primary_v_event → P1</x:v>
       </x:c>
       <x:c r="H304" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12847,7 +12847,7 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="G305" s="85" t="str">
-        <x:v>    phrase_end[1]   → P2</x:v>
+        <x:v>phrase_end[1]   → P2</x:v>
       </x:c>
       <x:c r="H305" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12882,7 +12882,7 @@
         <x:v>302</x:v>
       </x:c>
       <x:c r="G306" s="85" t="str">
-        <x:v>    phrase_end[2]   → P3</x:v>
+        <x:v>phrase_end[2]   → P3</x:v>
       </x:c>
       <x:c r="H306" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12917,7 +12917,7 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="G307" s="85" t="str">
-        <x:v>    마지막 구절     → P4 또는 춤 복귀 후 CTA</x:v>
+        <x:v>마지막 구절     → P4 또는 춤 복귀 후 CTA</x:v>
       </x:c>
       <x:c r="H307" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -12987,7 +12987,7 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="G309" s="85" t="str">
-        <x:v>    기본 0.3~0.6초</x:v>
+        <x:v>기본 0.3~0.6초</x:v>
       </x:c>
       <x:c r="H309" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -13022,7 +13022,7 @@
         <x:v>306</x:v>
       </x:c>
       <x:c r="G310" s="85" t="str">
-        <x:v>    정보 읽기가 필요한 P2/P4는 최대 0.8초</x:v>
+        <x:v>정보 읽기가 필요한 P2/P4는 최대 0.8초</x:v>
       </x:c>
       <x:c r="H310" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -13197,7 +13197,7 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="G315" s="85" t="str">
-        <x:v>  두 이벤트를 하나로 병합하고 V_event를 우선한다.</x:v>
+        <x:v>두 이벤트를 하나로 병합하고 V_event를 우선한다.</x:v>
       </x:c>
       <x:c r="H315" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -13683,7 +13683,7 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="G329" s="85" t="str">
-        <x:v>    0.40·피사체 점유율</x:v>
+        <x:v>0.40·피사체 점유율</x:v>
       </x:c>
       <x:c r="H329" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -13718,7 +13718,7 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="G330" s="85" t="str">
-        <x:v>  + 0.25·선명도</x:v>
+        <x:v>+ 0.25·선명도</x:v>
       </x:c>
       <x:c r="H330" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -13753,7 +13753,7 @@
         <x:v>327</x:v>
       </x:c>
       <x:c r="G331" s="85" t="str">
-        <x:v>  + 0.20·밝기/색 안정성</x:v>
+        <x:v>+ 0.20·밝기/색 안정성</x:v>
       </x:c>
       <x:c r="H331" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -13788,7 +13788,7 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="G332" s="85" t="str">
-        <x:v>  + 0.15·미세 움직임</x:v>
+        <x:v>+ 0.15·미세 움직임</x:v>
       </x:c>
       <x:c r="H332" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -13893,7 +13893,7 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="G335" s="85" t="str">
-        <x:v>  핵심 형태가 식별되지 않을 정도의 크롭은 금지한다.</x:v>
+        <x:v>핵심 형태가 식별되지 않을 정도의 크롭은 금지한다.</x:v>
       </x:c>
       <x:c r="H335" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -13998,7 +13998,7 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="G338" s="85" t="str">
-        <x:v>  홍보 화면은 사용자가 촬영·업로드한 영상 클립에서만 선택한다.</x:v>
+        <x:v>홍보 화면은 사용자가 촬영·업로드한 영상 클립에서만 선택한다.</x:v>
       </x:c>
       <x:c r="H338" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14136,7 +14136,7 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="G342" s="85" t="str">
-        <x:v>  전부 하드컷으로 전환한다.</x:v>
+        <x:v>전부 하드컷으로 전환한다.</x:v>
       </x:c>
       <x:c r="H342" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14206,7 +14206,7 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="G344" s="85" t="str">
-        <x:v>    첫 2~3프레임 scale 103% → 100%의 아주 짧은 punch-in 허용.</x:v>
+        <x:v>첫 2~3프레임 scale 103% → 100%의 아주 짧은 punch-in 허용.</x:v>
       </x:c>
       <x:c r="H344" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14276,7 +14276,7 @@
         <x:v>342</x:v>
       </x:c>
       <x:c r="G346" s="85" t="str">
-        <x:v>    별도 트랜지션 없이 바로 다음 댄스 프레임으로 복귀한다.</x:v>
+        <x:v>별도 트랜지션 없이 바로 다음 댄스 프레임으로 복귀한다.</x:v>
       </x:c>
       <x:c r="H346" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14346,7 +14346,7 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="G348" s="85" t="str">
-        <x:v>  이 포맷의 재미는 '갑자기 상품이 튀어나오는 타이밍' 자체다.</x:v>
+        <x:v>이 포맷의 재미는 '갑자기 상품이 튀어나오는 타이밍' 자체다.</x:v>
       </x:c>
       <x:c r="H348" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14519,7 +14519,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="G353" s="85" t="str">
-        <x:v>    "{{caption.hook}}"</x:v>
+        <x:v>"{{caption.hook}}"</x:v>
       </x:c>
       <x:c r="H353" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14554,7 +14554,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="G354" s="85" t="str">
-        <x:v>    예) "요즘 이 춤 다 추길래"</x:v>
+        <x:v>예) "요즘 이 춤 다 추길래"</x:v>
       </x:c>
       <x:c r="H354" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14624,7 +14624,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="G356" s="85" t="str">
-        <x:v>    텍스트 없이 상품 자체만 보여주는 것을 우선한다.</x:v>
+        <x:v>텍스트 없이 상품 자체만 보여주는 것을 우선한다.</x:v>
       </x:c>
       <x:c r="H356" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14694,7 +14694,7 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="G358" s="85" t="str">
-        <x:v>    "{{promo.name}} · {{promo.price}}"</x:v>
+        <x:v>"{{promo.name}} · {{promo.price}}"</x:v>
       </x:c>
       <x:c r="H358" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14764,7 +14764,7 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="G360" s="85" t="str">
-        <x:v>    필요 시 "{{promo.benefit}}" 한 줄만 표시한다.</x:v>
+        <x:v>필요 시 "{{promo.benefit}}" 한 줄만 표시한다.</x:v>
       </x:c>
       <x:c r="H360" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14834,7 +14834,7 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="G362" s="85" t="str">
-        <x:v>    "{{caption.message}}"</x:v>
+        <x:v>"{{caption.message}}"</x:v>
       </x:c>
       <x:c r="H362" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14869,7 +14869,7 @@
         <x:v>359</x:v>
       </x:c>
       <x:c r="G363" s="85" t="str">
-        <x:v>    예) "여름 끝나기 전에 ○○ 먹으러 오세요"</x:v>
+        <x:v>예) "여름 끝나기 전에 ○○ 먹으러 오세요"</x:v>
       </x:c>
       <x:c r="H363" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -14904,7 +14904,7 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="G364" s="85" t="str">
-        <x:v>    예) "{{promo.name}} · 8월 한정"</x:v>
+        <x:v>예) "{{promo.name}} · 8월 한정"</x:v>
       </x:c>
       <x:c r="H364" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -15182,7 +15182,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="G372" s="85" t="str">
-        <x:v>    "{{store.name}} · {{store.location}} · {{cta.text}}"</x:v>
+        <x:v>"{{store.name}} · {{store.location}} · {{cta.text}}"</x:v>
       </x:c>
       <x:c r="H372" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -15252,7 +15252,7 @@
         <x:v>370</x:v>
       </x:c>
       <x:c r="G374" s="85" t="str">
-        <x:v>  동작이 끝난 직후 또는 화면 하단 세이프존에 배치한다.</x:v>
+        <x:v>동작이 끝난 직후 또는 화면 하단 세이프존에 배치한다.</x:v>
       </x:c>
       <x:c r="H374" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -15633,7 +15633,7 @@
         <x:v>381</x:v>
       </x:c>
       <x:c r="G385" s="85" t="str">
-        <x:v>  1) 먹싱된 mp4</x:v>
+        <x:v>1) 먹싱된 mp4</x:v>
       </x:c>
       <x:c r="H385" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -15668,7 +15668,7 @@
         <x:v>382</x:v>
       </x:c>
       <x:c r="G386" s="85" t="str">
-        <x:v>  2) 편집 레시피 JSON</x:v>
+        <x:v>2) 편집 레시피 JSON</x:v>
       </x:c>
       <x:c r="H386" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -15703,7 +15703,7 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="G387" s="85" t="str">
-        <x:v>  3) 사장님용 촬영 피드백</x:v>
+        <x:v>3) 사장님용 촬영 피드백</x:v>
       </x:c>
       <x:c r="H387" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -15738,7 +15738,7 @@
         <x:v>384</x:v>
       </x:c>
       <x:c r="G388" s="85" t="str">
-        <x:v>  4) 자동 편집 결정 리포트</x:v>
+        <x:v>4) 자동 편집 결정 리포트</x:v>
       </x:c>
       <x:c r="H388" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -15773,7 +15773,7 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="G389" s="85" t="str">
-        <x:v>  5) QA 리포트</x:v>
+        <x:v>5) QA 리포트</x:v>
       </x:c>
       <x:c r="H389" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -16776,7 +16776,7 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="G418" s="85" t="str">
-        <x:v>  · 핸드폰 세로</x:v>
+        <x:v>· 핸드폰 세로</x:v>
       </x:c>
       <x:c r="H418" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -16811,7 +16811,7 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="G419" s="85" t="str">
-        <x:v>  · 전신 또는 허벅지 위까지 나오게</x:v>
+        <x:v>· 전신 또는 허벅지 위까지 나오게</x:v>
       </x:c>
       <x:c r="H419" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="G420" s="85" t="str">
-        <x:v>  · 카메라는 고정</x:v>
+        <x:v>· 카메라는 고정</x:v>
       </x:c>
       <x:c r="H420" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -16881,7 +16881,7 @@
         <x:v>417</x:v>
       </x:c>
       <x:c r="G421" s="85" t="str">
-        <x:v>  · 노래를 틀어놓고 후렴 안무를 처음부터 끝까지 한 번에 춥니다</x:v>
+        <x:v>· 노래를 틀어놓고 후렴 안무를 처음부터 끝까지 한 번에 춥니다</x:v>
       </x:c>
       <x:c r="H421" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -16916,7 +16916,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="G422" s="85" t="str">
-        <x:v>  · 중간에 틀려도 바로 멈추지 말고 끝까지 가세요</x:v>
+        <x:v>· 중간에 틀려도 바로 멈추지 말고 끝까지 가세요</x:v>
       </x:c>
       <x:c r="H422" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -16951,7 +16951,7 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="G423" s="85" t="str">
-        <x:v>  · ★ 브이(V) 포인트는 평소보다 크게 해주세요</x:v>
+        <x:v>· ★ 브이(V) 포인트는 평소보다 크게 해주세요</x:v>
       </x:c>
       <x:c r="H423" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -16986,7 +16986,7 @@
         <x:v>420</x:v>
       </x:c>
       <x:c r="G424" s="85" t="str">
-        <x:v>    → 편집에서는 이 순간의 브이 화면을 홍보 메뉴/상품으로 바꿉니다</x:v>
+        <x:v>→ 편집에서는 이 순간의 브이 화면을 홍보 메뉴/상품으로 바꿉니다</x:v>
       </x:c>
       <x:c r="H424" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17021,7 +17021,7 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="G425" s="85" t="str">
-        <x:v>  · 노래 한 마디가 끝나는 지점에서도 동작을 계속 이어가세요</x:v>
+        <x:v>· 노래 한 마디가 끝나는 지점에서도 동작을 계속 이어가세요</x:v>
       </x:c>
       <x:c r="H425" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17056,7 +17056,7 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="G426" s="85" t="str">
-        <x:v>    → 편집에서 그 순간에 짧은 홍보 컷을 덮습니다</x:v>
+        <x:v>→ 편집에서 그 순간에 짧은 홍보 컷을 덮습니다</x:v>
       </x:c>
       <x:c r="H426" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17159,7 +17159,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="G429" s="85" t="str">
-        <x:v>  · 화면의 절반 이상을 메뉴/상품이 차지하게</x:v>
+        <x:v>· 화면의 절반 이상을 메뉴/상품이 차지하게</x:v>
       </x:c>
       <x:c r="H429" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17194,7 +17194,7 @@
         <x:v>426</x:v>
       </x:c>
       <x:c r="G430" s="85" t="str">
-        <x:v>  · 가장 예쁜 면을 가까이 찍기</x:v>
+        <x:v>· 가장 예쁜 면을 가까이 찍기</x:v>
       </x:c>
       <x:c r="H430" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17229,7 +17229,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="G431" s="85" t="str">
-        <x:v>  · 천천히 5~10cm 정도만 다가가거나 옆으로 움직이기</x:v>
+        <x:v>· 천천히 5~10cm 정도만 다가가거나 옆으로 움직이기</x:v>
       </x:c>
       <x:c r="H431" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17264,7 +17264,7 @@
         <x:v>428</x:v>
       </x:c>
       <x:c r="G432" s="85" t="str">
-        <x:v>  · ★ 이 영상이 브이(V) 대신 들어갈 메인 홍보 컷입니다</x:v>
+        <x:v>· ★ 이 영상이 브이(V) 대신 들어갈 메인 홍보 컷입니다</x:v>
       </x:c>
       <x:c r="H432" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17367,7 +17367,7 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="G435" s="85" t="str">
-        <x:v>  · 메뉴판 전체를 찍지 말고 홍보할 한 항목만</x:v>
+        <x:v>· 메뉴판 전체를 찍지 말고 홍보할 한 항목만</x:v>
       </x:c>
       <x:c r="H435" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17402,7 +17402,7 @@
         <x:v>432</x:v>
       </x:c>
       <x:c r="G436" s="85" t="str">
-        <x:v>  · 가격이나 혜택이 있다면 화면에서 바로 읽히게</x:v>
+        <x:v>· 가격이나 혜택이 있다면 화면에서 바로 읽히게</x:v>
       </x:c>
       <x:c r="H436" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17437,7 +17437,7 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="G437" s="85" t="str">
-        <x:v>  · 손으로 메뉴를 가리키거나 상품을 들어도 됩니다</x:v>
+        <x:v>· 손으로 메뉴를 가리키거나 상품을 들어도 됩니다</x:v>
       </x:c>
       <x:c r="H437" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17540,7 +17540,7 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="G440" s="85" t="str">
-        <x:v>  · 소스 붓기 / 토핑 올리기 / 포장 / 제품 사용 / 결과물 보여주기 등</x:v>
+        <x:v>· 소스 붓기 / 토핑 올리기 / 포장 / 제품 사용 / 결과물 보여주기 등</x:v>
       </x:c>
       <x:c r="H440" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17575,7 +17575,7 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="G441" s="85" t="str">
-        <x:v>  · 한 동작만 짧고 분명하게 찍기</x:v>
+        <x:v>· 한 동작만 짧고 분명하게 찍기</x:v>
       </x:c>
       <x:c r="H441" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17678,7 +17678,7 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="G444" s="85" t="str">
-        <x:v>  · 간판 / 매장 입구 / 완성 메뉴를 들고 있는 장면 등</x:v>
+        <x:v>· 간판 / 매장 입구 / 완성 메뉴를 들고 있는 장면 등</x:v>
       </x:c>
       <x:c r="H444" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17713,7 +17713,7 @@
         <x:v>441</x:v>
       </x:c>
       <x:c r="G445" s="85" t="str">
-        <x:v>  · 마지막 문구와 함께 쓸 수 있는 단순한 화면</x:v>
+        <x:v>· 마지막 문구와 함께 쓸 수 있는 단순한 화면</x:v>
       </x:c>
       <x:c r="H445" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17816,7 +17816,7 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="G448" s="85" t="str">
-        <x:v>  · 춤 영상은 중간중간 끊어서 찍지 말고 한 번에 끝까지 찍기</x:v>
+        <x:v>· 춤 영상은 중간중간 끊어서 찍지 말고 한 번에 끝까지 찍기</x:v>
       </x:c>
       <x:c r="H448" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17851,7 +17851,7 @@
         <x:v>445</x:v>
       </x:c>
       <x:c r="G449" s="85" t="str">
-        <x:v>  · 브이 포인트 직전에 카메라 쪽으로 다가오지 않기</x:v>
+        <x:v>· 브이 포인트 직전에 카메라 쪽으로 다가오지 않기</x:v>
       </x:c>
       <x:c r="H449" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17886,7 +17886,7 @@
         <x:v>446</x:v>
       </x:c>
       <x:c r="G450" s="85" t="str">
-        <x:v>  · 춤 영상과 홍보 영상을 각각 따로 찍기</x:v>
+        <x:v>· 춤 영상과 홍보 영상을 각각 따로 찍기</x:v>
       </x:c>
       <x:c r="H450" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17921,7 +17921,7 @@
         <x:v>447</x:v>
       </x:c>
       <x:c r="G451" s="85" t="str">
-        <x:v>  · 홍보 영상은 사진처럼 멈춰 있지 말고 아주 작은 움직임이라도 넣기</x:v>
+        <x:v>· 홍보 영상은 사진처럼 멈춰 있지 말고 아주 작은 움직임이라도 넣기</x:v>
       </x:c>
       <x:c r="H451" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -17956,7 +17956,7 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="G452" s="85" t="str">
-        <x:v>  · 직원이 나오면 업로드 동의를 미리 받기</x:v>
+        <x:v>· 직원이 나오면 업로드 동의를 미리 받기</x:v>
       </x:c>
       <x:c r="H452" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18232,7 +18232,7 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="G460" s="85" t="str">
-        <x:v>  ① 오츠카레 썸머 안무를 처음부터 끝까지 춘 메인 영상</x:v>
+        <x:v>① 오츠카레 썸머 안무를 처음부터 끝까지 춘 메인 영상</x:v>
       </x:c>
       <x:c r="H460" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18267,7 +18267,7 @@
         <x:v>457</x:v>
       </x:c>
       <x:c r="G461" s="85" t="str">
-        <x:v>  ② 대표 메뉴/상품 클로즈업</x:v>
+        <x:v>② 대표 메뉴/상품 클로즈업</x:v>
       </x:c>
       <x:c r="H461" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18302,7 +18302,7 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="G462" s="85" t="str">
-        <x:v>  ③ 메뉴명·가격 또는 핵심 혜택</x:v>
+        <x:v>③ 메뉴명·가격 또는 핵심 혜택</x:v>
       </x:c>
       <x:c r="H462" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18337,7 +18337,7 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="G463" s="85" t="str">
-        <x:v>  ④ 만드는 장면/디테일</x:v>
+        <x:v>④ 만드는 장면/디테일</x:v>
       </x:c>
       <x:c r="H463" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18681,7 +18681,7 @@
         <x:v>469</x:v>
       </x:c>
       <x:c r="G473" s="85" t="str">
-        <x:v>  · Pose/Hands 분석으로 실제 안무가 포함된 영상을 Dance Base로 분류합니다.</x:v>
+        <x:v>· Pose/Hands 분석으로 실제 안무가 포함된 영상을 Dance Base로 분류합니다.</x:v>
       </x:c>
       <x:c r="H473" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18716,7 +18716,7 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="G474" s="85" t="str">
-        <x:v>  · 나머지 영상은 시각 정보와 프로젝트의 홍보 대상을 함께 분석해</x:v>
+        <x:v>· 나머지 영상은 시각 정보와 프로젝트의 홍보 대상을 함께 분석해</x:v>
       </x:c>
       <x:c r="H474" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18751,7 +18751,7 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="G475" s="85" t="str">
-        <x:v>      P1 = 대표 메뉴/상품 Hero Close-up</x:v>
+        <x:v>P1 = 대표 메뉴/상품 Hero Close-up</x:v>
       </x:c>
       <x:c r="H475" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18786,7 +18786,7 @@
         <x:v>472</x:v>
       </x:c>
       <x:c r="G476" s="85" t="str">
-        <x:v>      P2 = 메뉴명·가격 또는 핵심 혜택</x:v>
+        <x:v>P2 = 메뉴명·가격 또는 핵심 혜택</x:v>
       </x:c>
       <x:c r="H476" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18821,7 +18821,7 @@
         <x:v>473</x:v>
       </x:c>
       <x:c r="G477" s="85" t="str">
-        <x:v>      P3 = 만드는 장면/사용 장면/디테일</x:v>
+        <x:v>P3 = 만드는 장면/사용 장면/디테일</x:v>
       </x:c>
       <x:c r="H477" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18856,7 +18856,7 @@
         <x:v>474</x:v>
       </x:c>
       <x:c r="G478" s="85" t="str">
-        <x:v>      P4 = CTA용 화면</x:v>
+        <x:v>P4 = CTA용 화면</x:v>
       </x:c>
       <x:c r="H478" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18891,7 +18891,7 @@
         <x:v>475</x:v>
       </x:c>
       <x:c r="G479" s="85" t="str">
-        <x:v>    으로 자동 분류합니다.</x:v>
+        <x:v>으로 자동 분류합니다.</x:v>
       </x:c>
       <x:c r="H479" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -18926,7 +18926,7 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="G480" s="85" t="str">
-        <x:v>  · 여러 후보가 있으면 선명도, 피사체 점유율, 구도 안정성 기준으로 가장 적합한 컷을 선택합니다.</x:v>
+        <x:v>· 여러 후보가 있으면 선명도, 피사체 점유율, 구도 안정성 기준으로 가장 적합한 컷을 선택합니다.</x:v>
       </x:c>
       <x:c r="H480" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19029,7 +19029,7 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="G483" s="85" t="str">
-        <x:v>  · 상업 이용 가능 여부를 확인한 후렴 음원을 자동 로드합니다.</x:v>
+        <x:v>· 상업 이용 가능 여부를 확인한 후렴 음원을 자동 로드합니다.</x:v>
       </x:c>
       <x:c r="H483" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19064,7 +19064,7 @@
         <x:v>480</x:v>
       </x:c>
       <x:c r="G484" s="85" t="str">
-        <x:v>  · Dance Base 전체를 후렴 구간에 맞춰 정렬합니다.</x:v>
+        <x:v>· Dance Base 전체를 후렴 구간에 맞춰 정렬합니다.</x:v>
       </x:c>
       <x:c r="H484" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19099,7 +19099,7 @@
         <x:v>481</x:v>
       </x:c>
       <x:c r="G485" s="85" t="str">
-        <x:v>  · 필요한 경우 ±4% 이내의 미세 리타임만 적용합니다.</x:v>
+        <x:v>· 필요한 경우 ±4% 이내의 미세 리타임만 적용합니다.</x:v>
       </x:c>
       <x:c r="H485" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19134,7 +19134,7 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="G486" s="85" t="str">
-        <x:v>  · 댄스 영상의 시간축은 처음부터 끝까지 연속 유지합니다.</x:v>
+        <x:v>· 댄스 영상의 시간축은 처음부터 끝까지 연속 유지합니다.</x:v>
       </x:c>
       <x:c r="H486" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19237,7 +19237,7 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="G489" s="85" t="str">
-        <x:v>  · MediaPipe Hands로 검지·중지는 펴지고 약지·소지는 접힌 V 포즈를 탐지합니다.</x:v>
+        <x:v>· MediaPipe Hands로 검지·중지는 펴지고 약지·소지는 접힌 V 포즈를 탐지합니다.</x:v>
       </x:c>
       <x:c r="H489" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19272,7 +19272,7 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="G490" s="85" t="str">
-        <x:v>  · 가장 명확한 primary_v_event를 자동 선정합니다.</x:v>
+        <x:v>· 가장 명확한 primary_v_event를 자동 선정합니다.</x:v>
       </x:c>
       <x:c r="H490" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19307,7 +19307,7 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="G491" s="85" t="str">
-        <x:v>  · 해당 순간 중심 0.4~0.7초를 W_V로 설정합니다.</x:v>
+        <x:v>· 해당 순간 중심 0.4~0.7초를 W_V로 설정합니다.</x:v>
       </x:c>
       <x:c r="H491" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19342,7 +19342,7 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="G492" s="85" t="str">
-        <x:v>  · W_V 동안 댄스 화면 대신 P1 대표 메뉴/상품 클로즈업을 자동 삽입합니다.</x:v>
+        <x:v>· W_V 동안 댄스 화면 대신 P1 대표 메뉴/상품 클로즈업을 자동 삽입합니다.</x:v>
       </x:c>
       <x:c r="H492" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19377,7 +19377,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="G493" s="85" t="str">
-        <x:v>  · 즉, "브이와 상품을 같이 보여주는 것"이 아니라</x:v>
+        <x:v>· 즉, "브이와 상품을 같이 보여주는 것"이 아니라</x:v>
       </x:c>
       <x:c r="H493" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19412,7 +19412,7 @@
         <x:v>490</x:v>
       </x:c>
       <x:c r="G494" s="85" t="str">
-        <x:v>    "브이가 나오는 순간 화면 자체가 상품으로 교체"되게 합니다.</x:v>
+        <x:v>"브이가 나오는 순간 화면 자체가 상품으로 교체"되게 합니다.</x:v>
       </x:c>
       <x:c r="H494" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19515,7 +19515,7 @@
         <x:v>493</x:v>
       </x:c>
       <x:c r="G497" s="85" t="str">
-        <x:v>  · 음원을 phrase 단위로 분석해 phrase_end[]를 추출합니다.</x:v>
+        <x:v>· 음원을 phrase 단위로 분석해 phrase_end[]를 추출합니다.</x:v>
       </x:c>
       <x:c r="H497" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19550,7 +19550,7 @@
         <x:v>494</x:v>
       </x:c>
       <x:c r="G498" s="85" t="str">
-        <x:v>  · phrase_end마다 필요한 홍보 컷을 자동 배치합니다.</x:v>
+        <x:v>· phrase_end마다 필요한 홍보 컷을 자동 배치합니다.</x:v>
       </x:c>
       <x:c r="H498" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19585,7 +19585,7 @@
         <x:v>495</x:v>
       </x:c>
       <x:c r="G499" s="85" t="str">
-        <x:v>      첫 번째 유효 지점 → P2 메뉴명/가격</x:v>
+        <x:v>첫 번째 유효 지점 → P2 메뉴명/가격</x:v>
       </x:c>
       <x:c r="H499" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19620,7 +19620,7 @@
         <x:v>496</x:v>
       </x:c>
       <x:c r="G500" s="85" t="str">
-        <x:v>      두 번째 유효 지점 → P3 만드는 장면/디테일</x:v>
+        <x:v>두 번째 유효 지점 → P3 만드는 장면/디테일</x:v>
       </x:c>
       <x:c r="H500" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19655,7 +19655,7 @@
         <x:v>497</x:v>
       </x:c>
       <x:c r="G501" s="85" t="str">
-        <x:v>      필요 시 세 번째 → P4 혜택/한정 메시지</x:v>
+        <x:v>필요 시 세 번째 → P4 혜택/한정 메시지</x:v>
       </x:c>
       <x:c r="H501" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19690,7 +19690,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="G502" s="85" t="str">
-        <x:v>  · 각 홍보 컷은 0.3~0.8초로 자동 트리밍합니다.</x:v>
+        <x:v>· 각 홍보 컷은 0.3~0.8초로 자동 트리밍합니다.</x:v>
       </x:c>
       <x:c r="H502" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19725,7 +19725,7 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="G503" s="85" t="str">
-        <x:v>  · V 이벤트와 phrase_end가 0.4초 안에 겹치면 하나로 병합하고 V 이벤트를 우선합니다.</x:v>
+        <x:v>· V 이벤트와 phrase_end가 0.4초 안에 겹치면 하나로 병합하고 V 이벤트를 우선합니다.</x:v>
       </x:c>
       <x:c r="H503" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19760,7 +19760,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="G504" s="85" t="str">
-        <x:v>  · 전체 홍보 인터럽트 비중이 25%를 넘지 않도록 자동 제한합니다.</x:v>
+        <x:v>· 전체 홍보 인터럽트 비중이 25%를 넘지 않도록 자동 제한합니다.</x:v>
       </x:c>
       <x:c r="H504" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19863,7 +19863,7 @@
         <x:v>503</x:v>
       </x:c>
       <x:c r="G507" s="85" t="str">
-        <x:v>  · BGM은 처음부터 끝까지 절대 끊지 않습니다.</x:v>
+        <x:v>· BGM은 처음부터 끝까지 절대 끊지 않습니다.</x:v>
       </x:c>
       <x:c r="H507" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19898,7 +19898,7 @@
         <x:v>504</x:v>
       </x:c>
       <x:c r="G508" s="85" t="str">
-        <x:v>  · Dance Base 역시 내부 타임라인에서는 계속 진행됩니다.</x:v>
+        <x:v>· Dance Base 역시 내부 타임라인에서는 계속 진행됩니다.</x:v>
       </x:c>
       <x:c r="H508" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19933,7 +19933,7 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="G509" s="85" t="str">
-        <x:v>  · 홍보 컷이 끝나면 멈췄던 춤으로 돌아가는 것이 아니라,</x:v>
+        <x:v>· 홍보 컷이 끝나면 멈췄던 춤으로 돌아가는 것이 아니라,</x:v>
       </x:c>
       <x:c r="H509" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -19968,7 +19968,7 @@
         <x:v>506</x:v>
       </x:c>
       <x:c r="G510" s="85" t="str">
-        <x:v>    이미 진행 중이던 춤의 다음 시점으로 즉시 복귀합니다.</x:v>
+        <x:v>이미 진행 중이던 춤의 다음 시점으로 즉시 복귀합니다.</x:v>
       </x:c>
       <x:c r="H510" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20003,7 +20003,7 @@
         <x:v>507</x:v>
       </x:c>
       <x:c r="G511" s="85" t="str">
-        <x:v>  · 이 규칙으로 "광고 때문에 춤이 멈추는 느낌"을 방지합니다.</x:v>
+        <x:v>· 이 규칙으로 "광고 때문에 춤이 멈추는 느낌"을 방지합니다.</x:v>
       </x:c>
       <x:c r="H511" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20106,7 +20106,7 @@
         <x:v>510</x:v>
       </x:c>
       <x:c r="G514" s="85" t="str">
-        <x:v>  · 홍보 컷은 하드컷을 기본으로 사용합니다.</x:v>
+        <x:v>· 홍보 컷은 하드컷을 기본으로 사용합니다.</x:v>
       </x:c>
       <x:c r="H514" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20141,7 +20141,7 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="G515" s="85" t="str">
-        <x:v>  · 필요 시 시작 2~3프레임에만 103%→100%의 아주 짧은 punch-in을 적용합니다.</x:v>
+        <x:v>· 필요 시 시작 2~3프레임에만 103%→100%의 아주 짧은 punch-in을 적용합니다.</x:v>
       </x:c>
       <x:c r="H515" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20176,7 +20176,7 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="G516" s="85" t="str">
-        <x:v>  · 첫 화면에는 짧은 훅 1줄을 자동 생성합니다.</x:v>
+        <x:v>· 첫 화면에는 짧은 훅 1줄을 자동 생성합니다.</x:v>
       </x:c>
       <x:c r="H516" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20211,7 +20211,7 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="G517" s="85" t="str">
-        <x:v>  · P2에는 {{promo.name}} · {{promo.price}},</x:v>
+        <x:v>· P2에는 {{promo.name}} · {{promo.price}},</x:v>
       </x:c>
       <x:c r="H517" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20246,7 +20246,7 @@
         <x:v>514</x:v>
       </x:c>
       <x:c r="G518" s="85" t="str">
-        <x:v>    P3에는 필요 시 {{promo.benefit}} 한 줄만 배치합니다.</x:v>
+        <x:v>P3에는 필요 시 {{promo.benefit}} 한 줄만 배치합니다.</x:v>
       </x:c>
       <x:c r="H518" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20281,7 +20281,7 @@
         <x:v>515</x:v>
       </x:c>
       <x:c r="G519" s="85" t="str">
-        <x:v>  · 0.5초 미만의 홍보 컷에는 긴 문장을 생성하지 않습니다.</x:v>
+        <x:v>· 0.5초 미만의 홍보 컷에는 긴 문장을 생성하지 않습니다.</x:v>
       </x:c>
       <x:c r="H519" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20316,7 +20316,7 @@
         <x:v>516</x:v>
       </x:c>
       <x:c r="G520" s="85" t="str">
-        <x:v>  · 마지막에는 "{{caption.message}}"와 CTA를 자동 배치합니다.</x:v>
+        <x:v>· 마지막에는 "{{caption.message}}"와 CTA를 자동 배치합니다.</x:v>
       </x:c>
       <x:c r="H520" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20419,7 +20419,7 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="G523" s="85" t="str">
-        <x:v>  · 마지막 홍보 컷 이후 최소 0.8초 이상 Dance Base로 복귀시킵니다.</x:v>
+        <x:v>· 마지막 홍보 컷 이후 최소 0.8초 이상 Dance Base로 복귀시킵니다.</x:v>
       </x:c>
       <x:c r="H523" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20454,7 +20454,7 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="G524" s="85" t="str">
-        <x:v>  · 마지막 포인트 안무 또는 포즈가 실제로 보이는지 검사합니다.</x:v>
+        <x:v>· 마지막 포인트 안무 또는 포즈가 실제로 보이는지 검사합니다.</x:v>
       </x:c>
       <x:c r="H524" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20489,7 +20489,7 @@
         <x:v>521</x:v>
       </x:c>
       <x:c r="G525" s="85" t="str">
-        <x:v>  · CTA는 마지막 동작을 가리지 않는 위치와 시점에 자동 배치합니다.</x:v>
+        <x:v>· CTA는 마지막 동작을 가리지 않는 위치와 시점에 자동 배치합니다.</x:v>
       </x:c>
       <x:c r="H525" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20592,7 +20592,7 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="G528" s="85" t="str">
-        <x:v>  · dance_base_continuity = true</x:v>
+        <x:v>· dance_base_continuity = true</x:v>
       </x:c>
       <x:c r="H528" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20627,7 +20627,7 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="G529" s="85" t="str">
-        <x:v>  · audio_continuity = true</x:v>
+        <x:v>· audio_continuity = true</x:v>
       </x:c>
       <x:c r="H529" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20662,7 +20662,7 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="G530" s="85" t="str">
-        <x:v>  · v_event_replace_sync_error_frames ≤ 1</x:v>
+        <x:v>· v_event_replace_sync_error_frames ≤ 1</x:v>
       </x:c>
       <x:c r="H530" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20697,7 +20697,7 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="G531" s="85" t="str">
-        <x:v>  · phrase_interrupt_sync_error_frames ≤ 1</x:v>
+        <x:v>· phrase_interrupt_sync_error_frames ≤ 1</x:v>
       </x:c>
       <x:c r="H531" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20732,7 +20732,7 @@
         <x:v>528</x:v>
       </x:c>
       <x:c r="G532" s="85" t="str">
-        <x:v>  · promo_interrupt_count = 2~4</x:v>
+        <x:v>· promo_interrupt_count = 2~4</x:v>
       </x:c>
       <x:c r="H532" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20767,7 +20767,7 @@
         <x:v>529</x:v>
       </x:c>
       <x:c r="G533" s="85" t="str">
-        <x:v>  · promo_interrupt_total_ratio ≤ 0.25</x:v>
+        <x:v>· promo_interrupt_total_ratio ≤ 0.25</x:v>
       </x:c>
       <x:c r="H533" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20802,7 +20802,7 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="G534" s="85" t="str">
-        <x:v>  · promo_clip_max_duration_sec ≤ 0.8</x:v>
+        <x:v>· promo_clip_max_duration_sec ≤ 0.8</x:v>
       </x:c>
       <x:c r="H534" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20837,7 +20837,7 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="G535" s="85" t="str">
-        <x:v>  · final_return_to_dance = true</x:v>
+        <x:v>· final_return_to_dance = true</x:v>
       </x:c>
       <x:c r="H535" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20872,7 +20872,7 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="G536" s="85" t="str">
-        <x:v>    를 검사합니다.</x:v>
+        <x:v>를 검사합니다.</x:v>
       </x:c>
       <x:c r="H536" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -20907,7 +20907,7 @@
         <x:v>533</x:v>
       </x:c>
       <x:c r="G537" s="85" t="str">
-        <x:v>  · 통과하면 1080x1920 / 30fps 완성본을 자동 렌더링합니다.</x:v>
+        <x:v>· 통과하면 1080x1920 / 30fps 완성본을 자동 렌더링합니다.</x:v>
       </x:c>
       <x:c r="H537" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -21010,7 +21010,7 @@
         <x:v>536</x:v>
       </x:c>
       <x:c r="G540" s="85" t="str">
-        <x:v>  · 안무가 중간에 끊김 → 메인 춤만 다시 촬영 요청</x:v>
+        <x:v>· 안무가 중간에 끊김 → 메인 춤만 다시 촬영 요청</x:v>
       </x:c>
       <x:c r="H540" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -21045,7 +21045,7 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="G541" s="85" t="str">
-        <x:v>  · V 포인트 인식 불가 → "브이 동작을 더 크게"라고 구체적으로 요청</x:v>
+        <x:v>· V 포인트 인식 불가 → "브이 동작을 더 크게"라고 구체적으로 요청</x:v>
       </x:c>
       <x:c r="H541" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -21080,7 +21080,7 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="G542" s="85" t="str">
-        <x:v>  · 대표 메뉴 클로즈업이 흐림 → P1 컷만 재촬영 요청</x:v>
+        <x:v>· 대표 메뉴 클로즈업이 흐림 → P1 컷만 재촬영 요청</x:v>
       </x:c>
       <x:c r="H542" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -21115,7 +21115,7 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="G543" s="85" t="str">
-        <x:v>  · 홍보 B-roll 부족 → 부족한 역할(P2/P3 등)만 추가 촬영 요청</x:v>
+        <x:v>· 홍보 B-roll 부족 → 부족한 역할(P2/P3 등)만 추가 촬영 요청</x:v>
       </x:c>
       <x:c r="H543" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -21150,7 +21150,7 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="G544" s="85" t="str">
-        <x:v>  · 사용 가능한 음원 없음 → 렌더링 전에 대체 음원 선택 단계로 라우팅</x:v>
+        <x:v>· 사용 가능한 음원 없음 → 렌더링 전에 대체 음원 선택 단계로 라우팅</x:v>
       </x:c>
       <x:c r="H544" s="85" t="str">
         <x:v>편집가이드_3종.md</x:v>
@@ -23936,1044 +23936,2804 @@
       </x:c>
     </x:row>
     <x:row r="627" ht="18" customHeight="1">
-      <x:c r="A627"/>
-      <x:c r="B627"/>
-      <x:c r="C627"/>
-      <x:c r="D627"/>
-      <x:c r="E627"/>
-      <x:c r="F627"/>
-      <x:c r="G627"/>
-      <x:c r="H627"/>
-      <x:c r="I627"/>
-      <x:c r="J627"/>
-      <x:c r="K627"/>
+      <x:c r="A627" t="str">
+        <x:v>jujutsu5f_line_0001</x:v>
+      </x:c>
+      <x:c r="B627" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C627" t="n">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c r="D627" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E627" t="str">
+        <x:v>HEADER</x:v>
+      </x:c>
+      <x:c r="F627" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G627" t="str">
+        <x:v># 업로드 가이드 영상 정밀 재분석 · 주술회전.mp4 · 5프레임 타임라인</x:v>
+      </x:c>
+      <x:c r="H627" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I627" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J627" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K627" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="628" ht="18" customHeight="1">
-      <x:c r="A628"/>
-      <x:c r="B628"/>
-      <x:c r="C628"/>
-      <x:c r="D628"/>
-      <x:c r="E628"/>
-      <x:c r="F628"/>
-      <x:c r="G628"/>
-      <x:c r="H628"/>
-      <x:c r="I628"/>
-      <x:c r="J628"/>
-      <x:c r="K628"/>
+      <x:c r="A628" t="str">
+        <x:v>jujutsu5f_line_0002</x:v>
+      </x:c>
+      <x:c r="B628" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C628" t="n">
+        <x:v>844</x:v>
+      </x:c>
+      <x:c r="D628" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E628" t="str">
+        <x:v>SOURCE_METADATA</x:v>
+      </x:c>
+      <x:c r="F628" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G628" t="str">
+        <x:v>- source_type: VIDEO_ANALYSIS / granularity: 5 frames (30fps에서 약 166.667ms)</x:v>
+      </x:c>
+      <x:c r="H628" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I628" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J628" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K628" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="629" ht="18" customHeight="1">
-      <x:c r="A629"/>
-      <x:c r="B629"/>
-      <x:c r="C629"/>
-      <x:c r="D629"/>
-      <x:c r="E629"/>
-      <x:c r="F629"/>
-      <x:c r="G629"/>
-      <x:c r="H629"/>
-      <x:c r="I629"/>
-      <x:c r="J629"/>
-      <x:c r="K629"/>
+      <x:c r="A629" t="str">
+        <x:v>jujutsu5f_line_0003</x:v>
+      </x:c>
+      <x:c r="B629" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C629" t="n">
+        <x:v>845</x:v>
+      </x:c>
+      <x:c r="D629" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E629" t="str">
+        <x:v>SOURCE_METADATA</x:v>
+      </x:c>
+      <x:c r="F629" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G629" t="str">
+        <x:v>- source_file: 주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="H629" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I629" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J629" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K629" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="630" ht="18" customHeight="1">
-      <x:c r="A630"/>
-      <x:c r="B630"/>
-      <x:c r="C630"/>
-      <x:c r="D630"/>
-      <x:c r="E630"/>
-      <x:c r="F630"/>
-      <x:c r="G630"/>
-      <x:c r="H630"/>
-      <x:c r="I630"/>
-      <x:c r="J630"/>
-      <x:c r="K630"/>
+      <x:c r="A630" t="str">
+        <x:v>jujutsu5f_line_0004</x:v>
+      </x:c>
+      <x:c r="B630" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C630" t="n">
+        <x:v>846</x:v>
+      </x:c>
+      <x:c r="D630" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E630" t="str">
+        <x:v>SOURCE_METADATA</x:v>
+      </x:c>
+      <x:c r="F630" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G630" t="str">
+        <x:v>- sha256: 9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="H630" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I630" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J630" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K630" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="631" ht="18" customHeight="1">
-      <x:c r="A631"/>
-      <x:c r="B631"/>
-      <x:c r="C631"/>
-      <x:c r="D631"/>
-      <x:c r="E631"/>
-      <x:c r="F631"/>
-      <x:c r="G631"/>
-      <x:c r="H631"/>
-      <x:c r="I631"/>
-      <x:c r="J631"/>
-      <x:c r="K631"/>
+      <x:c r="A631" t="str">
+        <x:v>jujutsu5f_line_0005</x:v>
+      </x:c>
+      <x:c r="B631" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C631" t="n">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="D631" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E631" t="str">
+        <x:v>SOURCE_METADATA</x:v>
+      </x:c>
+      <x:c r="F631" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G631" t="str">
+        <x:v>- video_metadata: 676×1204 · 30fps · H.264 · 372 frames · visual duration 12.400s; AAC 48kHz stereo · container duration 12.459s</x:v>
+      </x:c>
+      <x:c r="H631" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I631" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J631" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K631" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="632" ht="18" customHeight="1">
-      <x:c r="A632"/>
-      <x:c r="B632"/>
-      <x:c r="C632"/>
-      <x:c r="D632"/>
-      <x:c r="E632"/>
-      <x:c r="F632"/>
-      <x:c r="G632"/>
-      <x:c r="H632"/>
-      <x:c r="I632"/>
-      <x:c r="J632"/>
-      <x:c r="K632"/>
+      <x:c r="A632" t="str">
+        <x:v>jujutsu5f_line_0006</x:v>
+      </x:c>
+      <x:c r="B632" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C632" t="n">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c r="D632" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E632" t="str">
+        <x:v>AUDIO</x:v>
+      </x:c>
+      <x:c r="F632" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G632" t="str">
+        <x:v>- audio_reference: 분석상 tempo≈143.55 BPM, 첫 beat≈0.093s. 원본 음원 자체는 렌더링 자산으로 복제하지 않고 타이밍 참고에만 사용</x:v>
+      </x:c>
+      <x:c r="H632" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I632" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J632" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K632" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="633" ht="18" customHeight="1">
-      <x:c r="A633"/>
-      <x:c r="B633"/>
-      <x:c r="C633"/>
-      <x:c r="D633"/>
-      <x:c r="E633"/>
-      <x:c r="F633"/>
-      <x:c r="G633"/>
-      <x:c r="H633"/>
-      <x:c r="I633"/>
-      <x:c r="J633"/>
-      <x:c r="K633"/>
+      <x:c r="A633" t="str">
+        <x:v>jujutsu5f_line_0007</x:v>
+      </x:c>
+      <x:c r="B633" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C633" t="n">
+        <x:v>849</x:v>
+      </x:c>
+      <x:c r="D633" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E633" t="str">
+        <x:v>FRAME_ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F633" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G633" t="str">
+        <x:v>- frame_timeline: F000–F371 전체를 5프레임 블록 75개로 분해해 03_GUIDE_TEMPLATES(action_pattern/timing_rule)에 저장. 전환 블록은 내부 exact frame 이벤트를 별도로 기록</x:v>
+      </x:c>
+      <x:c r="H633" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I633" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J633" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K633" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="634" ht="18" customHeight="1">
-      <x:c r="A634"/>
-      <x:c r="B634"/>
-      <x:c r="C634"/>
-      <x:c r="D634"/>
-      <x:c r="E634"/>
-      <x:c r="F634"/>
-      <x:c r="G634"/>
-      <x:c r="H634"/>
-      <x:c r="I634"/>
-      <x:c r="J634"/>
-      <x:c r="K634"/>
+      <x:c r="A634" t="str">
+        <x:v>jujutsu5f_line_0008</x:v>
+      </x:c>
+      <x:c r="B634" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C634" t="n">
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="D634" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E634" t="str">
+        <x:v>TIMING</x:v>
+      </x:c>
+      <x:c r="F634" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G634" t="str">
+        <x:v>- hard_cuts: F59(1.967s) S1→S2, F159(5.300s) S2→S3, F262(8.733s) S3→S4, F362(12.067s) S4→S1 loop reset</x:v>
+      </x:c>
+      <x:c r="H634" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I634" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J634" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K634" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="635" ht="18" customHeight="1">
-      <x:c r="A635"/>
-      <x:c r="B635"/>
-      <x:c r="C635"/>
-      <x:c r="D635"/>
-      <x:c r="E635"/>
-      <x:c r="F635"/>
-      <x:c r="G635"/>
-      <x:c r="H635"/>
-      <x:c r="I635"/>
-      <x:c r="J635"/>
-      <x:c r="K635"/>
+      <x:c r="A635" t="str">
+        <x:v>jujutsu5f_line_0009</x:v>
+      </x:c>
+      <x:c r="B635" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C635" t="n">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="D635" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E635" t="str">
+        <x:v>TIMING</x:v>
+      </x:c>
+      <x:c r="F635" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G635" t="str">
+        <x:v>- reveal_A: F10–11 수직 전 프레임 모션블러 → F12(0.400s) 아이스 음료 등장 → F58까지 홀드</x:v>
+      </x:c>
+      <x:c r="H635" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I635" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J635" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K635" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="636" ht="18" customHeight="1">
-      <x:c r="A636"/>
-      <x:c r="B636"/>
-      <x:c r="C636"/>
-      <x:c r="D636"/>
-      <x:c r="E636"/>
-      <x:c r="F636"/>
-      <x:c r="G636"/>
-      <x:c r="H636"/>
-      <x:c r="I636"/>
-      <x:c r="J636"/>
-      <x:c r="K636"/>
+      <x:c r="A636" t="str">
+        <x:v>jujutsu5f_line_0010</x:v>
+      </x:c>
+      <x:c r="B636" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C636" t="n">
+        <x:v>852</x:v>
+      </x:c>
+      <x:c r="D636" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E636" t="str">
+        <x:v>TIMING</x:v>
+      </x:c>
+      <x:c r="F636" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G636" t="str">
+        <x:v>- reveal_B: F110(3.667s) 약 1.23x 디지털 펀치인 → F111 줌/라디얼 블러 → F112(3.733s) 붉은 음료 등장 → F158까지 펀치인 홀드</x:v>
+      </x:c>
+      <x:c r="H636" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I636" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J636" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K636" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="637" ht="18" customHeight="1">
-      <x:c r="A637"/>
-      <x:c r="B637"/>
-      <x:c r="C637"/>
-      <x:c r="D637"/>
-      <x:c r="E637"/>
-      <x:c r="F637"/>
-      <x:c r="G637"/>
-      <x:c r="H637"/>
-      <x:c r="I637"/>
-      <x:c r="J637"/>
-      <x:c r="K637"/>
+      <x:c r="A637" t="str">
+        <x:v>jujutsu5f_line_0011</x:v>
+      </x:c>
+      <x:c r="B637" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C637" t="n">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="D637" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E637" t="str">
+        <x:v>TIMING</x:v>
+      </x:c>
+      <x:c r="F637" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G637" t="str">
+        <x:v>- reveal_C: F210–211 수직 전 프레임 모션블러 → F212(7.067s) 케이크 등장 → F261까지 홀드</x:v>
+      </x:c>
+      <x:c r="H637" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I637" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J637" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K637" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="638" ht="18" customHeight="1">
-      <x:c r="A638"/>
-      <x:c r="B638"/>
-      <x:c r="C638"/>
-      <x:c r="D638"/>
-      <x:c r="E638"/>
-      <x:c r="F638"/>
-      <x:c r="G638"/>
-      <x:c r="H638"/>
-      <x:c r="I638"/>
-      <x:c r="J638"/>
-      <x:c r="K638"/>
+      <x:c r="A638" t="str">
+        <x:v>jujutsu5f_line_0012</x:v>
+      </x:c>
+      <x:c r="B638" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C638" t="n">
+        <x:v>854</x:v>
+      </x:c>
+      <x:c r="D638" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E638" t="str">
+        <x:v>TIMING</x:v>
+      </x:c>
+      <x:c r="F638" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G638" t="str">
+        <x:v>- reveal_D: F309부터 블러 시작, F310–311 강한 전 프레임 블러 → F312(10.400s) 빵/페이스트리 등장 → F361까지 홀드</x:v>
+      </x:c>
+      <x:c r="H638" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I638" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J638" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K638" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="639" ht="18" customHeight="1">
-      <x:c r="A639"/>
-      <x:c r="B639"/>
-      <x:c r="C639"/>
-      <x:c r="D639"/>
-      <x:c r="E639"/>
-      <x:c r="F639"/>
-      <x:c r="G639"/>
-      <x:c r="H639"/>
-      <x:c r="I639"/>
-      <x:c r="J639"/>
-      <x:c r="K639"/>
+      <x:c r="A639" t="str">
+        <x:v>jujutsu5f_line_0013</x:v>
+      </x:c>
+      <x:c r="B639" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C639" t="n">
+        <x:v>855</x:v>
+      </x:c>
+      <x:c r="D639" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E639" t="str">
+        <x:v>OVERLAY</x:v>
+      </x:c>
+      <x:c r="F639" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G639" t="str">
+        <x:v>- pip_reference: 상단 VIDEO_PIP가 전 구간 지속. 근사 bbox_px=(80,0,300,169), norm=(0.118,0.000,0.444,0.140), 불투명·무테. 정확 복제 시 사용자 제공/라이선스 확인된 영상 자산 필요</x:v>
+      </x:c>
+      <x:c r="H639" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I639" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J639" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K639" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="640" ht="18" customHeight="1">
-      <x:c r="A640"/>
-      <x:c r="B640"/>
-      <x:c r="C640"/>
-      <x:c r="D640"/>
-      <x:c r="E640"/>
-      <x:c r="F640"/>
-      <x:c r="G640"/>
-      <x:c r="H640"/>
-      <x:c r="I640"/>
-      <x:c r="J640"/>
-      <x:c r="K640"/>
+      <x:c r="A640" t="str">
+        <x:v>jujutsu5f_line_0014</x:v>
+      </x:c>
+      <x:c r="B640" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C640" t="n">
+        <x:v>856</x:v>
+      </x:c>
+      <x:c r="D640" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E640" t="str">
+        <x:v>FLOW_RULE</x:v>
+      </x:c>
+      <x:c r="F640" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G640" t="str">
+        <x:v>- global_edit: speed=1.0 throughout; fade/cross-dissolve 없음; 독립 자막 오버레이 없음; 색보정은 컷마다 바뀌지 않아 KEEP_SOURCE_COLOR로 기록</x:v>
+      </x:c>
+      <x:c r="H640" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I640" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J640" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K640" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="641" ht="18" customHeight="1">
-      <x:c r="A641"/>
-      <x:c r="B641"/>
-      <x:c r="C641"/>
-      <x:c r="D641"/>
-      <x:c r="E641"/>
-      <x:c r="F641"/>
-      <x:c r="G641"/>
-      <x:c r="H641"/>
-      <x:c r="I641"/>
-      <x:c r="J641"/>
-      <x:c r="K641"/>
+      <x:c r="A641" t="str">
+        <x:v>jujutsu5f_line_0015</x:v>
+      </x:c>
+      <x:c r="B641" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C641" t="n">
+        <x:v>857</x:v>
+      </x:c>
+      <x:c r="D641" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E641" t="str">
+        <x:v>CAPABILITY</x:v>
+      </x:c>
+      <x:c r="F641" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G641" t="str">
+        <x:v>- capability_gap: 현재 DB 정책의 실행 지원 범위로는 full-frame motion blur와 VIDEO_PIP가 미지원이므로 03_GUIDE_TEMPLATES(action_pattern/timing_rule)에서 NEEDS_IMPLEMENTATION으로 표시; 1.23x punch-in과 hard cut은 기본 편집 기능으로 재현 가능</x:v>
+      </x:c>
+      <x:c r="H641" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I641" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J641" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K641" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="642" ht="18" customHeight="1">
-      <x:c r="A642"/>
-      <x:c r="B642"/>
-      <x:c r="C642"/>
-      <x:c r="D642"/>
-      <x:c r="E642"/>
-      <x:c r="F642"/>
-      <x:c r="G642"/>
-      <x:c r="H642"/>
-      <x:c r="I642"/>
-      <x:c r="J642"/>
-      <x:c r="K642"/>
+      <x:c r="A642" t="str">
+        <x:v>jujutsu5f_line_0016</x:v>
+      </x:c>
+      <x:c r="B642" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C642" t="n">
+        <x:v>858</x:v>
+      </x:c>
+      <x:c r="D642" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E642" t="str">
+        <x:v>MAPPING</x:v>
+      </x:c>
+      <x:c r="F642" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G642" t="str">
+        <x:v>- execution_mapping: 기존 gt_jujutsu_transition_v2와 5구간 gt_jujutsu_transition_v3는 SUPERSEDED로 보존하고, 현재 실행 템플릿은 18개 비중첩 구간의 gt_jujutsu_transition_v4를 ACTIVE/REFERENCE_ONLY로 사용</x:v>
+      </x:c>
+      <x:c r="H642" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I642" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J642" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K642" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="643" ht="18" customHeight="1">
-      <x:c r="A643"/>
-      <x:c r="B643"/>
-      <x:c r="C643"/>
-      <x:c r="D643"/>
-      <x:c r="E643"/>
-      <x:c r="F643"/>
-      <x:c r="G643"/>
-      <x:c r="H643"/>
-      <x:c r="I643"/>
-      <x:c r="J643"/>
-      <x:c r="K643"/>
+      <x:c r="A643" t="str">
+        <x:v>jujutsu5f_line_0017</x:v>
+      </x:c>
+      <x:c r="B643" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C643" t="n">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="D643" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E643" t="str">
+        <x:v>LAYER_ORDER</x:v>
+      </x:c>
+      <x:c r="F643" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G643" t="str">
+        <x:v>- layer_order: MAIN_VIDEO_BASE → MAIN_LAYER_EFFECTS → VIDEO_PIP_TOP. 블러/줌 구간에서도 PIP는 화면 고정·선명 상태를 유지하며 메인 레이어 효과의 영향을 받지 않음.</x:v>
+      </x:c>
+      <x:c r="H643" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I643" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J643" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K643" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="644" ht="18" customHeight="1">
-      <x:c r="A644"/>
-      <x:c r="B644"/>
-      <x:c r="C644"/>
-      <x:c r="D644"/>
-      <x:c r="E644"/>
-      <x:c r="F644"/>
-      <x:c r="G644"/>
-      <x:c r="H644"/>
-      <x:c r="I644"/>
-      <x:c r="J644"/>
-      <x:c r="K644"/>
+      <x:c r="A644" t="str">
+        <x:v>jujutsu5f_line_0018</x:v>
+      </x:c>
+      <x:c r="B644" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C644" t="n">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c r="D644" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E644" t="str">
+        <x:v>REVEAL_MECHANISM</x:v>
+      </x:c>
+      <x:c r="F644" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G644" t="str">
+        <x:v>- reveal_mechanism: F12/F112/F212/F312 상품 등장은 이미지 삽입이 아니라 동일 카메라 구도의 전(빈손)/후(상품 있음) 촬영 테이크를 손·얼굴 위치에 맞춘 MATCH_CUT로 재현해야 함.</x:v>
+      </x:c>
+      <x:c r="H644" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I644" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J644" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K644" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="645" ht="18" customHeight="1">
-      <x:c r="A645"/>
-      <x:c r="B645"/>
-      <x:c r="C645"/>
-      <x:c r="D645"/>
-      <x:c r="E645"/>
-      <x:c r="F645"/>
-      <x:c r="G645"/>
-      <x:c r="H645"/>
-      <x:c r="I645"/>
-      <x:c r="J645"/>
-      <x:c r="K645"/>
+      <x:c r="A645" t="str">
+        <x:v>jujutsu5f_line_0019</x:v>
+      </x:c>
+      <x:c r="B645" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C645" t="n">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c r="D645" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E645" t="str">
+        <x:v>CADENCE</x:v>
+      </x:c>
+      <x:c r="F645" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G645" t="str">
+        <x:v>- scene_cadence: S1=F0-58 59f(1.967s), S2=F59-158 100f(3.333s), S3=F159-261 103f(3.433s), S4=F262-361 100f(3.333s), loop reset=F362-371 10f(0.333s).</x:v>
+      </x:c>
+      <x:c r="H645" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I645" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J645" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K645" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="646" ht="18" customHeight="1">
-      <x:c r="A646"/>
-      <x:c r="B646"/>
-      <x:c r="C646"/>
-      <x:c r="D646"/>
-      <x:c r="E646"/>
-      <x:c r="F646"/>
-      <x:c r="G646"/>
-      <x:c r="H646"/>
-      <x:c r="I646"/>
-      <x:c r="J646"/>
-      <x:c r="K646"/>
+      <x:c r="A646" t="str">
+        <x:v>jujutsu5f_line_0020</x:v>
+      </x:c>
+      <x:c r="B646" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C646" t="n">
+        <x:v>862</x:v>
+      </x:c>
+      <x:c r="D646" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E646" t="str">
+        <x:v>EFFECT_SCOPE</x:v>
+      </x:c>
+      <x:c r="F646" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G646" t="str">
+        <x:v>- effect_scope: F10-11/F210-211/F309-311 블러와 F110~158 1.23x 펀치인은 MAIN_VIDEO에만 적용. VIDEO_PIP는 effect chain 이후 상단 레이어로 합성.</x:v>
+      </x:c>
+      <x:c r="H646" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I646" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J646" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K646" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="647" ht="18" customHeight="1">
-      <x:c r="A647"/>
-      <x:c r="B647"/>
-      <x:c r="C647"/>
-      <x:c r="D647"/>
-      <x:c r="E647"/>
-      <x:c r="F647"/>
-      <x:c r="G647"/>
-      <x:c r="H647"/>
-      <x:c r="I647"/>
-      <x:c r="J647"/>
-      <x:c r="K647"/>
+      <x:c r="A647" t="str">
+        <x:v>jujutsu5f_line_0021</x:v>
+      </x:c>
+      <x:c r="B647" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C647" t="n">
+        <x:v>863</x:v>
+      </x:c>
+      <x:c r="D647" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E647" t="str">
+        <x:v>PIP_COMPOSITE</x:v>
+      </x:c>
+      <x:c r="F647" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G647" t="str">
+        <x:v>- pip_composite: 전 구간 VIDEO_PIP 근사 bbox_px=(80,0,300,169), norm=(0.118,0.000,0.444,0.140), opaque/no-border/screen-fixed. 정확 복제 시 라이선스 또는 사용자 제공 자산 필요.</x:v>
+      </x:c>
+      <x:c r="H647" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I647" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J647" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K647" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="648" ht="18" customHeight="1">
-      <x:c r="A648"/>
-      <x:c r="B648"/>
-      <x:c r="C648"/>
-      <x:c r="D648"/>
-      <x:c r="E648"/>
-      <x:c r="F648"/>
-      <x:c r="G648"/>
-      <x:c r="H648"/>
-      <x:c r="I648"/>
-      <x:c r="J648"/>
-      <x:c r="K648"/>
+      <x:c r="A648" t="str">
+        <x:v>jujutsu5f_line_0022</x:v>
+      </x:c>
+      <x:c r="B648" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C648" t="n">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="D648" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E648" t="str">
+        <x:v>MATCH_ANCHOR</x:v>
+      </x:c>
+      <x:c r="F648" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G648" t="str">
+        <x:v>- match_anchors: 여성 장면은 얼굴 중심+오른손 손가락 포즈+왼손 손목/손바닥, 남성 장면은 얼굴/안경 중심+팔/손목 중심선을 전후 테이크에서 고정해 상품 출현 점프를 최소화.</x:v>
+      </x:c>
+      <x:c r="H648" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I648" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J648" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K648" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="649" ht="18" customHeight="1">
-      <x:c r="A649"/>
-      <x:c r="B649"/>
-      <x:c r="C649"/>
-      <x:c r="D649"/>
-      <x:c r="E649"/>
-      <x:c r="F649"/>
-      <x:c r="G649"/>
-      <x:c r="H649"/>
-      <x:c r="I649"/>
-      <x:c r="J649"/>
-      <x:c r="K649"/>
+      <x:c r="A649" t="str">
+        <x:v>jujutsu5f_line_0023</x:v>
+      </x:c>
+      <x:c r="B649" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C649" t="n">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="D649" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E649" t="str">
+        <x:v>CANVAS</x:v>
+      </x:c>
+      <x:c r="F649" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G649" t="str">
+        <x:v>- output_canvas: 676×1204 portrait(≈9:16), main camera는 고정. S2 F110에서만 main layer 디지털 크롭 약 1.23x; 나머지는 1.0x.</x:v>
+      </x:c>
+      <x:c r="H649" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I649" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J649" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K649" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="650" ht="18" customHeight="1">
-      <x:c r="A650"/>
-      <x:c r="B650"/>
-      <x:c r="C650"/>
-      <x:c r="D650"/>
-      <x:c r="E650"/>
-      <x:c r="F650"/>
-      <x:c r="G650"/>
-      <x:c r="H650"/>
-      <x:c r="I650"/>
-      <x:c r="J650"/>
-      <x:c r="K650"/>
+      <x:c r="A650" t="str">
+        <x:v>jujutsu5f_line_0024</x:v>
+      </x:c>
+      <x:c r="B650" t="str">
+        <x:v>guidevideo_jujutsu_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C650" t="n">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="D650" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E650" t="str">
+        <x:v>MAPPING</x:v>
+      </x:c>
+      <x:c r="F650" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G650" t="str">
+        <x:v>- template_mapping: gt_jujutsu_transition_v4는 F0-F371을 18개 비중첩 실행 구간으로 정의하고 모든 기존 템플릿 필드 및 신규 exact-edit 필드를 채움. v3는 SUPERSEDED.</x:v>
+      </x:c>
+      <x:c r="H650" t="str">
+        <x:v>주술회전.mp4</x:v>
+      </x:c>
+      <x:c r="I650" t="str">
+        <x:v>9EB5299872F8F5079A943A51F848E6D74410AC75ECAB3DFD31F46D1A937099C0</x:v>
+      </x:c>
+      <x:c r="J650" t="str">
+        <x:v>gt_jujutsu_transition_v4</x:v>
+      </x:c>
+      <x:c r="K650" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="651" ht="18" customHeight="1">
-      <x:c r="A651"/>
-      <x:c r="B651"/>
-      <x:c r="C651"/>
-      <x:c r="D651"/>
-      <x:c r="E651"/>
-      <x:c r="F651"/>
-      <x:c r="G651"/>
-      <x:c r="H651"/>
-      <x:c r="I651"/>
-      <x:c r="J651"/>
-      <x:c r="K651"/>
+      <x:c r="A651" t="str">
+        <x:v>summer5f_line_0001</x:v>
+      </x:c>
+      <x:c r="B651" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C651" t="n">
+        <x:v>867</x:v>
+      </x:c>
+      <x:c r="D651" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E651" t="str">
+        <x:v>HEADER</x:v>
+      </x:c>
+      <x:c r="F651" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G651" t="str">
+        <x:v># 업로드 가이드 영상 정밀 재분석 · 오츠카레 썸머 챌린지 · 썸머(1).mp4 · 5프레임 타임라인</x:v>
+      </x:c>
+      <x:c r="H651" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I651" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J651" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K651" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="652" ht="18" customHeight="1">
-      <x:c r="A652"/>
-      <x:c r="B652"/>
-      <x:c r="C652"/>
-      <x:c r="D652"/>
-      <x:c r="E652"/>
-      <x:c r="F652"/>
-      <x:c r="G652"/>
-      <x:c r="H652"/>
-      <x:c r="I652"/>
-      <x:c r="J652"/>
-      <x:c r="K652"/>
+      <x:c r="A652" t="str">
+        <x:v>summer5f_line_0002</x:v>
+      </x:c>
+      <x:c r="B652" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C652" t="n">
+        <x:v>868</x:v>
+      </x:c>
+      <x:c r="D652" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E652" t="str">
+        <x:v>SOURCE_METADATA</x:v>
+      </x:c>
+      <x:c r="F652" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G652" t="str">
+        <x:v>- source_type: VIDEO_ANALYSIS / granularity: 5 frames (30fps에서 약 166.667ms)</x:v>
+      </x:c>
+      <x:c r="H652" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I652" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J652" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K652" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="653" ht="18" customHeight="1">
-      <x:c r="A653"/>
-      <x:c r="B653"/>
-      <x:c r="C653"/>
-      <x:c r="D653"/>
-      <x:c r="E653"/>
-      <x:c r="F653"/>
-      <x:c r="G653"/>
-      <x:c r="H653"/>
-      <x:c r="I653"/>
-      <x:c r="J653"/>
-      <x:c r="K653"/>
+      <x:c r="A653" t="str">
+        <x:v>summer5f_line_0003</x:v>
+      </x:c>
+      <x:c r="B653" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C653" t="n">
+        <x:v>869</x:v>
+      </x:c>
+      <x:c r="D653" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E653" t="str">
+        <x:v>SOURCE_METADATA</x:v>
+      </x:c>
+      <x:c r="F653" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G653" t="str">
+        <x:v>- source_file: 썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="H653" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I653" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J653" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K653" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="654" ht="18" customHeight="1">
-      <x:c r="A654"/>
-      <x:c r="B654"/>
-      <x:c r="C654"/>
-      <x:c r="D654"/>
-      <x:c r="E654"/>
-      <x:c r="F654"/>
-      <x:c r="G654"/>
-      <x:c r="H654"/>
-      <x:c r="I654"/>
-      <x:c r="J654"/>
-      <x:c r="K654"/>
+      <x:c r="A654" t="str">
+        <x:v>summer5f_line_0004</x:v>
+      </x:c>
+      <x:c r="B654" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C654" t="n">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c r="D654" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E654" t="str">
+        <x:v>SOURCE_METADATA</x:v>
+      </x:c>
+      <x:c r="F654" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G654" t="str">
+        <x:v>- sha256: 81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="H654" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I654" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J654" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K654" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="655" ht="18" customHeight="1">
-      <x:c r="A655"/>
-      <x:c r="B655"/>
-      <x:c r="C655"/>
-      <x:c r="D655"/>
-      <x:c r="E655"/>
-      <x:c r="F655"/>
-      <x:c r="G655"/>
-      <x:c r="H655"/>
-      <x:c r="I655"/>
-      <x:c r="J655"/>
-      <x:c r="K655"/>
+      <x:c r="A655" t="str">
+        <x:v>summer5f_line_0005</x:v>
+      </x:c>
+      <x:c r="B655" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C655" t="n">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="D655" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E655" t="str">
+        <x:v>SOURCE_METADATA</x:v>
+      </x:c>
+      <x:c r="F655" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G655" t="str">
+        <x:v>- video_metadata: 670×1110 · 30fps · H.264 · 384 frames · 12.800s; AAC 48kHz stereo · container 12.800s</x:v>
+      </x:c>
+      <x:c r="H655" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I655" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J655" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K655" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="656" ht="18" customHeight="1">
-      <x:c r="A656"/>
-      <x:c r="B656"/>
-      <x:c r="C656"/>
-      <x:c r="D656"/>
-      <x:c r="E656"/>
-      <x:c r="F656"/>
-      <x:c r="G656"/>
-      <x:c r="H656"/>
-      <x:c r="I656"/>
-      <x:c r="J656"/>
-      <x:c r="K656"/>
+      <x:c r="A656" t="str">
+        <x:v>summer5f_line_0006</x:v>
+      </x:c>
+      <x:c r="B656" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C656" t="n">
+        <x:v>872</x:v>
+      </x:c>
+      <x:c r="D656" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E656" t="str">
+        <x:v>CLASSIFICATION</x:v>
+      </x:c>
+      <x:c r="F656" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G656" t="str">
+        <x:v>- normalized_name: 오츠카레 썸머 챌린지 / guide_shortform_type: DANCE_MEME / single performer</x:v>
+      </x:c>
+      <x:c r="H656" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I656" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J656" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K656" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="657" ht="18" customHeight="1">
-      <x:c r="A657"/>
-      <x:c r="B657"/>
-      <x:c r="C657"/>
-      <x:c r="D657"/>
-      <x:c r="E657"/>
-      <x:c r="F657"/>
-      <x:c r="G657"/>
-      <x:c r="H657"/>
-      <x:c r="I657"/>
-      <x:c r="J657"/>
-      <x:c r="K657"/>
+      <x:c r="A657" t="str">
+        <x:v>summer5f_line_0007</x:v>
+      </x:c>
+      <x:c r="B657" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C657" t="n">
+        <x:v>873</x:v>
+      </x:c>
+      <x:c r="D657" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E657" t="str">
+        <x:v>CANVAS</x:v>
+      </x:c>
+      <x:c r="F657" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G657" t="str">
+        <x:v>- source_canvas: 670×1110 portrait screen-capture style. TikTok/플랫폼 재생 UI가 화면 상·하단에 지속 노출되지만 편집 템플릿 레이어로 복제하지 않음.</x:v>
+      </x:c>
+      <x:c r="H657" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I657" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J657" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K657" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="658" ht="18" customHeight="1">
-      <x:c r="A658"/>
-      <x:c r="B658"/>
-      <x:c r="C658"/>
-      <x:c r="D658"/>
-      <x:c r="E658"/>
-      <x:c r="F658"/>
-      <x:c r="G658"/>
-      <x:c r="H658"/>
-      <x:c r="I658"/>
-      <x:c r="J658"/>
-      <x:c r="K658"/>
+      <x:c r="A658" t="str">
+        <x:v>summer5f_line_0008</x:v>
+      </x:c>
+      <x:c r="B658" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C658" t="n">
+        <x:v>874</x:v>
+      </x:c>
+      <x:c r="D658" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E658" t="str">
+        <x:v>AUDIO</x:v>
+      </x:c>
+      <x:c r="F658" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G658" t="str">
+        <x:v>- audio_reference: 분석상 tempo≈143.55 BPM, 첫 beat≈0.116s. 원본 음원은 렌더링 자산이 아니라 안무/컷 타이밍 참고용.</x:v>
+      </x:c>
+      <x:c r="H658" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I658" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J658" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K658" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="659" ht="18" customHeight="1">
-      <x:c r="A659"/>
-      <x:c r="B659"/>
-      <x:c r="C659"/>
-      <x:c r="D659"/>
-      <x:c r="E659"/>
-      <x:c r="F659"/>
-      <x:c r="G659"/>
-      <x:c r="H659"/>
-      <x:c r="I659"/>
-      <x:c r="J659"/>
-      <x:c r="K659"/>
+      <x:c r="A659" t="str">
+        <x:v>summer5f_line_0009</x:v>
+      </x:c>
+      <x:c r="B659" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C659" t="n">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="D659" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E659" t="str">
+        <x:v>FRAME_ANALYSIS</x:v>
+      </x:c>
+      <x:c r="F659" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G659" t="str">
+        <x:v>- frame_timeline: F000–F383 전체를 5프레임 블록 77개로 분해해 03_GUIDE_TEMPLATES(action_pattern/timing_rule)에 저장. 컷이 블록 내부에 있으면 exact frame 이벤트로 기록.</x:v>
+      </x:c>
+      <x:c r="H659" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I659" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J659" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K659" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="660" ht="18" customHeight="1">
-      <x:c r="A660"/>
-      <x:c r="B660"/>
-      <x:c r="C660"/>
-      <x:c r="D660"/>
-      <x:c r="E660"/>
-      <x:c r="F660"/>
-      <x:c r="G660"/>
-      <x:c r="H660"/>
-      <x:c r="I660"/>
-      <x:c r="J660"/>
-      <x:c r="K660"/>
+      <x:c r="A660" t="str">
+        <x:v>summer5f_line_0010</x:v>
+      </x:c>
+      <x:c r="B660" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C660" t="n">
+        <x:v>876</x:v>
+      </x:c>
+      <x:c r="D660" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E660" t="str">
+        <x:v>TIMING</x:v>
+      </x:c>
+      <x:c r="F660" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G660" t="str">
+        <x:v>- hard_cuts: F84(2.800s), F103(3.433s), F186(6.200s), F206(6.867s), F290(9.667s), F312(10.400s); 전부 0프레임 hard cut이며 fade/cross-dissolve 없음.</x:v>
+      </x:c>
+      <x:c r="H660" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I660" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J660" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K660" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="661" ht="18" customHeight="1">
-      <x:c r="A661"/>
-      <x:c r="B661"/>
-      <x:c r="C661"/>
-      <x:c r="D661"/>
-      <x:c r="E661"/>
-      <x:c r="F661"/>
-      <x:c r="G661"/>
-      <x:c r="H661"/>
-      <x:c r="I661"/>
-      <x:c r="J661"/>
-      <x:c r="K661"/>
+      <x:c r="A661" t="str">
+        <x:v>summer5f_line_0011</x:v>
+      </x:c>
+      <x:c r="B661" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C661" t="n">
+        <x:v>877</x:v>
+      </x:c>
+      <x:c r="D661" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E661" t="str">
+        <x:v>CADENCE</x:v>
+      </x:c>
+      <x:c r="F661" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G661" t="str">
+        <x:v>- shot_cadence: S1 WIDE F0-83 84f(2.800s) → S2 OVERHEAD F84-102 19f(0.633s) → S3 WIDE F103-185 83f(2.767s) → S4 OVERHEAD F186-205 20f(0.667s) → S5 WIDE F206-289 84f(2.800s) → S6 OVERHEAD F290-311 22f(0.733s) → S7 OVERHEAD F312-383 72f(2.400s).</x:v>
+      </x:c>
+      <x:c r="H661" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I661" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J661" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K661" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="662" ht="18" customHeight="1">
-      <x:c r="A662"/>
-      <x:c r="B662"/>
-      <x:c r="C662"/>
-      <x:c r="D662"/>
-      <x:c r="E662"/>
-      <x:c r="F662"/>
-      <x:c r="G662"/>
-      <x:c r="H662"/>
-      <x:c r="I662"/>
-      <x:c r="J662"/>
-      <x:c r="K662"/>
+      <x:c r="A662" t="str">
+        <x:v>summer5f_line_0012</x:v>
+      </x:c>
+      <x:c r="B662" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C662" t="n">
+        <x:v>878</x:v>
+      </x:c>
+      <x:c r="D662" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E662" t="str">
+        <x:v>CADENCE</x:v>
+      </x:c>
+      <x:c r="F662" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G662" t="str">
+        <x:v>- repeated_phrase_start: 와이드 안무가 F0, F103, F206에서 약 103프레임(3.433s) 간격으로 3회 반복. 음악 8박 프레이즈와 거의 동일한 주기.</x:v>
+      </x:c>
+      <x:c r="H662" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I662" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J662" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K662" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="663" ht="18" customHeight="1">
-      <x:c r="A663"/>
-      <x:c r="B663"/>
-      <x:c r="C663"/>
-      <x:c r="D663"/>
-      <x:c r="E663"/>
-      <x:c r="F663"/>
-      <x:c r="G663"/>
-      <x:c r="H663"/>
-      <x:c r="I663"/>
-      <x:c r="J663"/>
-      <x:c r="K663"/>
+      <x:c r="A663" t="str">
+        <x:v>summer5f_line_0013</x:v>
+      </x:c>
+      <x:c r="B663" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C663" t="n">
+        <x:v>879</x:v>
+      </x:c>
+      <x:c r="D663" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E663" t="str">
+        <x:v>CHOREOGRAPHY</x:v>
+      </x:c>
+      <x:c r="F663" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G663" t="str">
+        <x:v>- wide_phrase_pattern: 오른손 전방 뻗기/왼손 복부 고정 → 양손 어깨 위·손바닥 업 바운스 → 얼굴 근처 양손 포즈+한쪽 무릎 리프트 → 오른손 턱/볼+왼팔 허리 받침 좌우 스웨이.</x:v>
+      </x:c>
+      <x:c r="H663" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I663" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J663" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K663" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="664" ht="18" customHeight="1">
-      <x:c r="A664"/>
-      <x:c r="B664"/>
-      <x:c r="C664"/>
-      <x:c r="D664"/>
-      <x:c r="E664"/>
-      <x:c r="F664"/>
-      <x:c r="G664"/>
-      <x:c r="H664"/>
-      <x:c r="I664"/>
-      <x:c r="J664"/>
-      <x:c r="K664"/>
+      <x:c r="A664" t="str">
+        <x:v>summer5f_line_0014</x:v>
+      </x:c>
+      <x:c r="B664" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C664" t="n">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="D664" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E664" t="str">
+        <x:v>CHOREOGRAPHY</x:v>
+      </x:c>
+      <x:c r="F664" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G664" t="str">
+        <x:v>- overhead_A F84-102: 하이앵글 진입 후 한 손 V 사인을 얼굴/볼 옆에 두고 고개를 기울여 홀드.</x:v>
+      </x:c>
+      <x:c r="H664" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I664" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J664" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K664" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="665" ht="18" customHeight="1">
-      <x:c r="A665"/>
-      <x:c r="B665"/>
-      <x:c r="C665"/>
-      <x:c r="D665"/>
-      <x:c r="E665"/>
-      <x:c r="F665"/>
-      <x:c r="G665"/>
-      <x:c r="H665"/>
-      <x:c r="I665"/>
-      <x:c r="J665"/>
-      <x:c r="K665"/>
+      <x:c r="A665" t="str">
+        <x:v>summer5f_line_0015</x:v>
+      </x:c>
+      <x:c r="B665" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C665" t="n">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c r="D665" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E665" t="str">
+        <x:v>CHOREOGRAPHY</x:v>
+      </x:c>
+      <x:c r="F665" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G665" t="str">
+        <x:v>- overhead_B F186-205: 하이앵글 진입 후 양 주먹/손등을 양 볼 아래에 대고 눈을 감은 미소 포즈를 홀드.</x:v>
+      </x:c>
+      <x:c r="H665" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I665" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J665" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K665" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="666" ht="18" customHeight="1">
-      <x:c r="A666"/>
-      <x:c r="B666"/>
-      <x:c r="C666"/>
-      <x:c r="D666"/>
-      <x:c r="E666"/>
-      <x:c r="F666"/>
-      <x:c r="G666"/>
-      <x:c r="H666"/>
-      <x:c r="I666"/>
-      <x:c r="J666"/>
-      <x:c r="K666"/>
+      <x:c r="A666" t="str">
+        <x:v>summer5f_line_0016</x:v>
+      </x:c>
+      <x:c r="B666" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C666" t="n">
+        <x:v>882</x:v>
+      </x:c>
+      <x:c r="D666" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E666" t="str">
+        <x:v>CHOREOGRAPHY</x:v>
+      </x:c>
+      <x:c r="F666" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G666" t="str">
+        <x:v>- overhead_C F290-311: 하이앵글 진입 후 손가락을 입술에 대고 키스/쉿처럼 입술을 오므린 포즈를 홀드.</x:v>
+      </x:c>
+      <x:c r="H666" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I666" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J666" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K666" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="667" ht="18" customHeight="1">
-      <x:c r="A667"/>
-      <x:c r="B667"/>
-      <x:c r="C667"/>
-      <x:c r="D667"/>
-      <x:c r="E667"/>
-      <x:c r="F667"/>
-      <x:c r="G667"/>
-      <x:c r="H667"/>
-      <x:c r="I667"/>
-      <x:c r="J667"/>
-      <x:c r="K667"/>
+      <x:c r="A667" t="str">
+        <x:v>summer5f_line_0017</x:v>
+      </x:c>
+      <x:c r="B667" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C667" t="n">
+        <x:v>883</x:v>
+      </x:c>
+      <x:c r="D667" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E667" t="str">
+        <x:v>CHOREOGRAPHY</x:v>
+      </x:c>
+      <x:c r="F667" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G667" t="str">
+        <x:v>- finale F312-383: 동일 오버헤드 구도에서 F312 점프컷으로 양팔 내린 중립 포즈 → F330 양팔 좌우 오픈 → F340 양손 V 포즈 진입 → F345-383 최종 V 포즈 홀드.</x:v>
+      </x:c>
+      <x:c r="H667" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I667" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J667" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K667" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="668" ht="18" customHeight="1">
-      <x:c r="A668"/>
-      <x:c r="B668"/>
-      <x:c r="C668"/>
-      <x:c r="D668"/>
-      <x:c r="E668"/>
-      <x:c r="F668"/>
-      <x:c r="G668"/>
-      <x:c r="H668"/>
-      <x:c r="I668"/>
-      <x:c r="J668"/>
-      <x:c r="K668"/>
+      <x:c r="A668" t="str">
+        <x:v>summer5f_line_0018</x:v>
+      </x:c>
+      <x:c r="B668" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C668" t="n">
+        <x:v>884</x:v>
+      </x:c>
+      <x:c r="D668" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E668" t="str">
+        <x:v>FLOW_RULE</x:v>
+      </x:c>
+      <x:c r="F668" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G668" t="str">
+        <x:v>- global_edit: speed=1.0 throughout; digital zoom/blur/flash/film grain/transition effect 없음; 모든 장면 연결은 hard cut only.</x:v>
+      </x:c>
+      <x:c r="H668" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I668" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J668" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K668" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="669" ht="18" customHeight="1">
-      <x:c r="A669"/>
-      <x:c r="B669"/>
-      <x:c r="C669"/>
-      <x:c r="D669"/>
-      <x:c r="E669"/>
-      <x:c r="F669"/>
-      <x:c r="G669"/>
-      <x:c r="H669"/>
-      <x:c r="I669"/>
-      <x:c r="J669"/>
-      <x:c r="K669"/>
+      <x:c r="A669" t="str">
+        <x:v>summer5f_line_0019</x:v>
+      </x:c>
+      <x:c r="B669" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C669" t="n">
+        <x:v>885</x:v>
+      </x:c>
+      <x:c r="D669" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E669" t="str">
+        <x:v>CAMERA</x:v>
+      </x:c>
+      <x:c r="F669" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G669" t="str">
+        <x:v>- CAMERA_A_WIDE: 세로 풀바디 정면 와이드. 출연자 전신/발을 포함하고 좌측 나무·우측 가로등/표지 기둥의 배경 배치를 반복 테이크에서 최대한 유지.</x:v>
+      </x:c>
+      <x:c r="H669" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I669" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J669" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K669" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="670" ht="18" customHeight="1">
-      <x:c r="A670"/>
-      <x:c r="B670"/>
-      <x:c r="C670"/>
-      <x:c r="D670"/>
-      <x:c r="E670"/>
-      <x:c r="F670"/>
-      <x:c r="G670"/>
-      <x:c r="H670"/>
-      <x:c r="I670"/>
-      <x:c r="J670"/>
-      <x:c r="K670"/>
+      <x:c r="A670" t="str">
+        <x:v>summer5f_line_0020</x:v>
+      </x:c>
+      <x:c r="B670" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C670" t="n">
+        <x:v>886</x:v>
+      </x:c>
+      <x:c r="D670" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E670" t="str">
+        <x:v>CAMERA</x:v>
+      </x:c>
+      <x:c r="F670" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G670" t="str">
+        <x:v>- CAMERA_B_OVERHEAD: 출연자보다 높은 위치에서 아래로 기울인 하이앵글/오버헤드 근접. 얼굴이 크게 보이면서 발까지 남는 광각 원근을 유지. 디지털 줌으로 대체하지 않음.</x:v>
+      </x:c>
+      <x:c r="H670" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I670" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J670" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K670" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="671" ht="18" customHeight="1">
-      <x:c r="A671"/>
-      <x:c r="B671"/>
-      <x:c r="C671"/>
-      <x:c r="D671"/>
-      <x:c r="E671"/>
-      <x:c r="F671"/>
-      <x:c r="G671"/>
-      <x:c r="H671"/>
-      <x:c r="I671"/>
-      <x:c r="J671"/>
-      <x:c r="K671"/>
+      <x:c r="A671" t="str">
+        <x:v>summer5f_line_0021</x:v>
+      </x:c>
+      <x:c r="B671" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C671" t="n">
+        <x:v>887</x:v>
+      </x:c>
+      <x:c r="D671" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E671" t="str">
+        <x:v>MATCH_ANCHOR</x:v>
+      </x:c>
+      <x:c r="F671" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G671" t="str">
+        <x:v>- cut_match: 같은 출연자·의상·장소·조명을 유지하고 안무 악센트에서 와이드↔오버헤드로 즉시 전환. F312는 동일 CAMERA_B 배경/얼굴 중심을 맞춘 intentional jump cut.</x:v>
+      </x:c>
+      <x:c r="H671" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I671" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J671" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K671" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="672" ht="18" customHeight="1">
-      <x:c r="A672"/>
-      <x:c r="B672"/>
-      <x:c r="C672"/>
-      <x:c r="D672"/>
-      <x:c r="E672"/>
-      <x:c r="F672"/>
-      <x:c r="G672"/>
-      <x:c r="H672"/>
-      <x:c r="I672"/>
-      <x:c r="J672"/>
-      <x:c r="K672"/>
+      <x:c r="A672" t="str">
+        <x:v>summer5f_line_0022</x:v>
+      </x:c>
+      <x:c r="B672" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C672" t="n">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="D672" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E672" t="str">
+        <x:v>AUDIO_SYNC</x:v>
+      </x:c>
+      <x:c r="F672" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G672" t="str">
+        <x:v>- cut_audio_alignment: F84: beat B8 Δ-172ms / onset Δ+60ms | F103: beat B9 Δ+43ms / onset Δ+66ms | F186: beat B16 Δ-185ms / onset Δ-603ms | F206: beat B17 Δ+63ms / onset Δ+63ms | F290: beat B24 Δ-16ms / onset Δ-782ms | F312: beat B26 Δ-49ms / onset Δ-49ms</x:v>
+      </x:c>
+      <x:c r="H672" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I672" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J672" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K672" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="673" ht="18" customHeight="1">
-      <x:c r="A673"/>
-      <x:c r="B673"/>
-      <x:c r="C673"/>
-      <x:c r="D673"/>
-      <x:c r="E673"/>
-      <x:c r="F673"/>
-      <x:c r="G673"/>
-      <x:c r="H673"/>
-      <x:c r="I673"/>
-      <x:c r="J673"/>
-      <x:c r="K673"/>
+      <x:c r="A673" t="str">
+        <x:v>summer5f_line_0023</x:v>
+      </x:c>
+      <x:c r="B673" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C673" t="n">
+        <x:v>889</x:v>
+      </x:c>
+      <x:c r="D673" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E673" t="str">
+        <x:v>OVERLAY</x:v>
+      </x:c>
+      <x:c r="F673" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G673" t="str">
+        <x:v>- platform_ui_rule: 소스의 pause/CC/프로필/@Regina/구독/음악 저장 등 플랫폼 UI는 화면 녹화 흔적이며 템플릿 요소가 아님. 생성·합성 금지.</x:v>
+      </x:c>
+      <x:c r="H673" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I673" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J673" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K673" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="674" ht="18" customHeight="1">
-      <x:c r="A674"/>
-      <x:c r="B674"/>
-      <x:c r="C674"/>
-      <x:c r="D674"/>
-      <x:c r="E674"/>
-      <x:c r="F674"/>
-      <x:c r="G674"/>
-      <x:c r="H674"/>
-      <x:c r="I674"/>
-      <x:c r="J674"/>
-      <x:c r="K674"/>
+      <x:c r="A674" t="str">
+        <x:v>summer5f_line_0024</x:v>
+      </x:c>
+      <x:c r="B674" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C674" t="n">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="D674" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E674" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="F674" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G674" t="str">
+        <x:v>- content_text: 별도 챌린지 자막/CTA/메뉴 텍스트는 관찰되지 않음. 정확 재현 템플릿에는 콘텐츠 자막을 자동 추가하지 않음.</x:v>
+      </x:c>
+      <x:c r="H674" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I674" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J674" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K674" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="675" ht="18" customHeight="1">
-      <x:c r="A675"/>
-      <x:c r="B675"/>
-      <x:c r="C675"/>
-      <x:c r="D675"/>
-      <x:c r="E675"/>
-      <x:c r="F675"/>
-      <x:c r="G675"/>
-      <x:c r="H675"/>
-      <x:c r="I675"/>
-      <x:c r="J675"/>
-      <x:c r="K675"/>
+      <x:c r="A675" t="str">
+        <x:v>summer5f_line_0025</x:v>
+      </x:c>
+      <x:c r="B675" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C675" t="n">
+        <x:v>891</x:v>
+      </x:c>
+      <x:c r="D675" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E675" t="str">
+        <x:v>COLOR</x:v>
+      </x:c>
+      <x:c r="F675" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G675" t="str">
+        <x:v>- color_rule: 자연광/원본 색감을 유지하고 wide/overhead 테이크 사이 노출·화이트밸런스만 최대한 일치. 컷에 맞춘 별도 컬러 효과는 관찰되지 않음.</x:v>
+      </x:c>
+      <x:c r="H675" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I675" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J675" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K675" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="676" ht="18" customHeight="1">
-      <x:c r="A676"/>
-      <x:c r="B676"/>
-      <x:c r="C676"/>
-      <x:c r="D676"/>
-      <x:c r="E676"/>
-      <x:c r="F676"/>
-      <x:c r="G676"/>
-      <x:c r="H676"/>
-      <x:c r="I676"/>
-      <x:c r="J676"/>
-      <x:c r="K676"/>
+      <x:c r="A676" t="str">
+        <x:v>summer5f_line_0026</x:v>
+      </x:c>
+      <x:c r="B676" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C676" t="n">
+        <x:v>892</x:v>
+      </x:c>
+      <x:c r="D676" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E676" t="str">
+        <x:v>CAPABILITY</x:v>
+      </x:c>
+      <x:c r="F676" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G676" t="str">
+        <x:v>- renderer: 하드컷·트림·1.0배속만으로 편집 구조 재현 가능. 오버헤드 시점은 실제 두 번째 카메라 위치/테이크가 필요하며 합성 카메라 워프로 생성하지 않음.</x:v>
+      </x:c>
+      <x:c r="H676" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I676" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J676" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K676" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="677" ht="18" customHeight="1">
-      <x:c r="A677"/>
-      <x:c r="B677"/>
-      <x:c r="C677"/>
-      <x:c r="D677"/>
-      <x:c r="E677"/>
-      <x:c r="F677"/>
-      <x:c r="G677"/>
-      <x:c r="H677"/>
-      <x:c r="I677"/>
-      <x:c r="J677"/>
-      <x:c r="K677"/>
+      <x:c r="A677" t="str">
+        <x:v>summer5f_line_0027</x:v>
+      </x:c>
+      <x:c r="B677" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C677" t="n">
+        <x:v>893</x:v>
+      </x:c>
+      <x:c r="D677" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E677" t="str">
+        <x:v>MAPPING</x:v>
+      </x:c>
+      <x:c r="F677" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G677" t="str">
+        <x:v>- execution_mapping: 기존 gt_otsukare_summer_v2(구형 썸머.mp4 분석)는 SUPERSEDED로 보존하고, 현재 업로드 썸머(1).mp4 기준 gt_otsukare_summer_v3의 22개 비중첩 안무/컷 실행 구간을 ACTIVE로 사용.</x:v>
+      </x:c>
+      <x:c r="H677" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I677" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J677" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K677" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="678" ht="18" customHeight="1">
-      <x:c r="A678"/>
-      <x:c r="B678"/>
-      <x:c r="C678"/>
-      <x:c r="D678"/>
-      <x:c r="E678"/>
-      <x:c r="F678"/>
-      <x:c r="G678"/>
-      <x:c r="H678"/>
-      <x:c r="I678"/>
-      <x:c r="J678"/>
-      <x:c r="K678"/>
+      <x:c r="A678" t="str">
+        <x:v>summer5f_line_0028</x:v>
+      </x:c>
+      <x:c r="B678" t="str">
+        <x:v>guidevideo_summer_5f_20260825</x:v>
+      </x:c>
+      <x:c r="C678" t="n">
+        <x:v>894</x:v>
+      </x:c>
+      <x:c r="D678" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="E678" t="str">
+        <x:v>MAPPING</x:v>
+      </x:c>
+      <x:c r="F678" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G678" t="str">
+        <x:v>- template_extension: 03_GUIDE_TEMPLATES 기존 A:W에 dance_move_id, 손/상체/하체/표정, 카메라 각도, 컷 매칭, beat offset, 플랫폼 UI 제외 규칙을 추가.</x:v>
+      </x:c>
+      <x:c r="H678" t="str">
+        <x:v>썸머(1).mp4</x:v>
+      </x:c>
+      <x:c r="I678" t="str">
+        <x:v>81F5DCED70DFF4B7F6F0A5F6B393413FA6EB90AC1F8CF0027D90729257DA5CC9</x:v>
+      </x:c>
+      <x:c r="J678" t="str">
+        <x:v>gt_otsukare_summer_v3</x:v>
+      </x:c>
+      <x:c r="K678" t="str">
+        <x:v>VIDEO_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="679" ht="18" customHeight="1">
-      <x:c r="A679"/>
-      <x:c r="B679"/>
-      <x:c r="C679"/>
-      <x:c r="D679"/>
-      <x:c r="E679"/>
-      <x:c r="F679"/>
-      <x:c r="G679"/>
-      <x:c r="H679"/>
-      <x:c r="I679"/>
-      <x:c r="J679"/>
-      <x:c r="K679"/>
+      <x:c r="A679" t="str">
+        <x:v>jujutsu20260830_line_0001</x:v>
+      </x:c>
+      <x:c r="B679" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C679" t="n">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="D679" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E679" t="str">
+        <x:v>SUMMARY</x:v>
+      </x:c>
+      <x:c r="F679" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G679" t="str">
+        <x:v>- source_url: https://www.youtube.com/shorts/Aa-CGr9-c8E; 14초, 8컷, 4개 SETUP/REVEAL 매치컷 쌍, confidence=0.98, 촬영 난이도 ★★.</x:v>
+      </x:c>
+      <x:c r="H679" t="str">
+        <x:v>주술회전_1프레임분석.json</x:v>
+      </x:c>
+      <x:c r="I679" t="str">
+        <x:v>6868F640E082BDCFE1616CAF43F36267706D571358838896B5CDC74CC6646F31</x:v>
+      </x:c>
+      <x:c r="J679" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K679" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="680" ht="18" customHeight="1">
-      <x:c r="A680"/>
-      <x:c r="B680"/>
-      <x:c r="C680"/>
-      <x:c r="D680"/>
-      <x:c r="E680"/>
-      <x:c r="F680"/>
-      <x:c r="G680"/>
-      <x:c r="H680"/>
-      <x:c r="I680"/>
-      <x:c r="J680"/>
-      <x:c r="K680"/>
+      <x:c r="A680" t="str">
+        <x:v>jujutsu20260830_line_0002</x:v>
+      </x:c>
+      <x:c r="B680" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C680" t="n">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="D680" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E680" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F680" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G680" t="str">
+        <x:v>- S01 0-1500ms HOOK_SETUP: 인물 A가 고정 미디엄 구도에서 빈손 시그니처 포즈에 진입해 안정적으로 유지</x:v>
+      </x:c>
+      <x:c r="H680" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I680" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J680" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K680" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="681" ht="18" customHeight="1">
-      <x:c r="A681"/>
-      <x:c r="B681"/>
-      <x:c r="C681"/>
-      <x:c r="D681"/>
-      <x:c r="E681"/>
-      <x:c r="F681"/>
-      <x:c r="G681"/>
-      <x:c r="H681"/>
-      <x:c r="I681"/>
-      <x:c r="J681"/>
-      <x:c r="K681"/>
+      <x:c r="A681" t="str">
+        <x:v>jujutsu20260830_line_0003</x:v>
+      </x:c>
+      <x:c r="B681" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C681" t="n">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c r="D681" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E681" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F681" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G681" t="str">
+        <x:v>- S02 1500-3500ms MAGIC_REVEAL: S01과 동일 포즈·구도에서 인물 A의 손에 실제 음료가 나타난 상태로 시작해 결과를 유지</x:v>
+      </x:c>
+      <x:c r="H681" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I681" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J681" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K681" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="682" ht="18" customHeight="1">
-      <x:c r="A682"/>
-      <x:c r="B682"/>
-      <x:c r="C682"/>
-      <x:c r="D682"/>
-      <x:c r="E682"/>
-      <x:c r="F682"/>
-      <x:c r="G682"/>
-      <x:c r="H682"/>
-      <x:c r="I682"/>
-      <x:c r="J682"/>
-      <x:c r="K682"/>
+      <x:c r="A682" t="str">
+        <x:v>jujutsu20260830_line_0004</x:v>
+      </x:c>
+      <x:c r="B682" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C682" t="n">
+        <x:v>898</x:v>
+      </x:c>
+      <x:c r="D682" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E682" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F682" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G682" t="str">
+        <x:v>- S03 3500-5000ms SETUP: 인물 B가 같은 고정 카메라에서 새로운 빈손 포즈를 취하고 안정 구간을 유지</x:v>
+      </x:c>
+      <x:c r="H682" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I682" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J682" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K682" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="683" ht="18" customHeight="1">
-      <x:c r="A683"/>
-      <x:c r="B683"/>
-      <x:c r="C683"/>
-      <x:c r="D683"/>
-      <x:c r="E683"/>
-      <x:c r="F683"/>
-      <x:c r="G683"/>
-      <x:c r="H683"/>
-      <x:c r="I683"/>
-      <x:c r="J683"/>
-      <x:c r="K683"/>
+      <x:c r="A683" t="str">
+        <x:v>jujutsu20260830_line_0005</x:v>
+      </x:c>
+      <x:c r="B683" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C683" t="n">
+        <x:v>899</x:v>
+      </x:c>
+      <x:c r="D683" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E683" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F683" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G683" t="str">
+        <x:v>- S04 5000-7000ms MAGIC_REVEAL: S03과 동일 포즈·구도에서 인물 B의 손에 다른 음료가 나타난 상태로 전환</x:v>
+      </x:c>
+      <x:c r="H683" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I683" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J683" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K683" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="684" ht="18" customHeight="1">
-      <x:c r="A684"/>
-      <x:c r="B684"/>
-      <x:c r="C684"/>
-      <x:c r="D684"/>
-      <x:c r="E684"/>
-      <x:c r="F684"/>
-      <x:c r="G684"/>
-      <x:c r="H684"/>
-      <x:c r="I684"/>
-      <x:c r="J684"/>
-      <x:c r="K684"/>
+      <x:c r="A684" t="str">
+        <x:v>jujutsu20260830_line_0006</x:v>
+      </x:c>
+      <x:c r="B684" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C684" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="D684" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E684" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F684" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G684" t="str">
+        <x:v>- S05 7000-8500ms SETUP: 인물 A가 다시 등장해 케이크 공개 전 새 빈손 포즈를 안정적으로 유지</x:v>
+      </x:c>
+      <x:c r="H684" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I684" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J684" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K684" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="685" ht="18" customHeight="1">
-      <x:c r="A685"/>
-      <x:c r="B685"/>
-      <x:c r="C685"/>
-      <x:c r="D685"/>
-      <x:c r="E685"/>
-      <x:c r="F685"/>
-      <x:c r="G685"/>
-      <x:c r="H685"/>
-      <x:c r="I685"/>
-      <x:c r="J685"/>
-      <x:c r="K685"/>
+      <x:c r="A685" t="str">
+        <x:v>jujutsu20260830_line_0007</x:v>
+      </x:c>
+      <x:c r="B685" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C685" t="n">
+        <x:v>901</x:v>
+      </x:c>
+      <x:c r="D685" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E685" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F685" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G685" t="str">
+        <x:v>- S06 8500-10500ms MAGIC_REVEAL: S05와 동일 포즈·구도에서 인물 A가 실제 케이크 접시를 든 상태로 시작</x:v>
+      </x:c>
+      <x:c r="H685" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I685" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J685" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K685" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="686" ht="18" customHeight="1">
-      <x:c r="A686"/>
-      <x:c r="B686"/>
-      <x:c r="C686"/>
-      <x:c r="D686"/>
-      <x:c r="E686"/>
-      <x:c r="F686"/>
-      <x:c r="G686"/>
-      <x:c r="H686"/>
-      <x:c r="I686"/>
-      <x:c r="J686"/>
-      <x:c r="K686"/>
+      <x:c r="A686" t="str">
+        <x:v>jujutsu20260830_line_0008</x:v>
+      </x:c>
+      <x:c r="B686" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C686" t="n">
+        <x:v>902</x:v>
+      </x:c>
+      <x:c r="D686" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E686" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F686" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G686" t="str">
+        <x:v>- S07 10500-12000ms SETUP: 인물 B가 마지막 공개를 위한 빈손 포즈를 취하고 배경·카메라를 고정</x:v>
+      </x:c>
+      <x:c r="H686" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I686" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J686" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K686" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="687" ht="18" customHeight="1">
-      <x:c r="A687"/>
-      <x:c r="B687"/>
-      <x:c r="C687"/>
-      <x:c r="D687"/>
-      <x:c r="E687"/>
-      <x:c r="F687"/>
-      <x:c r="G687"/>
-      <x:c r="H687"/>
-      <x:c r="I687"/>
-      <x:c r="J687"/>
-      <x:c r="K687"/>
+      <x:c r="A687" t="str">
+        <x:v>jujutsu20260830_line_0009</x:v>
+      </x:c>
+      <x:c r="B687" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C687" t="n">
+        <x:v>903</x:v>
+      </x:c>
+      <x:c r="D687" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E687" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F687" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G687" t="str">
+        <x:v>- S08 12000-14000ms MAGIC_REVEAL: S07과 동일 포즈·구도에서 실제 빵 접시가 나타난 상태로 전환해 아웃트로 유지</x:v>
+      </x:c>
+      <x:c r="H687" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I687" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J687" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K687" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="688" ht="18" customHeight="1">
-      <x:c r="A688"/>
-      <x:c r="B688"/>
-      <x:c r="C688"/>
-      <x:c r="D688"/>
-      <x:c r="E688"/>
-      <x:c r="F688"/>
-      <x:c r="G688"/>
-      <x:c r="H688"/>
-      <x:c r="I688"/>
-      <x:c r="J688"/>
-      <x:c r="K688"/>
+      <x:c r="A688" t="str">
+        <x:v>jujutsu20260830_line_0010</x:v>
+      </x:c>
+      <x:c r="B688" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C688" t="n">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c r="D688" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E688" t="str">
+        <x:v>AUDIO_SYNC</x:v>
+      </x:c>
+      <x:c r="F688" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G688" t="str">
+        <x:v>- reveal_sfx_markers_ms: 1500, 5000, 8500, 12000; 모든 MAGIC_REVEAL 첫 프레임을 타격점에 정렬.</x:v>
+      </x:c>
+      <x:c r="H688" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I688" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J688" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K688" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="689" ht="18" customHeight="1">
-      <x:c r="A689"/>
-      <x:c r="B689"/>
-      <x:c r="C689"/>
-      <x:c r="D689"/>
-      <x:c r="E689"/>
-      <x:c r="F689"/>
-      <x:c r="G689"/>
-      <x:c r="H689"/>
-      <x:c r="I689"/>
-      <x:c r="J689"/>
-      <x:c r="K689"/>
+      <x:c r="A689" t="str">
+        <x:v>jujutsu20260830_line_0011</x:v>
+      </x:c>
+      <x:c r="B689" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C689" t="n">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c r="D689" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E689" t="str">
+        <x:v>MATCH_RULE</x:v>
+      </x:c>
+      <x:c r="F689" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G689" t="str">
+        <x:v>- 각 SETUP/REVEAL 쌍은 동일 인물·카메라·배경·포즈를 유지하고 SETUP에는 아이템이 없어야 하며 REVEAL에는 명확히 보여야 함.</x:v>
+      </x:c>
+      <x:c r="H689" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I689" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J689" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K689" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="690" ht="18" customHeight="1">
-      <x:c r="A690"/>
-      <x:c r="B690"/>
-      <x:c r="C690"/>
-      <x:c r="D690"/>
-      <x:c r="E690"/>
-      <x:c r="F690"/>
-      <x:c r="G690"/>
-      <x:c r="H690"/>
-      <x:c r="I690"/>
-      <x:c r="J690"/>
-      <x:c r="K690"/>
+      <x:c r="A690" t="str">
+        <x:v>jujutsu20260830_line_0012</x:v>
+      </x:c>
+      <x:c r="B690" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C690" t="n">
+        <x:v>906</x:v>
+      </x:c>
+      <x:c r="D690" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E690" t="str">
+        <x:v>OVERLAY</x:v>
+      </x:c>
+      <x:c r="F690" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G690" t="str">
+        <x:v>- 별도 자막·애니메이션 오버레이 없음. 플랫폼 UI와 레퍼런스 오디오는 편집 요소로 복제하지 않음.</x:v>
+      </x:c>
+      <x:c r="H690" t="str">
+        <x:v>주술회전_1프레임분석.json</x:v>
+      </x:c>
+      <x:c r="I690" t="str">
+        <x:v>6868F640E082BDCFE1616CAF43F36267706D571358838896B5CDC74CC6646F31</x:v>
+      </x:c>
+      <x:c r="J690" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K690" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="691" ht="18" customHeight="1">
-      <x:c r="A691"/>
-      <x:c r="B691"/>
-      <x:c r="C691"/>
-      <x:c r="D691"/>
-      <x:c r="E691"/>
-      <x:c r="F691"/>
-      <x:c r="G691"/>
-      <x:c r="H691"/>
-      <x:c r="I691"/>
-      <x:c r="J691"/>
-      <x:c r="K691"/>
+      <x:c r="A691" t="str">
+        <x:v>jujutsu20260830_line_0013</x:v>
+      </x:c>
+      <x:c r="B691" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C691" t="n">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="D691" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E691" t="str">
+        <x:v>VALIDATION</x:v>
+      </x:c>
+      <x:c r="F691" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G691" t="str">
+        <x:v>- hard_fail: 카메라 이동, 배경/인물 불일치, SETUP 아이템 노출, REVEAL 아이템 미노출, SFX 비동기, 경계 디졸브/페이드.</x:v>
+      </x:c>
+      <x:c r="H691" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I691" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J691" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K691" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="692" ht="18" customHeight="1">
-      <x:c r="A692"/>
-      <x:c r="B692"/>
-      <x:c r="C692"/>
-      <x:c r="D692"/>
-      <x:c r="E692"/>
-      <x:c r="F692"/>
-      <x:c r="G692"/>
-      <x:c r="H692"/>
-      <x:c r="I692"/>
-      <x:c r="J692"/>
-      <x:c r="K692"/>
+      <x:c r="A692" t="str">
+        <x:v>jujutsu20260830_line_0014</x:v>
+      </x:c>
+      <x:c r="B692" t="str">
+        <x:v>uploaded_jujutsu_json_20260830</x:v>
+      </x:c>
+      <x:c r="C692" t="n">
+        <x:v>908</x:v>
+      </x:c>
+      <x:c r="D692" t="str">
+        <x:v>jujutsu_transition</x:v>
+      </x:c>
+      <x:c r="E692" t="str">
+        <x:v>PROVENANCE</x:v>
+      </x:c>
+      <x:c r="F692" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G692" t="str">
+        <x:v>- 포즈/배경 정렬 점수·안정 구간 탐색·대체 테이크·미세 crop/translation 복구를 추가하되 수치는 서버 정책에서만 해결.</x:v>
+      </x:c>
+      <x:c r="H692" t="str">
+        <x:v>주술회전_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I692" t="str">
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+      </x:c>
+      <x:c r="J692" t="str">
+        <x:v>gt_jujutsu_transition_v5</x:v>
+      </x:c>
+      <x:c r="K692" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="693" ht="18" customHeight="1">
-      <x:c r="A693"/>
-      <x:c r="B693"/>
-      <x:c r="C693"/>
-      <x:c r="D693"/>
-      <x:c r="E693"/>
-      <x:c r="F693"/>
-      <x:c r="G693"/>
-      <x:c r="H693"/>
-      <x:c r="I693"/>
-      <x:c r="J693"/>
-      <x:c r="K693"/>
+      <x:c r="A693" t="str">
+        <x:v>donggeurio20260830_line_0001</x:v>
+      </x:c>
+      <x:c r="B693" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C693" t="n">
+        <x:v>909</x:v>
+      </x:c>
+      <x:c r="D693" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E693" t="str">
+        <x:v>SUMMARY</x:v>
+      </x:c>
+      <x:c r="F693" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G693" t="str">
+        <x:v>- source_url: https://www.youtube.com/shorts/iWyRoIJheV4; 실측 12.067초, 7컷 웜톤 카페 브이로그, shooting_difficulty: ★★, confidence=0.95.</x:v>
+      </x:c>
+      <x:c r="H693" t="str">
+        <x:v>동그리오_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I693" t="str">
+        <x:v>F8C3D8926CE141C84DF9C8077E82B5ABB6A90162A4E8BAF689277EDA85400A71</x:v>
+      </x:c>
+      <x:c r="J693" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K693" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="694" ht="18" customHeight="1">
-      <x:c r="A694"/>
-      <x:c r="B694"/>
-      <x:c r="C694"/>
-      <x:c r="D694"/>
-      <x:c r="E694"/>
-      <x:c r="F694"/>
-      <x:c r="G694"/>
-      <x:c r="H694"/>
-      <x:c r="I694"/>
-      <x:c r="J694"/>
-      <x:c r="K694"/>
+      <x:c r="A694" t="str">
+        <x:v>donggeurio20260830_line_0002</x:v>
+      </x:c>
+      <x:c r="B694" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C694" t="n">
+        <x:v>910</x:v>
+      </x:c>
+      <x:c r="D694" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E694" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F694" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G694" t="str">
+        <x:v>- S01 0-1033ms HOOK: 안정적인 벽면·공간 디테일을 고정 구도로 보여주고 중앙 프로젝트 타이틀 배치</x:v>
+      </x:c>
+      <x:c r="H694" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I694" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J694" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K694" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="695" ht="18" customHeight="1">
-      <x:c r="A695"/>
-      <x:c r="B695"/>
-      <x:c r="C695"/>
-      <x:c r="D695"/>
-      <x:c r="E695"/>
-      <x:c r="F695"/>
-      <x:c r="G695"/>
-      <x:c r="H695"/>
-      <x:c r="I695"/>
-      <x:c r="J695"/>
-      <x:c r="K695"/>
+      <x:c r="A695" t="str">
+        <x:v>donggeurio20260830_line_0003</x:v>
+      </x:c>
+      <x:c r="B695" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C695" t="n">
+        <x:v>911</x:v>
+      </x:c>
+      <x:c r="D695" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E695" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F695" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G695" t="str">
+        <x:v>- S02 1033-3767ms REVEAL: 메뉴 전체가 보이는 탑다운/하이앵글 샷에 1.00→1.05 선형 줌인과 하단 보조 텍스트 적용</x:v>
+      </x:c>
+      <x:c r="H695" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I695" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J695" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K695" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="696" ht="18" customHeight="1">
-      <x:c r="A696"/>
-      <x:c r="B696"/>
-      <x:c r="C696"/>
-      <x:c r="D696"/>
-      <x:c r="E696"/>
-      <x:c r="F696"/>
-      <x:c r="G696"/>
-      <x:c r="H696"/>
-      <x:c r="I696"/>
-      <x:c r="J696"/>
-      <x:c r="K696"/>
+      <x:c r="A696" t="str">
+        <x:v>donggeurio20260830_line_0004</x:v>
+      </x:c>
+      <x:c r="B696" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C696" t="n">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="D696" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E696" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F696" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G696" t="str">
+        <x:v>- S03 3767-4700ms AMBIENCE: 조명·좌석·인테리어를 보여주는 가장 매끄러운 우향 팬/측면 이동 구간 선택</x:v>
+      </x:c>
+      <x:c r="H696" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I696" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J696" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K696" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="697" ht="18" customHeight="1">
-      <x:c r="A697"/>
-      <x:c r="B697"/>
-      <x:c r="C697"/>
-      <x:c r="D697"/>
-      <x:c r="E697"/>
-      <x:c r="F697"/>
-      <x:c r="G697"/>
-      <x:c r="H697"/>
-      <x:c r="I697"/>
-      <x:c r="J697"/>
-      <x:c r="K697"/>
+      <x:c r="A697" t="str">
+        <x:v>donggeurio20260830_line_0005</x:v>
+      </x:c>
+      <x:c r="B697" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C697" t="n">
+        <x:v>913</x:v>
+      </x:c>
+      <x:c r="D697" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E697" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F697" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G697" t="str">
+        <x:v>- S04 4700-7000ms ACTION: 손이나 도구가 음식에 개입하는 클로즈업에서 동작 시작·피크·종료를 보존</x:v>
+      </x:c>
+      <x:c r="H697" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I697" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J697" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K697" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="698" ht="18" customHeight="1">
-      <x:c r="A698"/>
-      <x:c r="B698"/>
-      <x:c r="C698"/>
-      <x:c r="D698"/>
-      <x:c r="E698"/>
-      <x:c r="F698"/>
-      <x:c r="G698"/>
-      <x:c r="H698"/>
-      <x:c r="I698"/>
-      <x:c r="J698"/>
-      <x:c r="K698"/>
+      <x:c r="A698" t="str">
+        <x:v>donggeurio20260830_line_0006</x:v>
+      </x:c>
+      <x:c r="B698" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C698" t="n">
+        <x:v>914</x:v>
+      </x:c>
+      <x:c r="D698" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E698" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F698" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G698" t="str">
+        <x:v>- S05 7000-8333ms ACTION_HIGHLIGHT: 포크/나이프로 음식을 자르거나 분리하는 핵심 순간을 타이트한 클로즈업으로 강조</x:v>
+      </x:c>
+      <x:c r="H698" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I698" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J698" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K698" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="699" ht="18" customHeight="1">
-      <x:c r="A699"/>
-      <x:c r="B699"/>
-      <x:c r="C699"/>
-      <x:c r="D699"/>
-      <x:c r="E699"/>
-      <x:c r="F699"/>
-      <x:c r="G699"/>
-      <x:c r="H699"/>
-      <x:c r="I699"/>
-      <x:c r="J699"/>
-      <x:c r="K699"/>
+      <x:c r="A699" t="str">
+        <x:v>donggeurio20260830_line_0007</x:v>
+      </x:c>
+      <x:c r="B699" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C699" t="n">
+        <x:v>915</x:v>
+      </x:c>
+      <x:c r="D699" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E699" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F699" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G699" t="str">
+        <x:v>- S06 8333-9633ms LOCATION: 매장 외관·간판·입구 등 장소를 식별할 수 있는 구도를 짧게 제시하고 지원될 때만 미세 줌</x:v>
+      </x:c>
+      <x:c r="H699" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I699" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J699" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K699" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="700" ht="18" customHeight="1">
-      <x:c r="A700"/>
-      <x:c r="B700"/>
-      <x:c r="C700"/>
-      <x:c r="D700"/>
-      <x:c r="E700"/>
-      <x:c r="F700"/>
-      <x:c r="G700"/>
-      <x:c r="H700"/>
-      <x:c r="I700"/>
-      <x:c r="J700"/>
-      <x:c r="K700"/>
+      <x:c r="A700" t="str">
+        <x:v>donggeurio20260830_line_0008</x:v>
+      </x:c>
+      <x:c r="B700" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C700" t="n">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="D700" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E700" t="str">
+        <x:v>SHOT</x:v>
+      </x:c>
+      <x:c r="F700" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G700" t="str">
+        <x:v>- S07 9633-12067ms OUTRO: 비비기·들어올리기·떠먹기 등 최종 음식 클로즈업에 1.05→1.00 ease-out 줌아웃</x:v>
+      </x:c>
+      <x:c r="H700" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I700" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J700" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K700" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="701" ht="18" customHeight="1">
-      <x:c r="A701"/>
-      <x:c r="B701"/>
-      <x:c r="C701"/>
-      <x:c r="D701"/>
-      <x:c r="E701"/>
-      <x:c r="F701"/>
-      <x:c r="G701"/>
-      <x:c r="H701"/>
-      <x:c r="I701"/>
-      <x:c r="J701"/>
-      <x:c r="K701"/>
+      <x:c r="A701" t="str">
+        <x:v>donggeurio20260830_line_0009</x:v>
+      </x:c>
+      <x:c r="B701" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C701" t="n">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="D701" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E701" t="str">
+        <x:v>TIMELINE</x:v>
+      </x:c>
+      <x:c r="F701" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G701" t="str">
+        <x:v>- measured_boundaries_ms: 0,1033,3767,4700,7000,8333,9633,12067. 실행 시간축은 MP4 실측 경계를, 의미 라벨은 분석 JSON을 우선.</x:v>
+      </x:c>
+      <x:c r="H701" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I701" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J701" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K701" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="702" ht="18" customHeight="1">
-      <x:c r="A702"/>
-      <x:c r="B702"/>
-      <x:c r="C702"/>
-      <x:c r="D702"/>
-      <x:c r="E702"/>
-      <x:c r="F702"/>
-      <x:c r="G702"/>
-      <x:c r="H702"/>
-      <x:c r="I702"/>
-      <x:c r="J702"/>
-      <x:c r="K702"/>
+      <x:c r="A702" t="str">
+        <x:v>donggeurio20260830_line_0010</x:v>
+      </x:c>
+      <x:c r="B702" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C702" t="n">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="D702" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E702" t="str">
+        <x:v>COLOR</x:v>
+      </x:c>
+      <x:c r="F702" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G702" t="str">
+        <x:v>- WARM tone; contrast/saturation +10~15%. 정확한 temperature 값은 COLOR.WARM_VLOG.TEMPERATURE 정책에서 해결.</x:v>
+      </x:c>
+      <x:c r="H702" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I702" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J702" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K702" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="703" ht="18" customHeight="1">
-      <x:c r="A703"/>
-      <x:c r="B703"/>
-      <x:c r="C703"/>
-      <x:c r="D703"/>
-      <x:c r="E703"/>
-      <x:c r="F703"/>
-      <x:c r="G703"/>
-      <x:c r="H703"/>
-      <x:c r="I703"/>
-      <x:c r="J703"/>
-      <x:c r="K703"/>
+      <x:c r="A703" t="str">
+        <x:v>donggeurio20260830_line_0011</x:v>
+      </x:c>
+      <x:c r="B703" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C703" t="n">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="D703" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E703" t="str">
+        <x:v>OVERLAY</x:v>
+      </x:c>
+      <x:c r="F703" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G703" t="str">
+        <x:v>- S01 중앙 타이틀, S02 하단 보조 텍스트. 레퍼런스 상호·핸들은 복제하지 않고 사용자 프로젝트 메타데이터로 교체.</x:v>
+      </x:c>
+      <x:c r="H703" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I703" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J703" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K703" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="704" ht="18" customHeight="1">
-      <x:c r="A704"/>
-      <x:c r="B704"/>
-      <x:c r="C704"/>
-      <x:c r="D704"/>
-      <x:c r="E704"/>
-      <x:c r="F704"/>
-      <x:c r="G704"/>
-      <x:c r="H704"/>
-      <x:c r="I704"/>
-      <x:c r="J704"/>
-      <x:c r="K704"/>
+      <x:c r="A704" t="str">
+        <x:v>donggeurio20260830_line_0012</x:v>
+      </x:c>
+      <x:c r="B704" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C704" t="n">
+        <x:v>920</x:v>
+      </x:c>
+      <x:c r="D704" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E704" t="str">
+        <x:v>AUDIO_SYNC</x:v>
+      </x:c>
+      <x:c r="F704" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G704" t="str">
+        <x:v>- BEAT_SYNC_MUSIC; 의미 앵커를 훼손하지 않는 범위에서 인접 강한 onset에 컷을 스냅. 플랫폼 음원은 사용자가 추가.</x:v>
+      </x:c>
+      <x:c r="H704" t="str">
+        <x:v>동그리오_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I704" t="str">
+        <x:v>F8C3D8926CE141C84DF9C8077E82B5ABB6A90162A4E8BAF689277EDA85400A71</x:v>
+      </x:c>
+      <x:c r="J704" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K704" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="705" ht="18" customHeight="1">
-      <x:c r="A705"/>
-      <x:c r="B705"/>
-      <x:c r="C705"/>
-      <x:c r="D705"/>
-      <x:c r="E705"/>
-      <x:c r="F705"/>
-      <x:c r="G705"/>
-      <x:c r="H705"/>
-      <x:c r="I705"/>
-      <x:c r="J705"/>
-      <x:c r="K705"/>
+      <x:c r="A705" t="str">
+        <x:v>donggeurio20260830_line_0013</x:v>
+      </x:c>
+      <x:c r="B705" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C705" t="n">
+        <x:v>921</x:v>
+      </x:c>
+      <x:c r="D705" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E705" t="str">
+        <x:v>PARAMETER_POLICY</x:v>
+      </x:c>
+      <x:c r="F705" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G705" t="str">
+        <x:v>- 미해결 키: COLOR.WARM_VLOG.TEMPERATURE, CAMERA.SLIGHT_ZOOM.DEFAULT, TRANSITION.FADE_OUT.DEFAULT_DURATION_MS.</x:v>
+      </x:c>
+      <x:c r="H705" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I705" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J705" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K705" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="706" ht="18" customHeight="1">
-      <x:c r="A706"/>
-      <x:c r="B706"/>
-      <x:c r="C706"/>
-      <x:c r="D706"/>
-      <x:c r="E706"/>
-      <x:c r="F706"/>
-      <x:c r="G706"/>
-      <x:c r="H706"/>
-      <x:c r="I706"/>
-      <x:c r="J706"/>
-      <x:c r="K706"/>
+      <x:c r="A706" t="str">
+        <x:v>donggeurio20260830_line_0014</x:v>
+      </x:c>
+      <x:c r="B706" t="str">
+        <x:v>uploaded_donggeurio_json_20260830</x:v>
+      </x:c>
+      <x:c r="C706" t="n">
+        <x:v>922</x:v>
+      </x:c>
+      <x:c r="D706" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="E706" t="str">
+        <x:v>VALIDATION</x:v>
+      </x:c>
+      <x:c r="F706" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G706" t="str">
+        <x:v>- 7개 슬롯, 컷 경계 단조 증가, 전체 12067±34ms, 액션 앵커 보존, 속도 범위 준수, 레퍼런스 브랜드 미복제.</x:v>
+      </x:c>
+      <x:c r="H706" t="str">
+        <x:v>동그리오_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I706" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+      <x:c r="J706" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K706" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="707" ht="18" customHeight="1">
       <x:c r="A707"/>
@@ -26824,7 +28584,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>실제 등록된 가이드 3종과 이후 누적되는 사용자 영상 레코드를 집계합니다.</x:v>
+        <x:v>실제 등록된 가이드 3종과 이후 누적되는 사용자 영상 레코드를 집계합니다. 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -26855,10 +28615,10 @@
         <x:v>챌린지 입력</x:v>
       </x:c>
       <x:c r="B5" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
-        <x:v>랭킹 1위와 3위만 유지하며 2위는 공란</x:v>
+        <x:v>주술회전 1위·동그리오 2위·오츠카레 썸머 3위</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>02_INPUT_GUIDES</x:v>
@@ -26869,10 +28629,10 @@
         <x:v>가이드 템플릿 구간</x:v>
       </x:c>
       <x:c r="B6" s="26" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="18" t="str">
-        <x:v>Gemini가 생성한 가이드 구간 수</x:v>
+        <x:v>신규 주술회전 8컷 + 동그리오 7컷 + 기존 오츠카레 5구간</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
         <x:v>03_GUIDE_TEMPLATES</x:v>
@@ -27001,7 +28761,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>실제 업로드 MP4를 기준으로 주술회전·오츠카레 썸머를 재분석했습니다. 사용자 지정 순위는 주술회전 1위·카페 추천 리뷰 2위·오츠카레 썸머 3위이며, 기존 YouTube 가이드 링크를 연결했습니다.</x:v>
+        <x:v>주술회전·동그리오·오츠카레 썸머의 승인된 가이드와 순위 1·2·3을 유지하며 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -27054,10 +28814,10 @@
     </x:row>
     <x:row r="5" ht="38" customHeight="1">
       <x:c r="A5" s="47" t="str">
-        <x:v>uploaded_guide_videos_20260824</x:v>
+        <x:v>uploaded_analysis_json_20260830</x:v>
       </x:c>
       <x:c r="B5" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="C5" s="47" t="str">
         <x:v>jujutsu_transition</x:v>
@@ -27072,10 +28832,10 @@
         <x:v>주술회전 트랜지션</x:v>
       </x:c>
       <x:c r="G5" s="47" t="str">
-        <x:v>https://www.youtube.com/shorts/Yc7ZjC0n7oY?si=p0vD4OMH9It_RBk_</x:v>
+        <x:v>https://www.youtube.com/shorts/Aa-CGr9-c8E</x:v>
       </x:c>
       <x:c r="H5" s="47" t="str">
-        <x:v>Yc7ZjC0n7oY</x:v>
+        <x:v>Aa-CGr9-c8E</x:v>
       </x:c>
       <x:c r="I5" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27083,43 +28843,61 @@
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
       <x:c r="A6" s="47" t="str">
-        <x:v>uploaded_guide_videos_20260824</x:v>
+        <x:v>uploaded_analysis_json_20260830</x:v>
       </x:c>
       <x:c r="B6" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="C6" s="47" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>donggeurio_challenge</x:v>
       </x:c>
       <x:c r="D6" s="47" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E6" s="47" t="str">
-        <x:v>오츠카레 썸머 챌린지</x:v>
+        <x:v>동그리오 챌린지</x:v>
       </x:c>
       <x:c r="F6" s="47" t="str">
-        <x:v>오츠카레 썸머 챌린지</x:v>
+        <x:v>동그리오 챌린지</x:v>
       </x:c>
       <x:c r="G6" s="47" t="str">
-        <x:v>https://www.youtube.com/shorts/e-dU9yQfmik?si=fGCn4wuBsTEm2Q-p</x:v>
+        <x:v>https://www.youtube.com/shorts/iWyRoIJheV4</x:v>
       </x:c>
       <x:c r="H6" s="47" t="str">
-        <x:v>e-dU9yQfmik</x:v>
+        <x:v>iWyRoIJheV4</x:v>
       </x:c>
       <x:c r="I6" s="47" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
-      <x:c r="A7"/>
-      <x:c r="B7"/>
-      <x:c r="C7"/>
-      <x:c r="D7"/>
-      <x:c r="E7"/>
-      <x:c r="F7"/>
-      <x:c r="G7"/>
-      <x:c r="H7"/>
-      <x:c r="I7"/>
+      <x:c r="A7" t="str">
+        <x:v>uploaded_guide_videos_20260824</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>오츠카레 썸머 챌린지</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>오츠카레 썸머 챌린지</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>https://www.youtube.com/shorts/e-dU9yQfmik?si=fGCn4wuBsTEm2Q-p</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>e-dU9yQfmik</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -27166,7 +28944,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="53" t="str">
-        <x:v>실제 편집 가이드 3종 · 실행용 구간 규칙</x:v>
+        <x:v>실제 편집 가이드 3종 · 실행용 구간 규칙 v5.4</x:v>
       </x:c>
       <x:c r="B1" s="53"/>
       <x:c r="C1" s="53"/>
@@ -27193,7 +28971,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="56" t="str">
-        <x:v>업로드된 두 MP4의 실제 타임라인을 기준으로 장면 구간·얼굴 노출·숏폼 유형·촬영 난이도·개인화 범위를 v2 세그먼트에 반영했습니다. 예상 제작시간은 5·10·30·60분 분류를 사용합니다.</x:v>
+        <x:v>업로드 JSON의 주술회전 8컷·동그리오 7컷과 기존 오츠카레 실행 구간을 같은 A:W 스키마로 보존합니다. 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -27316,16 +29094,16 @@
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="47" t="str">
-        <x:v>gts_jujutsu_01</x:v>
+        <x:v>gts_jujutsu_v5_01</x:v>
       </x:c>
       <x:c r="B5" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v2</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C5" s="47" t="str">
         <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D5" s="49" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="49" t="n">
         <x:v>1</x:v>
@@ -27334,37 +29112,35 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="67" t="n">
-        <x:v>3433</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="H5" s="47" t="str">
-        <x:v>첫 번째 손짓 변환 · 디저트와 음료 등장</x:v>
+        <x:v>인물 A 빈손 포즈 훅</x:v>
       </x:c>
       <x:c r="I5" s="47" t="str">
-        <x:v>TRANSFORM_DEMO_A</x:v>
+        <x:v>HOOK_SETUP</x:v>
       </x:c>
       <x:c r="J5" s="47" t="str">
-        <x:v>노란 상의 인물이 빈 테이블 앞에서 손가락·손짓을 만들고 모션 피크 직후 실제 디저트와 음료 2잔을 공개한 뒤 결과를 유지</x:v>
+        <x:v>인물 A가 고정 미디엄 구도에서 빈손 시그니처 포즈에 진입해 안정적으로 유지</x:v>
       </x:c>
       <x:c r="K5" s="47" t="str">
-        <x:v>SETUP 0–967ms → REVEAL 967–3433ms; 손동작 피크와 상품 등장 프레임을 ±1프레임 안에 정렬; hard cut only</x:v>
-      </x:c>
-      <x:c r="L5" s="47" t="str">
-        <x:v>{{caption.hook}}</x:v>
-      </x:c>
+        <x:v>POSE_HOLD_END_ANCHORED; S02와 신체·손·배경 특징점을 정렬하고 1500ms SFX 직전에 종료</x:v>
+      </x:c>
+      <x:c r="L5" s="47"/>
       <x:c r="M5" s="47" t="str">
-        <x:v>caption.hook,promo.primary,store.owner_face_allowed</x:v>
+        <x:v>promo.primary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N5" s="47" t="str">
-        <x:v>실제 촬영된 대표 메뉴만 치환하고 출연자가 매장 관계자인 경우 얼굴 촬영 허용 여부를 확인</x:v>
+        <x:v>첫 공개 아이템은 실제 대표 메뉴/상품으로 정하고 동일 인물·구도·배경의 S02와 한 쌍으로 촬영</x:v>
       </x:c>
       <x:c r="O5" s="47" t="str">
-        <x:v>caption,text_2d,image_2d,sfx</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P5" s="49" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="Q5" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R5" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27373,69 +29149,67 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T5" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$810:$G$827</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U5" s="47" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V5" s="47" t="str">
-        <x:v>플랫폼 UI·애니메이션 상단 영상/자막·원본 BGM은 복제하지 않음. 권리 확인된 전면 2D 자산과 SFX만 허용.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W5" s="47" t="str">
-        <x:v>61AAC25E38688E48000B399277828732BC201C1806FEFAA23419C76662B1B0E7</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="47" t="str">
-        <x:v>gts_jujutsu_02</x:v>
+        <x:v>gts_jujutsu_v5_02</x:v>
       </x:c>
       <x:c r="B6" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v2</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C6" s="47" t="str">
         <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D6" s="49" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="67" t="n">
-        <x:v>3433</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G6" s="67" t="n">
-        <x:v>5800</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="H6" s="47" t="str">
-        <x:v>두 번째 팔 스윕 변환 · 붉은 음료 공개</x:v>
+        <x:v>인물 A 첫 아이템 공개</x:v>
       </x:c>
       <x:c r="I6" s="47" t="str">
-        <x:v>TRANSFORM_DEMO_B</x:v>
+        <x:v>MAGIC_REVEAL</x:v>
       </x:c>
       <x:c r="J6" s="47" t="str">
-        <x:v>흰 상의 인물이 팔로 화면을 가로질러 스윕하고 같은 자리에서 실제 보조 메뉴가 등장한 뒤 짧게 가까워지는 구도를 유지</x:v>
+        <x:v>S01과 동일 포즈·구도에서 인물 A의 손에 실제 음료가 나타난 상태로 시작해 결과를 유지</x:v>
       </x:c>
       <x:c r="K6" s="47" t="str">
-        <x:v>SETUP 3433–4400ms → REVEAL 4400–5100ms → PUNCH_IN_REFERENCE 5100–5800ms; 상품 등장 ±1프레임</x:v>
-      </x:c>
-      <x:c r="L6" s="47" t="str">
-        <x:v>{{promo.secondary.name}}</x:v>
-      </x:c>
+        <x:v>1500ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 디졸브·페이드 금지</x:v>
+      </x:c>
+      <x:c r="L6" s="47"/>
       <x:c r="M6" s="47" t="str">
-        <x:v>promo.secondary.name,store.owner_face_allowed</x:v>
+        <x:v>promo.primary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N6" s="47" t="str">
-        <x:v>보조 메뉴명은 실제 촬영·검증된 대상만 사용하고 얼굴·손을 자막으로 가리지 않음</x:v>
+        <x:v>S01 마지막 프레임과 가장 일치하는 ITEM_PRESENT 프레임을 선택하고 실제 음료/상품만 노출</x:v>
       </x:c>
       <x:c r="O6" s="47" t="str">
-        <x:v>caption,text_2d,image_2d,sfx</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P6" s="49" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="Q6" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R6" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27444,69 +29218,67 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T6" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$810:$G$827</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U6" s="47" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V6" s="47" t="str">
-        <x:v>가이드의 펀치인 구도는 촬영 또는 실제 컷 크롭으로만 참고하고 미지원 효과는 생성하지 않음.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W6" s="47" t="str">
-        <x:v>61AAC25E38688E48000B399277828732BC201C1806FEFAA23419C76662B1B0E7</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="47" t="str">
-        <x:v>gts_jujutsu_03</x:v>
+        <x:v>gts_jujutsu_v5_03</x:v>
       </x:c>
       <x:c r="B7" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v2</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C7" s="47" t="str">
         <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D7" s="49" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E7" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F7" s="67" t="n">
-        <x:v>5800</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G7" s="67" t="n">
-        <x:v>9300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="H7" s="47" t="str">
-        <x:v>세 번째 양손 변환 · 피자 공개</x:v>
+        <x:v>인물 B 빈손 포즈 셋업</x:v>
       </x:c>
       <x:c r="I7" s="47" t="str">
-        <x:v>TRANSFORM_DEMO_C</x:v>
+        <x:v>SETUP</x:v>
       </x:c>
       <x:c r="J7" s="47" t="str">
-        <x:v>양손을 모았다가 테이블 쪽으로 여는 동작을 유지하고 손이 열리는 순간 실제 세 번째 메뉴가 나타난 뒤 결과를 충분히 보여줌</x:v>
+        <x:v>인물 B가 같은 고정 카메라에서 새로운 빈손 포즈를 취하고 안정 구간을 유지</x:v>
       </x:c>
       <x:c r="K7" s="47" t="str">
-        <x:v>SETUP 5800–7700ms → REVEAL/HOLD 7700–9300ms; 손 열림과 상품 등장 ±1프레임; speed=1.0</x:v>
-      </x:c>
-      <x:c r="L7" s="47" t="str">
-        <x:v>{{promo.tertiary.name}}</x:v>
-      </x:c>
+        <x:v>POSE_HOLD_END_ANCHORED; S04와 포즈·배경을 정렬하고 5000ms SFX 직전에 종료</x:v>
+      </x:c>
+      <x:c r="L7" s="47"/>
       <x:c r="M7" s="47" t="str">
-        <x:v>promo.tertiary.name,store.owner_face_allowed</x:v>
+        <x:v>promo.secondary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N7" s="47" t="str">
-        <x:v>세 번째 메뉴가 없으면 대표 또는 보조 메뉴의 다른 실제 구도로 대체하되 변환 시범 세 개와 순서는 유지</x:v>
+        <x:v>두 번째 출연자와 보조 메뉴를 사용하되 S04와 동일 인물·의상·배경 유지</x:v>
       </x:c>
       <x:c r="O7" s="47" t="str">
-        <x:v>caption,text_2d,image_2d,sfx</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P7" s="49" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="Q7" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R7" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27515,134 +29287,136 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T7" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$810:$G$827</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U7" s="47" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V7" s="47" t="str">
-        <x:v>실제 영상에 없는 상품을 생성하지 않고 촬영된 메뉴 또는 권리 확인된 전면 2D 자산만 사용.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W7" s="47" t="str">
-        <x:v>61AAC25E38688E48000B399277828732BC201C1806FEFAA23419C76662B1B0E7</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="47" t="str">
-        <x:v>gts_jujutsu_04</x:v>
+        <x:v>gts_jujutsu_v5_04</x:v>
       </x:c>
       <x:c r="B8" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v2</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C8" s="47" t="str">
         <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D8" s="49" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E8" s="49" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="67" t="n">
-        <x:v>9300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G8" s="67" t="n">
-        <x:v>10067</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="H8" s="47" t="str">
-        <x:v>첫 장면 재등장 · 플랫폼 루프 리셋 참고</x:v>
+        <x:v>인물 B 두 번째 아이템 공개</x:v>
       </x:c>
       <x:c r="I8" s="47" t="str">
-        <x:v>LOOP_RESET_REFERENCE</x:v>
+        <x:v>MAGIC_REVEAL</x:v>
       </x:c>
       <x:c r="J8" s="47" t="str">
-        <x:v>가이드 파일에서 첫 번째 노란 상의 장면이 재등장하지만 플랫폼 반복을 위한 리셋이므로 새 콘텐츠 장면으로 생성하지 않음</x:v>
+        <x:v>S03과 동일 포즈·구도에서 인물 B의 손에 다른 음료가 나타난 상태로 전환</x:v>
       </x:c>
       <x:c r="K8" s="47" t="str">
-        <x:v>관찰 범위 9300–10067ms; 제작본은 세 번째 결과 홀드에서 종료하고 필요하면 첫 프레임과 자연스럽게 이어지는지 검사</x:v>
+        <x:v>5000ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 7000ms HARD_CUT</x:v>
       </x:c>
       <x:c r="L8" s="47"/>
-      <x:c r="M8" s="47"/>
+      <x:c r="M8" s="47" t="str">
+        <x:v>promo.secondary,store.owner_face_allowed</x:v>
+      </x:c>
       <x:c r="N8" s="47" t="str">
-        <x:v>루프 리셋 구간은 사용자 개인화 대상이 아니며 중복 장면을 추가하지 않음</x:v>
-      </x:c>
-      <x:c r="O8" s="47"/>
+        <x:v>S03 마지막 프레임과 가장 일치하는 ITEM_PRESENT 프레임을 시작점으로 선택</x:v>
+      </x:c>
+      <x:c r="O8" s="47" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
       <x:c r="P8" s="49" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="Q8" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R8" s="47" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S8" s="47" t="str">
-        <x:v>REFERENCE_ONLY</x:v>
+        <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T8" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$810:$G$827</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U8" s="47" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V8" s="47" t="str">
-        <x:v>화면 녹화 UI와 플랫폼 반복 구간을 실행 레시피에 복제하지 않음.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W8" s="47" t="str">
-        <x:v>61AAC25E38688E48000B399277828732BC201C1806FEFAA23419C76662B1B0E7</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="47" t="str">
-        <x:v>gts_otsukare_01</x:v>
+        <x:v>gts_jujutsu_v5_05</x:v>
       </x:c>
       <x:c r="B9" s="47" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C9" s="47" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D9" s="47" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E9" s="47" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F9" s="47" t="n">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G9" s="47" t="n">
-        <x:v>467</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="H9" s="47" t="str">
-        <x:v>오버헤드 V 포즈 훅</x:v>
+        <x:v>인물 A 새 빈손 포즈 셋업</x:v>
       </x:c>
       <x:c r="I9" s="47" t="str">
-        <x:v>DANCE_OVERHEAD_HOOK</x:v>
+        <x:v>SETUP</x:v>
       </x:c>
       <x:c r="J9" s="47" t="str">
-        <x:v>한 명의 출연자가 오버헤드 근접 구도에서 V 포즈와 표정으로 시작하고 즉시 메인 안무로 연결</x:v>
+        <x:v>인물 A가 다시 등장해 제품 공개 전 새 빈손 포즈를 안정적으로 유지</x:v>
       </x:c>
       <x:c r="K9" s="47" t="str">
-        <x:v>0–467ms; speed=1.0; 다음 와이드 구간으로 동작이 끊기지 않게 연결</x:v>
-      </x:c>
-      <x:c r="L9" s="47" t="str">
-        <x:v>{{caption.hook}}</x:v>
-      </x:c>
+        <x:v>POSE_HOLD_END_ANCHORED; S06과 정렬하고 8500ms SFX 직전에 종료</x:v>
+      </x:c>
+      <x:c r="L9" s="47"/>
       <x:c r="M9" s="47" t="str">
-        <x:v>caption.hook,store.owner_face_allowed</x:v>
+        <x:v>promo.tertiary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N9" s="47" t="str">
-        <x:v>출연자는 촬영 동의된 매장 관계자만 사용하고 훅 자막은 얼굴·손을 가리지 않는 세이프존에 1줄로 표시</x:v>
+        <x:v>세 번째 실제 메뉴의 형태를 고려해 손과 테이블이 가리지 않는 포즈 선택</x:v>
       </x:c>
       <x:c r="O9" s="47" t="str">
-        <x:v>caption,text_2d</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P9" s="47" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q9" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R9" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27651,65 +29425,67 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T9" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U9" s="47" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V9" s="47" t="str">
-        <x:v>원본 BGM은 합성하지 않고 플랫폼 UI를 복제하지 않음. 안무와 얼굴 가시성을 우선.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W9" s="47" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="47" t="str">
-        <x:v>gts_otsukare_02</x:v>
+        <x:v>gts_jujutsu_v5_06</x:v>
       </x:c>
       <x:c r="B10" s="47" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C10" s="47" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D10" s="47" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E10" s="47" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F10" s="47" t="n">
-        <x:v>467</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G10" s="47" t="n">
-        <x:v>3933</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="H10" s="47" t="str">
-        <x:v>와이드 안무 A → 오버헤드 포인트</x:v>
+        <x:v>인물 A 제품 공개</x:v>
       </x:c>
       <x:c r="I10" s="47" t="str">
-        <x:v>DANCE_PHRASE_A</x:v>
+        <x:v>MAGIC_REVEAL</x:v>
       </x:c>
       <x:c r="J10" s="47" t="str">
-        <x:v>전신이 보이는 와이드 안무를 연속 수행한 뒤 같은 동작 흐름에서 카메라가 위쪽 가까운 포인트로 이동</x:v>
+        <x:v>S05와 동일 포즈·구도에서 인물 A가 실제 제품을 든 상태로 시작</x:v>
       </x:c>
       <x:c r="K10" s="47" t="str">
-        <x:v>WIDE 467–3300ms → OVERHEAD 3300–3933ms; speed=1.0; 중간 홍보 컷 삽입 금지</x:v>
+        <x:v>8500ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 아이템 전체가 보이는 결과 홀드</x:v>
       </x:c>
       <x:c r="L10" s="47"/>
       <x:c r="M10" s="47" t="str">
-        <x:v>store.owner_face_allowed</x:v>
+        <x:v>promo.tertiary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N10" s="47" t="str">
-        <x:v>실제 촬영 장소와 동의된 출연자로 개인화하되 안무 프레이즈와 카메라 전환 순서를 유지</x:v>
-      </x:c>
-      <x:c r="O10" s="47"/>
+        <x:v>실제 촬영된 제품/대표 상품으로 치환하고 S05 경계의 포즈 일치 우선</x:v>
+      </x:c>
+      <x:c r="O10" s="47" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
       <x:c r="P10" s="47" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q10" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R10" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27718,65 +29494,67 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T10" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U10" s="47" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V10" s="47" t="str">
-        <x:v>가이드에 없는 메뉴 B-roll·생성 장면을 중간에 넣지 않음.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W10" s="47" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="47" t="str">
-        <x:v>gts_otsukare_03</x:v>
+        <x:v>gts_jujutsu_v5_07</x:v>
       </x:c>
       <x:c r="B11" s="47" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C11" s="47" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D11" s="47" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="47" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F11" s="47" t="n">
-        <x:v>3933</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G11" s="47" t="n">
-        <x:v>7400</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="H11" s="47" t="str">
-        <x:v>와이드 안무 B → 오버헤드 포인트</x:v>
+        <x:v>인물 B 마지막 빈손 포즈 셋업</x:v>
       </x:c>
       <x:c r="I11" s="47" t="str">
-        <x:v>DANCE_PHRASE_B</x:v>
+        <x:v>SETUP</x:v>
       </x:c>
       <x:c r="J11" s="47" t="str">
-        <x:v>전신 와이드 안무를 이어가며 팔과 상체 제스처를 보여준 뒤 두 번째 오버헤드 포인트로 연결</x:v>
+        <x:v>인물 B가 마지막 공개를 위한 빈손 포즈를 취하고 배경·카메라를 고정</x:v>
       </x:c>
       <x:c r="K11" s="47" t="str">
-        <x:v>WIDE 3933–6733ms → OVERHEAD 6733–7400ms; speed=1.0; 앞뒤 동작 연속성 유지</x:v>
+        <x:v>POSE_HOLD_END_ANCHORED; S08과 정렬하고 12000ms SFX 직전에 종료</x:v>
       </x:c>
       <x:c r="L11" s="47"/>
       <x:c r="M11" s="47" t="str">
-        <x:v>store.owner_face_allowed</x:v>
+        <x:v>promo.quaternary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N11" s="47" t="str">
-        <x:v>의상·배경은 실제 촬영 맥락에 맞출 수 있으나 얼굴·손·몸동작을 이미지나 긴 자막으로 가리지 않음</x:v>
-      </x:c>
-      <x:c r="O11" s="47"/>
+        <x:v>네 번째 실제 메뉴를 놓을 위치를 비워 두고 S08과 동일 인물·구도 유지</x:v>
+      </x:c>
+      <x:c r="O11" s="47" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
       <x:c r="P11" s="47" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q11" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R11" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27785,65 +29563,67 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T11" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U11" s="47" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V11" s="47" t="str">
-        <x:v>춤 프레임을 메뉴 이미지로 교체하지 않으며 실제 안무 수행 영상을 유지.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W11" s="47" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
       <x:c r="A12" s="47" t="str">
-        <x:v>gts_otsukare_04</x:v>
+        <x:v>gts_jujutsu_v5_08</x:v>
       </x:c>
       <x:c r="B12" s="47" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C12" s="47" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D12" s="47" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="47" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F12" s="47" t="n">
-        <x:v>7400</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G12" s="47" t="n">
-        <x:v>10900</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="H12" s="47" t="str">
-        <x:v>와이드 안무 C → 마지막 오버헤드 전환</x:v>
+        <x:v>인물 B 제품 최종 공개</x:v>
       </x:c>
       <x:c r="I12" s="47" t="str">
-        <x:v>DANCE_PHRASE_C</x:v>
+        <x:v>MAGIC_REVEAL</x:v>
       </x:c>
       <x:c r="J12" s="47" t="str">
-        <x:v>세 번째 와이드 안무 프레이즈를 이어가고 카메라가 위쪽으로 이동하면서 마지막 포즈를 준비</x:v>
+        <x:v>S07과 동일 포즈·구도에서 실제 제품이 나타난 상태로 전환해 아웃트로 유지</x:v>
       </x:c>
       <x:c r="K12" s="47" t="str">
-        <x:v>WIDE 7400–10200ms → OVERHEAD 10200–10900ms; speed=1.0; 흐름 삭제·재배열 금지</x:v>
+        <x:v>12000ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 14000ms까지 결과 홀드</x:v>
       </x:c>
       <x:c r="L12" s="47"/>
       <x:c r="M12" s="47" t="str">
-        <x:v>store.owner_face_allowed</x:v>
+        <x:v>promo.quaternary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N12" s="47" t="str">
-        <x:v>매장 홍보는 촬영 배경과 출연 맥락으로 자연스럽게 드러내고 별도 홍보 컷을 삽입하지 않음</x:v>
-      </x:c>
-      <x:c r="O12" s="47"/>
+        <x:v>실제 촬영된 제품/상품을 명확히 보여주고 추가 전환 없이 종료</x:v>
+      </x:c>
+      <x:c r="O12" s="47" t="str">
+        <x:v>sfx</x:v>
+      </x:c>
       <x:c r="P12" s="47" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q12" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R12" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27852,69 +29632,69 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T12" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U12" s="47" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V12" s="47" t="str">
-        <x:v>미지원 피사체 추적·배경 합성 없이 실제 촬영 카메라 동선과 컷 연결만 사용.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W12" s="47" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" s="47" t="str">
-        <x:v>gts_otsukare_05</x:v>
+        <x:v>gts_donggeurio_v1_01</x:v>
       </x:c>
       <x:c r="B13" s="47" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_donggeurio_challenge_v1</x:v>
       </x:c>
       <x:c r="C13" s="47" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>donggeurio_challenge</x:v>
       </x:c>
       <x:c r="D13" s="47" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="47" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="47" t="n">
-        <x:v>10900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="47" t="n">
-        <x:v>11500</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="H13" s="47" t="str">
-        <x:v>오버헤드 근접 마지막 포즈</x:v>
+        <x:v>감성 타이틀 훅</x:v>
       </x:c>
       <x:c r="I13" s="47" t="str">
-        <x:v>DANCE_FINAL_POSE</x:v>
+        <x:v>HOOK</x:v>
       </x:c>
       <x:c r="J13" s="47" t="str">
-        <x:v>얼굴과 손동작이 가까워지는 오버헤드 포즈로 안무를 닫고 짧은 CTA를 안전 영역에 표시</x:v>
+        <x:v>안정적인 벽면·공간 디테일을 고정 구도로 보여주고 중앙 프로젝트 타이틀 배치</x:v>
       </x:c>
       <x:c r="K13" s="47" t="str">
-        <x:v>10900–11500ms; speed=1.0; CTA는 마지막 0.6초 안에서 한 줄만 사용</x:v>
+        <x:v>실측 0~1033ms; 안정 구간 중심 trim; speed 0.95~1.05; 1033ms HARD_CUT</x:v>
       </x:c>
       <x:c r="L13" s="47" t="str">
-        <x:v>{{store.name}} · {{caption.cta}}</x:v>
+        <x:v>{{project.title}}</x:v>
       </x:c>
       <x:c r="M13" s="47" t="str">
-        <x:v>store.name,caption.cta,store.owner_face_allowed</x:v>
+        <x:v>project.title,store.name</x:v>
       </x:c>
       <x:c r="N13" s="47" t="str">
-        <x:v>검증된 매장명과 짧은 CTA만 사용하고 얼굴·손을 가리지 않는 하단 세이프존에 배치</x:v>
+        <x:v>레퍼런스 상호·핸들은 복제하지 않고 검증된 프로젝트명/매장명으로 교체</x:v>
       </x:c>
       <x:c r="O13" s="47" t="str">
-        <x:v>caption,text_2d,sfx</x:v>
+        <x:v>caption,text_2d</x:v>
       </x:c>
       <x:c r="P13" s="47" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q13" s="48" t="n">
-        <x:v>46258.916666666664</x:v>
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R13" s="47" t="str">
         <x:v>PASS</x:v>
@@ -27923,167 +29703,776 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T13" s="47" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U13" s="47" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V13" s="47" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W13" s="47" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="62" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>gts_donggeurio_v1_02</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F14" t="n">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="G14" t="n">
+        <x:v>3767</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>메뉴 항공샷 공개</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>REVEAL</x:v>
+      </x:c>
+      <x:c r="J14" t="str">
+        <x:v>메뉴 전체가 보이는 탑다운/하이앵글 샷에 1.00→1.05 선형 줌인과 하단 보조 텍스트 적용</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>실측 1033~3767ms; 구성 최적 구간 trim; speed 0.9~1.1; 3767ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L14" t="str">
+        <x:v>{{store.location_or_context}}</x:v>
+      </x:c>
+      <x:c r="M14" t="str">
+        <x:v>store.location,store.context,promo.primary</x:v>
+      </x:c>
+      <x:c r="N14" t="str">
+        <x:v>실제 메뉴와 검증된 장소/맥락만 사용하고 숫자·혜택을 임의 생성하지 않음</x:v>
+      </x:c>
+      <x:c r="O14" t="str">
+        <x:v>caption,text_2d,transform</x:v>
+      </x:c>
+      <x:c r="P14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q14" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R14" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S14" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T14" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U14" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V14" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W14" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="62" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>gts_donggeurio_v1_03</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F15" t="n">
+        <x:v>3767</x:v>
+      </x:c>
+      <x:c r="G15" t="n">
+        <x:v>4700</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>카페 공간 팬</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>AMBIENCE</x:v>
+      </x:c>
+      <x:c r="J15" t="str">
+        <x:v>조명·좌석·인테리어를 보여주는 가장 매끄러운 우향 팬/측면 이동 구간 선택</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>실측 3767~4700ms; 모션 중심 trim; speed 0.9~1.35; 소스 팬 보존; 4700ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L15"/>
+      <x:c r="M15" t="str">
+        <x:v>store.interior</x:v>
+      </x:c>
+      <x:c r="N15" t="str">
+        <x:v>실제 촬영된 공간 정보량이 높은 구간을 사용하고 긴 팬 전체를 강제 고배속하지 않음</x:v>
+      </x:c>
+      <x:c r="O15" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="P15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q15" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R15" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S15" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T15" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U15" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V15" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W15" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="62" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>gts_donggeurio_v1_04</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F16" t="n">
+        <x:v>4700</x:v>
+      </x:c>
+      <x:c r="G16" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>메뉴 인터랙션 클로즈업</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>ACTION</x:v>
+      </x:c>
+      <x:c r="J16" t="str">
+        <x:v>손이나 도구가 음식에 개입하는 클로즈업에서 동작 시작·피크·종료를 보존</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>실측 4700~7000ms; ACTION_PEAK를 슬롯 58% 부근에 배치; speed 0.9~1.1; 7000ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L16"/>
+      <x:c r="M16" t="str">
+        <x:v>promo.primary.action</x:v>
+      </x:c>
+      <x:c r="N16" t="str">
+        <x:v>실제 촬영된 섞기·집기·서빙 행동을 우선하며 없는 행동을 생성하지 않음</x:v>
+      </x:c>
+      <x:c r="O16" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="P16" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q16" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R16" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S16" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T16" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U16" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V16" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W16" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="62" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>gts_donggeurio_v1_05</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F17" t="n">
+        <x:v>7000</x:v>
+      </x:c>
+      <x:c r="G17" t="n">
+        <x:v>8333</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>음식 자르기 액션 하이라이트</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>ACTION_HIGHLIGHT</x:v>
+      </x:c>
+      <x:c r="J17" t="str">
+        <x:v>포크/나이프로 음식을 자르거나 분리하는 핵심 순간을 타이트한 클로즈업으로 강조</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>실측 7000~8333ms; ACTION_PEAK 중심 trim; speed 0.75~1.0, 0.8 선호; 8333ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L17"/>
+      <x:c r="M17" t="str">
+        <x:v>promo.secondary.action</x:v>
+      </x:c>
+      <x:c r="N17" t="str">
+        <x:v>자르기 장면이 없으면 다른 실제 메뉴 액션으로 대체하고 0.9배 수준까지 완화</x:v>
+      </x:c>
+      <x:c r="O17" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="P17" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q17" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R17" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S17" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T17" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U17" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V17" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W17" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="62" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>gts_donggeurio_v1_06</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F18" t="n">
+        <x:v>8333</x:v>
+      </x:c>
+      <x:c r="G18" t="n">
+        <x:v>9633</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>매장 외관·위치 공개</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>LOCATION</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>매장 외관·간판·입구 등 장소를 식별할 수 있는 구도를 짧게 제시하고 지원될 때만 미세 줌</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>실측 8333~9633ms; 구성 중심 trim; speed 0.9~1.1; 실제 경계는 HARD_CUT 우선</x:v>
+      </x:c>
+      <x:c r="L18"/>
+      <x:c r="M18" t="str">
+        <x:v>store.name,store.location</x:v>
+      </x:c>
+      <x:c r="N18" t="str">
+        <x:v>검증된 매장 외관/위치만 사용하고 SLIDE_LEFT 느낌은 선택적 악센트로만 취급</x:v>
+      </x:c>
+      <x:c r="O18" t="str">
+        <x:v>caption,text_2d,transform</x:v>
+      </x:c>
+      <x:c r="P18" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q18" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R18" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S18" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T18" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U18" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V18" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W18" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>gts_donggeurio_v1_07</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>gt_donggeurio_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>donggeurio_challenge</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F19" t="n">
+        <x:v>9633</x:v>
+      </x:c>
+      <x:c r="G19" t="n">
+        <x:v>12067</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>최종 메뉴 액션 아웃트로</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>OUTRO</x:v>
+      </x:c>
+      <x:c r="J19" t="str">
+        <x:v>비비기·들어올리기·떠먹기 등 최종 음식 클로즈업에 1.05→1.00 ease-out 줌아웃</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>실측 9633~12067ms; ACTION_PEAK를 슬롯 48% 부근에 배치; speed 0.9~1.1; 정책값 해소 시에만 FADE_OUT</x:v>
+      </x:c>
+      <x:c r="L19"/>
+      <x:c r="M19" t="str">
+        <x:v>promo.primary,promo.secondary</x:v>
+      </x:c>
+      <x:c r="N19" t="str">
+        <x:v>가장 강한 실제 메뉴 액션을 사용하고 레퍼런스 브랜딩은 복제하지 않음</x:v>
+      </x:c>
+      <x:c r="O19" t="str">
+        <x:v>transform</x:v>
+      </x:c>
+      <x:c r="P19" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q19" t="n">
+        <x:v>46264.395833333336</x:v>
+      </x:c>
+      <x:c r="R19" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S19" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T19" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+      </x:c>
+      <x:c r="U19" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V19" t="str">
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+      </x:c>
+      <x:c r="W19" t="str">
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>gts_otsukare_01</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>gt_otsukare_summer_v2</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>오버헤드 V 포즈 훅</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>DANCE_OVERHEAD_HOOK</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>한 명의 출연자가 오버헤드 근접 구도에서 V 포즈와 표정으로 시작하고 즉시 메인 안무로 연결</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>0–467ms; speed=1.0; 다음 와이드 구간으로 동작이 끊기지 않게 연결</x:v>
+      </x:c>
+      <x:c r="L20" t="str">
+        <x:v>{{caption.hook}}</x:v>
+      </x:c>
+      <x:c r="M20" t="str">
+        <x:v>caption.hook,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>출연자는 촬영 동의된 매장 관계자만 사용하고 훅 자막은 얼굴·손을 가리지 않는 세이프존에 1줄로 표시</x:v>
+      </x:c>
+      <x:c r="O20" t="str">
+        <x:v>caption,text_2d</x:v>
+      </x:c>
+      <x:c r="P20" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q20" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
+      </x:c>
+      <x:c r="R20" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S20" t="str">
+        <x:v>SUPERSEDED</x:v>
+      </x:c>
+      <x:c r="T20" t="str">
         <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
       </x:c>
-      <x:c r="U13" s="47" t="str">
+      <x:c r="U20" t="str">
         <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
-      <x:c r="V13" s="47" t="str">
+      <x:c r="V20" t="str">
+        <x:v>원본 BGM은 합성하지 않고 플랫폼 UI를 복제하지 않음. 안무와 얼굴 가시성을 우선.</x:v>
+      </x:c>
+      <x:c r="W20" t="str">
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>gts_otsukare_02</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>gt_otsukare_summer_v2</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F21" t="n">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="G21" t="n">
+        <x:v>3933</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>와이드 안무 A → 오버헤드 포인트</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>DANCE_PHRASE_A</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>전신이 보이는 와이드 안무를 연속 수행한 뒤 같은 동작 흐름에서 카메라가 위쪽 가까운 포인트로 이동</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>WIDE 467–3300ms → OVERHEAD 3300–3933ms; speed=1.0; 중간 홍보 컷 삽입 금지</x:v>
+      </x:c>
+      <x:c r="L21"/>
+      <x:c r="M21" t="str">
+        <x:v>store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>실제 촬영 장소와 동의된 출연자로 개인화하되 안무 프레이즈와 카메라 전환 순서를 유지</x:v>
+      </x:c>
+      <x:c r="O21"/>
+      <x:c r="P21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q21" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
+      </x:c>
+      <x:c r="R21" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S21" t="str">
+        <x:v>SUPERSEDED</x:v>
+      </x:c>
+      <x:c r="T21" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+      </x:c>
+      <x:c r="U21" t="str">
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V21" t="str">
+        <x:v>가이드에 없는 메뉴 B-roll·생성 장면을 중간에 넣지 않음.</x:v>
+      </x:c>
+      <x:c r="W21" t="str">
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>gts_otsukare_03</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>gt_otsukare_summer_v2</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
+        <x:v>3933</x:v>
+      </x:c>
+      <x:c r="G22" t="n">
+        <x:v>7400</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>와이드 안무 B → 오버헤드 포인트</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>DANCE_PHRASE_B</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>전신 와이드 안무를 이어가며 팔과 상체 제스처를 보여준 뒤 두 번째 오버헤드 포인트로 연결</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>WIDE 3933–6733ms → OVERHEAD 6733–7400ms; speed=1.0; 앞뒤 동작 연속성 유지</x:v>
+      </x:c>
+      <x:c r="L22"/>
+      <x:c r="M22" t="str">
+        <x:v>store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>의상·배경은 실제 촬영 맥락에 맞출 수 있으나 얼굴·손·몸동작을 이미지나 긴 자막으로 가리지 않음</x:v>
+      </x:c>
+      <x:c r="O22"/>
+      <x:c r="P22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q22" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
+      </x:c>
+      <x:c r="R22" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S22" t="str">
+        <x:v>SUPERSEDED</x:v>
+      </x:c>
+      <x:c r="T22" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+      </x:c>
+      <x:c r="U22" t="str">
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V22" t="str">
+        <x:v>춤 프레임을 메뉴 이미지로 교체하지 않으며 실제 안무 수행 영상을 유지.</x:v>
+      </x:c>
+      <x:c r="W22" t="str">
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>gts_otsukare_04</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>gt_otsukare_summer_v2</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>7400</x:v>
+      </x:c>
+      <x:c r="G23" t="n">
+        <x:v>10900</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>와이드 안무 C → 마지막 오버헤드 전환</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>DANCE_PHRASE_C</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>세 번째 와이드 안무 프레이즈를 이어가고 카메라가 위쪽으로 이동하면서 마지막 포즈를 준비</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>WIDE 7400–10200ms → OVERHEAD 10200–10900ms; speed=1.0; 흐름 삭제·재배열 금지</x:v>
+      </x:c>
+      <x:c r="L23"/>
+      <x:c r="M23" t="str">
+        <x:v>store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N23" t="str">
+        <x:v>매장 홍보는 촬영 배경과 출연 맥락으로 자연스럽게 드러내고 별도 홍보 컷을 삽입하지 않음</x:v>
+      </x:c>
+      <x:c r="O23"/>
+      <x:c r="P23" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q23" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
+      </x:c>
+      <x:c r="R23" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S23" t="str">
+        <x:v>SUPERSEDED</x:v>
+      </x:c>
+      <x:c r="T23" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+      </x:c>
+      <x:c r="U23" t="str">
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V23" t="str">
+        <x:v>미지원 피사체 추적·배경 합성 없이 실제 촬영 카메라 동선과 컷 연결만 사용.</x:v>
+      </x:c>
+      <x:c r="W23" t="str">
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>gts_otsukare_05</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>gt_otsukare_summer_v2</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>otsukare_summer_challenge</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>10900</x:v>
+      </x:c>
+      <x:c r="G24" t="n">
+        <x:v>11500</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>오버헤드 근접 마지막 포즈</x:v>
+      </x:c>
+      <x:c r="I24" t="str">
+        <x:v>DANCE_FINAL_POSE</x:v>
+      </x:c>
+      <x:c r="J24" t="str">
+        <x:v>얼굴과 손동작이 가까워지는 오버헤드 포즈로 안무를 닫고 짧은 CTA를 안전 영역에 표시</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>10900–11500ms; speed=1.0; CTA는 마지막 0.6초 안에서 한 줄만 사용</x:v>
+      </x:c>
+      <x:c r="L24" t="str">
+        <x:v>{{store.name}} · {{caption.cta}}</x:v>
+      </x:c>
+      <x:c r="M24" t="str">
+        <x:v>store.name,caption.cta,store.owner_face_allowed</x:v>
+      </x:c>
+      <x:c r="N24" t="str">
+        <x:v>검증된 매장명과 짧은 CTA만 사용하고 얼굴·손을 가리지 않는 하단 세이프존에 배치</x:v>
+      </x:c>
+      <x:c r="O24" t="str">
+        <x:v>caption,text_2d,sfx</x:v>
+      </x:c>
+      <x:c r="P24" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q24" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
+      </x:c>
+      <x:c r="R24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S24" t="str">
+        <x:v>SUPERSEDED</x:v>
+      </x:c>
+      <x:c r="T24" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+      </x:c>
+      <x:c r="U24" t="str">
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V24" t="str">
         <x:v>사용자는 앱에서 음원을 직접 추가하며 템플릿은 음원 제목·시작 위치만 최종 제공.</x:v>
       </x:c>
-      <x:c r="W13" s="47" t="str">
+      <x:c r="W24" t="str">
         <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="62" customHeight="1">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
-      <x:c r="I14"/>
-      <x:c r="J14"/>
-      <x:c r="K14"/>
-      <x:c r="L14"/>
-      <x:c r="M14"/>
-      <x:c r="N14"/>
-      <x:c r="O14"/>
-      <x:c r="P14"/>
-      <x:c r="Q14"/>
-      <x:c r="R14"/>
-      <x:c r="S14"/>
-      <x:c r="T14"/>
-      <x:c r="U14"/>
-      <x:c r="V14"/>
-      <x:c r="W14"/>
-    </x:row>
-    <x:row r="15" ht="62" customHeight="1">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
-      <x:c r="I15"/>
-      <x:c r="J15"/>
-      <x:c r="K15"/>
-      <x:c r="L15"/>
-      <x:c r="M15"/>
-      <x:c r="N15"/>
-      <x:c r="O15"/>
-      <x:c r="P15"/>
-      <x:c r="Q15"/>
-      <x:c r="R15"/>
-      <x:c r="S15"/>
-      <x:c r="T15"/>
-      <x:c r="U15"/>
-      <x:c r="V15"/>
-      <x:c r="W15"/>
-    </x:row>
-    <x:row r="16" ht="62" customHeight="1">
-      <x:c r="A16"/>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16"/>
-      <x:c r="E16"/>
-      <x:c r="F16"/>
-      <x:c r="G16"/>
-      <x:c r="H16"/>
-      <x:c r="I16"/>
-      <x:c r="J16"/>
-      <x:c r="K16"/>
-      <x:c r="L16"/>
-      <x:c r="M16"/>
-      <x:c r="N16"/>
-      <x:c r="O16"/>
-      <x:c r="P16"/>
-      <x:c r="Q16"/>
-      <x:c r="R16"/>
-      <x:c r="S16"/>
-      <x:c r="T16"/>
-      <x:c r="U16"/>
-      <x:c r="V16"/>
-      <x:c r="W16"/>
-    </x:row>
-    <x:row r="17" ht="62" customHeight="1">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-      <x:c r="I17"/>
-      <x:c r="J17"/>
-      <x:c r="K17"/>
-      <x:c r="L17"/>
-      <x:c r="M17"/>
-      <x:c r="N17"/>
-      <x:c r="O17"/>
-      <x:c r="P17"/>
-      <x:c r="Q17"/>
-      <x:c r="R17"/>
-      <x:c r="S17"/>
-      <x:c r="T17"/>
-      <x:c r="U17"/>
-      <x:c r="V17"/>
-      <x:c r="W17"/>
-    </x:row>
-    <x:row r="18" ht="62" customHeight="1">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
-      <x:c r="I18"/>
-      <x:c r="J18"/>
-      <x:c r="K18"/>
-      <x:c r="L18"/>
-      <x:c r="M18"/>
-      <x:c r="N18"/>
-      <x:c r="O18"/>
-      <x:c r="P18"/>
-      <x:c r="Q18"/>
-      <x:c r="R18"/>
-      <x:c r="S18"/>
-      <x:c r="T18"/>
-      <x:c r="U18"/>
-      <x:c r="V18"/>
-      <x:c r="W18"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-      <x:c r="I19"/>
-      <x:c r="J19"/>
-      <x:c r="K19"/>
-      <x:c r="L19"/>
-      <x:c r="M19"/>
-      <x:c r="N19"/>
-      <x:c r="O19"/>
-      <x:c r="P19"/>
-      <x:c r="Q19"/>
-      <x:c r="R19"/>
-      <x:c r="S19"/>
-      <x:c r="T19"/>
-      <x:c r="U19"/>
-      <x:c r="V19"/>
-      <x:c r="W19"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/app/template_knowledge/sources/영상편집DB_원본구간.xlsx
+++ b/app/template_knowledge/sources/영상편집DB_원본구간.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="Rf724c0532b10471e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="Rc209c255fcc84583"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="Rfb8ccf188f6a4154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="Rfc4c116a82fa4c40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="Rd0501696557c4639"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="R4d353376ced846c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R3a2735aba24c4175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="Rafd7c9cb14c44b1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R356bef69aa3342e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R62d140c102664418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="Rddef04beeea44f27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="Rfeca9a9d91524650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R4fd58b2a37b745ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_GUIDE" sheetId="1" r:id="Rda825a8180664b7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_DASHBOARD" sheetId="2" r:id="Rec2eaf8a274548ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_INPUT_GUIDES" sheetId="3" r:id="Rb6fb039cceaa443f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GUIDE_TEMPLATES" sheetId="4" r:id="R4f587b8cf92f41fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_SHOOT_AND_CUTS" sheetId="5" r:id="R5cdfd42a3cf84f12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_PRODUCED_VIDEOS" sheetId="6" r:id="Rcac0de5d85174c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_EDIT_RECIPES" sheetId="7" r:id="R12f44648c4e74a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_OVERLAYS" sheetId="8" r:id="R280ae784aa8c4756"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_USER_OUTPUTS" sheetId="9" r:id="R8e8392e717424049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PERFORMANCE" sheetId="10" r:id="R73d3673e2d884e00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_POST_TEMPLATES" sheetId="11" r:id="R1c99463878904ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_MODEL_POLICIES" sheetId="12" r:id="Rda9766f492774808"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_SOURCE_GUIDES" sheetId="13" r:id="R7f4d9921bfca4d66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -630,7 +630,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="21" t="str">
-        <x:v>SARILS 영상편집 의사결정 템플릿 v5.4 · 실제 가이드 3종</x:v>
+        <x:v>SARILS 영상편집 의사결정 템플릿 v5.4 · 실제 가이드 4종</x:v>
       </x:c>
       <x:c r="B1" s="21"/>
       <x:c r="C1" s="21"/>
@@ -638,7 +638,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>주술회전·동그리오·오츠카레 원문과 실제 장면 분석을 실행 템플릿에 연결하며, 삭제된 카페 랭킹 데이터는 포함하지 않습니다.</x:v>
+        <x:v>주술회전·동그리오·오츠카레·도마 BAD 원문과 장면 분석을 실행 템플릿에 연결하며, 삭제된 카페 랭킹 데이터는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -932,16 +932,16 @@
     </x:row>
     <x:row r="24" ht="44" customHeight="1">
       <x:c r="A24" s="42" t="str">
-        <x:v>실제 가이드 3종</x:v>
+        <x:v>실제 가이드 4종</x:v>
       </x:c>
       <x:c r="B24" s="46" t="str">
-        <x:v>주술회전 트랜지션 · 동그리오 챌린지 · 오츠카레 썸머 챌린지를 실제 레코드로 등록</x:v>
+        <x:v>주술회전 트랜지션 · 동그리오 챌린지 · 오츠카레 썸머 챌린지 · 도마 BAD 챌린지를 실제 레코드로 등록</x:v>
       </x:c>
       <x:c r="C24" s="46" t="str">
         <x:v>02, 03, 12</x:v>
       </x:c>
       <x:c r="D24" s="46" t="str">
-        <x:v>세 가이드의 원문·분석 근거와 실행 구간만 보존</x:v>
+        <x:v>네 가이드의 원문·분석 근거와 실행 구간만 보존</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -26736,134 +26736,354 @@
       </x:c>
     </x:row>
     <x:row r="707" ht="18" customHeight="1">
-      <x:c r="A707"/>
-      <x:c r="B707"/>
-      <x:c r="C707"/>
-      <x:c r="D707"/>
-      <x:c r="E707"/>
-      <x:c r="F707"/>
-      <x:c r="G707"/>
-      <x:c r="H707"/>
-      <x:c r="I707"/>
-      <x:c r="J707"/>
-      <x:c r="K707"/>
+      <x:c r="A707" t="str">
+        <x:v>domabad20260831_line_0001</x:v>
+      </x:c>
+      <x:c r="B707" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C707" t="n">
+        <x:v>923</x:v>
+      </x:c>
+      <x:c r="D707" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E707" t="str">
+        <x:v>SUMMARY</x:v>
+      </x:c>
+      <x:c r="F707" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G707" t="str">
+        <x:v>- source_url: https://www.youtube.com/shorts/rUIEHnyoPrU; 11초 STATIC_FULL_SHOT 원테이크, physical_cut_count=0, confidence=0.98, shooting_difficulty: ★★.</x:v>
+      </x:c>
+      <x:c r="H707" t="str">
+        <x:v>도마BAD_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I707" t="str">
+        <x:v>91A65C9532353963E3F00EC831CC46F59464A361F8A598F2CECBCD2E6E168BA1</x:v>
+      </x:c>
+      <x:c r="J707" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K707" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="708" ht="18" customHeight="1">
-      <x:c r="A708"/>
-      <x:c r="B708"/>
-      <x:c r="C708"/>
-      <x:c r="D708"/>
-      <x:c r="E708"/>
-      <x:c r="F708"/>
-      <x:c r="G708"/>
-      <x:c r="H708"/>
-      <x:c r="I708"/>
-      <x:c r="J708"/>
-      <x:c r="K708"/>
+      <x:c r="A708" t="str">
+        <x:v>domabad20260831_line_0002</x:v>
+      </x:c>
+      <x:c r="B708" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C708" t="n">
+        <x:v>924</x:v>
+      </x:c>
+      <x:c r="D708" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E708" t="str">
+        <x:v>SEMANTIC_PHASE</x:v>
+      </x:c>
+      <x:c r="F708" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G708" t="str">
+        <x:v>- 0~4000ms HOOK_SETUP: 고정 전신 구도에서 자연스러운 준비 동작을 연속 수행.</x:v>
+      </x:c>
+      <x:c r="H708" t="str">
+        <x:v>도마BAD_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I708" t="str">
+        <x:v>91A65C9532353963E3F00EC831CC46F59464A361F8A598F2CECBCD2E6E168BA1</x:v>
+      </x:c>
+      <x:c r="J708" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K708" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="709" ht="18" customHeight="1">
-      <x:c r="A709"/>
-      <x:c r="B709"/>
-      <x:c r="C709"/>
-      <x:c r="D709"/>
-      <x:c r="E709"/>
-      <x:c r="F709"/>
-      <x:c r="G709"/>
-      <x:c r="H709"/>
-      <x:c r="I709"/>
-      <x:c r="J709"/>
-      <x:c r="K709"/>
+      <x:c r="A709" t="str">
+        <x:v>domabad20260831_line_0003</x:v>
+      </x:c>
+      <x:c r="B709" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C709" t="n">
+        <x:v>925</x:v>
+      </x:c>
+      <x:c r="D709" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E709" t="str">
+        <x:v>SEMANTIC_PHASE</x:v>
+      </x:c>
+      <x:c r="F709" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G709" t="str">
+        <x:v>- 4000~5000ms PRE_DROP_BUILDUP: 드롭 직전 짧은 준비·방향 전환 동작. 경계에서 영상을 분할하지 않음.</x:v>
+      </x:c>
+      <x:c r="H709" t="str">
+        <x:v>도마BAD_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I709" t="str">
+        <x:v>91A65C9532353963E3F00EC831CC46F59464A361F8A598F2CECBCD2E6E168BA1</x:v>
+      </x:c>
+      <x:c r="J709" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K709" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="710" ht="18" customHeight="1">
-      <x:c r="A710"/>
-      <x:c r="B710"/>
-      <x:c r="C710"/>
-      <x:c r="D710"/>
-      <x:c r="E710"/>
-      <x:c r="F710"/>
-      <x:c r="G710"/>
-      <x:c r="H710"/>
-      <x:c r="I710"/>
-      <x:c r="J710"/>
-      <x:c r="K710"/>
+      <x:c r="A710" t="str">
+        <x:v>domabad20260831_line_0004</x:v>
+      </x:c>
+      <x:c r="B710" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C710" t="n">
+        <x:v>926</x:v>
+      </x:c>
+      <x:c r="D710" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E710" t="str">
+        <x:v>SEMANTIC_PHASE</x:v>
+      </x:c>
+      <x:c r="F710" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G710" t="str">
+        <x:v>- 5000~11000ms CLIMAX_DANCE: 비트 드롭과 동시에 방향을 반전하고 대비되는 안무를 연속 수행.</x:v>
+      </x:c>
+      <x:c r="H710" t="str">
+        <x:v>도마BAD_1프레임.json</x:v>
+      </x:c>
+      <x:c r="I710" t="str">
+        <x:v>91A65C9532353963E3F00EC831CC46F59464A361F8A598F2CECBCD2E6E168BA1</x:v>
+      </x:c>
+      <x:c r="J710" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K710" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="711" ht="18" customHeight="1">
-      <x:c r="A711"/>
-      <x:c r="B711"/>
-      <x:c r="C711"/>
-      <x:c r="D711"/>
-      <x:c r="E711"/>
-      <x:c r="F711"/>
-      <x:c r="G711"/>
-      <x:c r="H711"/>
-      <x:c r="I711"/>
-      <x:c r="J711"/>
-      <x:c r="K711"/>
+      <x:c r="A711" t="str">
+        <x:v>domabad20260831_line_0005</x:v>
+      </x:c>
+      <x:c r="B711" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C711" t="n">
+        <x:v>927</x:v>
+      </x:c>
+      <x:c r="D711" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E711" t="str">
+        <x:v>CONTINUITY</x:v>
+      </x:c>
+      <x:c r="F711" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G711" t="str">
+        <x:v>- ONE_TAKE, expected_take_count_per_output=1, split/reorder/internal trim/start trim/end trim 모두 금지.</x:v>
+      </x:c>
+      <x:c r="H711" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I711" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J711" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K711" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="712" ht="18" customHeight="1">
-      <x:c r="A712"/>
-      <x:c r="B712"/>
-      <x:c r="C712"/>
-      <x:c r="D712"/>
-      <x:c r="E712"/>
-      <x:c r="F712"/>
-      <x:c r="G712"/>
-      <x:c r="H712"/>
-      <x:c r="I712"/>
-      <x:c r="J712"/>
-      <x:c r="K712"/>
+      <x:c r="A712" t="str">
+        <x:v>domabad20260831_line_0006</x:v>
+      </x:c>
+      <x:c r="B712" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C712" t="n">
+        <x:v>928</x:v>
+      </x:c>
+      <x:c r="D712" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E712" t="str">
+        <x:v>CAMERA</x:v>
+      </x:c>
+      <x:c r="F712" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G712" t="str">
+        <x:v>- 전체 STATIC_FULL_SHOT. 카메라 이동, 디지털 줌, animated pan/rotation, punch-in 및 transform keyframe 없음.</x:v>
+      </x:c>
+      <x:c r="H712" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I712" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J712" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K712" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="713" ht="18" customHeight="1">
-      <x:c r="A713"/>
-      <x:c r="B713"/>
-      <x:c r="C713"/>
-      <x:c r="D713"/>
-      <x:c r="E713"/>
-      <x:c r="F713"/>
-      <x:c r="G713"/>
-      <x:c r="H713"/>
-      <x:c r="I713"/>
-      <x:c r="J713"/>
-      <x:c r="K713"/>
+      <x:c r="A713" t="str">
+        <x:v>domabad20260831_line_0007</x:v>
+      </x:c>
+      <x:c r="B713" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C713" t="n">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c r="D713" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E713" t="str">
+        <x:v>AUDIO_SYNC</x:v>
+      </x:c>
+      <x:c r="F713" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G713" t="str">
+        <x:v>- 5000ms VISUAL_DROP_REVERSAL과 AUDIO_DROP_HIT 정렬. 외부 음원이 있을 때 audio offset만 조정하고 영상 타임라인은 유지.</x:v>
+      </x:c>
+      <x:c r="H713" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I713" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J713" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K713" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="714" ht="18" customHeight="1">
-      <x:c r="A714"/>
-      <x:c r="B714"/>
-      <x:c r="C714"/>
-      <x:c r="D714"/>
-      <x:c r="E714"/>
-      <x:c r="F714"/>
-      <x:c r="G714"/>
-      <x:c r="H714"/>
-      <x:c r="I714"/>
-      <x:c r="J714"/>
-      <x:c r="K714"/>
+      <x:c r="A714" t="str">
+        <x:v>domabad20260831_line_0008</x:v>
+      </x:c>
+      <x:c r="B714" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C714" t="n">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="D714" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E714" t="str">
+        <x:v>CAPTION</x:v>
+      </x:c>
+      <x:c r="F714" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G714" t="str">
+        <x:v>- 레퍼런스 자막 근거 없음. 고정 문구를 복제하지 않고 사용자 영상·홍보 맥락에서 동적으로 생성하며 드롭 앵커를 가리지 않음.</x:v>
+      </x:c>
+      <x:c r="H714" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I714" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J714" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K714" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="715" ht="18" customHeight="1">
-      <x:c r="A715"/>
-      <x:c r="B715"/>
-      <x:c r="C715"/>
-      <x:c r="D715"/>
-      <x:c r="E715"/>
-      <x:c r="F715"/>
-      <x:c r="G715"/>
-      <x:c r="H715"/>
-      <x:c r="I715"/>
-      <x:c r="J715"/>
-      <x:c r="K715"/>
+      <x:c r="A715" t="str">
+        <x:v>domabad20260831_line_0009</x:v>
+      </x:c>
+      <x:c r="B715" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C715" t="n">
+        <x:v>931</x:v>
+      </x:c>
+      <x:c r="D715" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E715" t="str">
+        <x:v>INPUT_POLICY</x:v>
+      </x:c>
+      <x:c r="F715" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G715" t="str">
+        <x:v>- 단일 연속 사용자 영상 1개만 사용. 사진, B-roll, cutaway, multi-clip montage는 허용하지 않음.</x:v>
+      </x:c>
+      <x:c r="H715" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I715" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J715" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K715" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="716" ht="18" customHeight="1">
-      <x:c r="A716"/>
-      <x:c r="B716"/>
-      <x:c r="C716"/>
-      <x:c r="D716"/>
-      <x:c r="E716"/>
-      <x:c r="F716"/>
-      <x:c r="G716"/>
-      <x:c r="H716"/>
-      <x:c r="I716"/>
-      <x:c r="J716"/>
-      <x:c r="K716"/>
+      <x:c r="A716" t="str">
+        <x:v>domabad20260831_line_0010</x:v>
+      </x:c>
+      <x:c r="B716" t="str">
+        <x:v>uploaded_doma_bad_json_20260831</x:v>
+      </x:c>
+      <x:c r="C716" t="n">
+        <x:v>932</x:v>
+      </x:c>
+      <x:c r="D716" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="E716" t="str">
+        <x:v>VALIDATION</x:v>
+      </x:c>
+      <x:c r="F716" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G716" t="str">
+        <x:v>- video span=1, split=false, physical transition=0, speed=1.0, reverse=false, freeze=false, image/B-roll=0, reference caption reuse=false.</x:v>
+      </x:c>
+      <x:c r="H716" t="str">
+        <x:v>도마BAD_인사이트.json</x:v>
+      </x:c>
+      <x:c r="I716" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+      <x:c r="J716" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="K716" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS</x:v>
+      </x:c>
     </x:row>
     <x:row r="717" ht="18" customHeight="1">
       <x:c r="A717"/>
@@ -28584,7 +28804,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>실제 등록된 가이드 3종과 이후 누적되는 사용자 영상 레코드를 집계합니다. 카페 추천 리뷰는 포함하지 않습니다.</x:v>
+        <x:v>실제 등록된 가이드 4종과 이후 누적되는 사용자 영상 레코드를 집계합니다. 삭제된 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -28615,10 +28835,10 @@
         <x:v>챌린지 입력</x:v>
       </x:c>
       <x:c r="B5" s="26" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
-        <x:v>주술회전 1위·동그리오 2위·오츠카레 썸머 3위</x:v>
+        <x:v>주술회전 1위·동그리오 2위·오츠카레 썸머 3위·도마 BAD 4위</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>02_INPUT_GUIDES</x:v>
@@ -28629,10 +28849,10 @@
         <x:v>가이드 템플릿 구간</x:v>
       </x:c>
       <x:c r="B6" s="26" t="n">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C6" s="18" t="str">
-        <x:v>신규 주술회전 8컷 + 동그리오 7컷 + 기존 오츠카레 5구간</x:v>
+        <x:v>주술회전 8컷 + 동그리오 7컷 + 기존 오츠카레 5구간 + 도마 BAD 3개 의미 구간</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
         <x:v>03_GUIDE_TEMPLATES</x:v>
@@ -28761,7 +28981,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>주술회전·동그리오·오츠카레 썸머의 승인된 가이드와 순위 1·2·3을 유지하며 카페 추천 리뷰는 포함하지 않습니다.</x:v>
+        <x:v>주술회전·동그리오·오츠카레 썸머·도마 BAD 가이드와 순위 1·2·3·4를 유지하며 삭제된 카페 추천 리뷰는 포함하지 않습니다.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -28896,6 +29116,35 @@
         <x:v>e-dU9yQfmik</x:v>
       </x:c>
       <x:c r="I7" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>uploaded_analysis_json_20260831</x:v>
+      </x:c>
+      <x:c r="B8" t="n">
+        <x:v>46264.99015046296</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>도마 BAD 챌린지</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>도마 BAD 챌린지</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>https://www.youtube.com/shorts/rUIEHnyoPrU</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>rUIEHnyoPrU</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
@@ -28944,7 +29193,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="53" t="str">
-        <x:v>실제 편집 가이드 3종 · 실행용 구간 규칙 v5.4</x:v>
+        <x:v>실제 편집 가이드 4종 · 실행용 구간 규칙 v5.4</x:v>
       </x:c>
       <x:c r="B1" s="53"/>
       <x:c r="C1" s="53"/>
@@ -28971,7 +29220,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="56" t="str">
-        <x:v>업로드 JSON의 주술회전 8컷·동그리오 7컷과 기존 오츠카레 실행 구간을 같은 A:W 스키마로 보존합니다. 카페 추천 리뷰는 포함하지 않습니다.</x:v>
+        <x:v>주술회전 8컷·동그리오 7컷·기존 오츠카레 실행 구간·도마 BAD 원테이크 의미 구간을 같은 A:W 스키마로 보존합니다.</x:v>
       </x:c>
       <x:c r="B2" s="56"/>
       <x:c r="C2" s="56"/>
@@ -29094,16 +29343,16 @@
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="47" t="str">
-        <x:v>gts_jujutsu_v5_01</x:v>
+        <x:v>gts_otsukare_01</x:v>
       </x:c>
       <x:c r="B5" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v5</x:v>
+        <x:v>gt_otsukare_summer_v2</x:v>
       </x:c>
       <x:c r="C5" s="47" t="str">
-        <x:v>jujutsu_transition</x:v>
+        <x:v>otsukare_summer_challenge</x:v>
       </x:c>
       <x:c r="D5" s="49" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="49" t="n">
         <x:v>1</x:v>
@@ -29112,334 +29361,332 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="67" t="n">
-        <x:v>1500</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="H5" s="47" t="str">
-        <x:v>인물 A 빈손 포즈 훅</x:v>
+        <x:v>오버헤드 V 포즈 훅</x:v>
       </x:c>
       <x:c r="I5" s="47" t="str">
-        <x:v>HOOK_SETUP</x:v>
+        <x:v>DANCE_OVERHEAD_HOOK</x:v>
       </x:c>
       <x:c r="J5" s="47" t="str">
-        <x:v>인물 A가 고정 미디엄 구도에서 빈손 시그니처 포즈에 진입해 안정적으로 유지</x:v>
+        <x:v>한 명의 출연자가 오버헤드 근접 구도에서 V 포즈와 표정으로 시작하고 즉시 메인 안무로 연결</x:v>
       </x:c>
       <x:c r="K5" s="47" t="str">
-        <x:v>POSE_HOLD_END_ANCHORED; S02와 신체·손·배경 특징점을 정렬하고 1500ms SFX 직전에 종료</x:v>
-      </x:c>
-      <x:c r="L5" s="47"/>
+        <x:v>0–467ms; speed=1.0; 다음 와이드 구간으로 동작이 끊기지 않게 연결</x:v>
+      </x:c>
+      <x:c r="L5" s="47" t="str">
+        <x:v>{{caption.hook}}</x:v>
+      </x:c>
       <x:c r="M5" s="47" t="str">
-        <x:v>promo.primary,store.owner_face_allowed</x:v>
+        <x:v>caption.hook,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N5" s="47" t="str">
-        <x:v>첫 공개 아이템은 실제 대표 메뉴/상품으로 정하고 동일 인물·구도·배경의 S02와 한 쌍으로 촬영</x:v>
+        <x:v>출연자는 촬영 동의된 매장 관계자만 사용하고 훅 자막은 얼굴·손을 가리지 않는 세이프존에 1줄로 표시</x:v>
       </x:c>
       <x:c r="O5" s="47" t="str">
-        <x:v>sfx</x:v>
+        <x:v>caption,text_2d</x:v>
       </x:c>
       <x:c r="P5" s="49" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q5" s="48" t="n">
-        <x:v>46264.395833333336</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q5" s="48" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
       </x:c>
       <x:c r="R5" s="47" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S5" s="47" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T5" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
       </x:c>
       <x:c r="U5" s="47" t="str">
-        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V5" s="47" t="str">
-        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+        <x:v>원본 BGM은 합성하지 않고 플랫폼 UI를 복제하지 않음. 안무와 얼굴 가시성을 우선.</x:v>
       </x:c>
       <x:c r="W5" s="47" t="str">
-        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="47" t="str">
-        <x:v>gts_jujutsu_v5_02</x:v>
+        <x:v>gts_otsukare_02</x:v>
       </x:c>
       <x:c r="B6" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v5</x:v>
+        <x:v>gt_otsukare_summer_v2</x:v>
       </x:c>
       <x:c r="C6" s="47" t="str">
-        <x:v>jujutsu_transition</x:v>
+        <x:v>otsukare_summer_challenge</x:v>
       </x:c>
       <x:c r="D6" s="49" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E6" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="67" t="n">
-        <x:v>1500</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="G6" s="67" t="n">
-        <x:v>3500</x:v>
+        <x:v>3933</x:v>
       </x:c>
       <x:c r="H6" s="47" t="str">
-        <x:v>인물 A 첫 아이템 공개</x:v>
+        <x:v>와이드 안무 A → 오버헤드 포인트</x:v>
       </x:c>
       <x:c r="I6" s="47" t="str">
-        <x:v>MAGIC_REVEAL</x:v>
+        <x:v>DANCE_PHRASE_A</x:v>
       </x:c>
       <x:c r="J6" s="47" t="str">
-        <x:v>S01과 동일 포즈·구도에서 인물 A의 손에 실제 음료가 나타난 상태로 시작해 결과를 유지</x:v>
+        <x:v>전신이 보이는 와이드 안무를 연속 수행한 뒤 같은 동작 흐름에서 카메라가 위쪽 가까운 포인트로 이동</x:v>
       </x:c>
       <x:c r="K6" s="47" t="str">
-        <x:v>1500ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 디졸브·페이드 금지</x:v>
+        <x:v>WIDE 467–3300ms → OVERHEAD 3300–3933ms; speed=1.0; 중간 홍보 컷 삽입 금지</x:v>
       </x:c>
       <x:c r="L6" s="47"/>
       <x:c r="M6" s="47" t="str">
-        <x:v>promo.primary,store.owner_face_allowed</x:v>
+        <x:v>store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N6" s="47" t="str">
-        <x:v>S01 마지막 프레임과 가장 일치하는 ITEM_PRESENT 프레임을 선택하고 실제 음료/상품만 노출</x:v>
-      </x:c>
-      <x:c r="O6" s="47" t="str">
-        <x:v>sfx</x:v>
-      </x:c>
+        <x:v>실제 촬영 장소와 동의된 출연자로 개인화하되 안무 프레이즈와 카메라 전환 순서를 유지</x:v>
+      </x:c>
+      <x:c r="O6" s="47"/>
       <x:c r="P6" s="49" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q6" s="48" t="n">
-        <x:v>46264.395833333336</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q6" s="48" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
       </x:c>
       <x:c r="R6" s="47" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S6" s="47" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T6" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
       </x:c>
       <x:c r="U6" s="47" t="str">
-        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V6" s="47" t="str">
-        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+        <x:v>가이드에 없는 메뉴 B-roll·생성 장면을 중간에 넣지 않음.</x:v>
       </x:c>
       <x:c r="W6" s="47" t="str">
-        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="47" t="str">
-        <x:v>gts_jujutsu_v5_03</x:v>
+        <x:v>gts_otsukare_03</x:v>
       </x:c>
       <x:c r="B7" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v5</x:v>
+        <x:v>gt_otsukare_summer_v2</x:v>
       </x:c>
       <x:c r="C7" s="47" t="str">
-        <x:v>jujutsu_transition</x:v>
+        <x:v>otsukare_summer_challenge</x:v>
       </x:c>
       <x:c r="D7" s="49" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F7" s="67" t="n">
-        <x:v>3500</x:v>
+        <x:v>3933</x:v>
       </x:c>
       <x:c r="G7" s="67" t="n">
-        <x:v>5000</x:v>
+        <x:v>7400</x:v>
       </x:c>
       <x:c r="H7" s="47" t="str">
-        <x:v>인물 B 빈손 포즈 셋업</x:v>
+        <x:v>와이드 안무 B → 오버헤드 포인트</x:v>
       </x:c>
       <x:c r="I7" s="47" t="str">
-        <x:v>SETUP</x:v>
+        <x:v>DANCE_PHRASE_B</x:v>
       </x:c>
       <x:c r="J7" s="47" t="str">
-        <x:v>인물 B가 같은 고정 카메라에서 새로운 빈손 포즈를 취하고 안정 구간을 유지</x:v>
+        <x:v>전신 와이드 안무를 이어가며 팔과 상체 제스처를 보여준 뒤 두 번째 오버헤드 포인트로 연결</x:v>
       </x:c>
       <x:c r="K7" s="47" t="str">
-        <x:v>POSE_HOLD_END_ANCHORED; S04와 포즈·배경을 정렬하고 5000ms SFX 직전에 종료</x:v>
+        <x:v>WIDE 3933–6733ms → OVERHEAD 6733–7400ms; speed=1.0; 앞뒤 동작 연속성 유지</x:v>
       </x:c>
       <x:c r="L7" s="47"/>
       <x:c r="M7" s="47" t="str">
-        <x:v>promo.secondary,store.owner_face_allowed</x:v>
+        <x:v>store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N7" s="47" t="str">
-        <x:v>두 번째 출연자와 보조 메뉴를 사용하되 S04와 동일 인물·의상·배경 유지</x:v>
-      </x:c>
-      <x:c r="O7" s="47" t="str">
-        <x:v>sfx</x:v>
-      </x:c>
+        <x:v>의상·배경은 실제 촬영 맥락에 맞출 수 있으나 얼굴·손·몸동작을 이미지나 긴 자막으로 가리지 않음</x:v>
+      </x:c>
+      <x:c r="O7" s="47"/>
       <x:c r="P7" s="49" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q7" s="48" t="n">
-        <x:v>46264.395833333336</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q7" s="48" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
       </x:c>
       <x:c r="R7" s="47" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S7" s="47" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T7" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
       </x:c>
       <x:c r="U7" s="47" t="str">
-        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V7" s="47" t="str">
-        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+        <x:v>춤 프레임을 메뉴 이미지로 교체하지 않으며 실제 안무 수행 영상을 유지.</x:v>
       </x:c>
       <x:c r="W7" s="47" t="str">
-        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="47" t="str">
-        <x:v>gts_jujutsu_v5_04</x:v>
+        <x:v>gts_otsukare_04</x:v>
       </x:c>
       <x:c r="B8" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v5</x:v>
+        <x:v>gt_otsukare_summer_v2</x:v>
       </x:c>
       <x:c r="C8" s="47" t="str">
-        <x:v>jujutsu_transition</x:v>
+        <x:v>otsukare_summer_challenge</x:v>
       </x:c>
       <x:c r="D8" s="49" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E8" s="49" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="67" t="n">
-        <x:v>5000</x:v>
+        <x:v>7400</x:v>
       </x:c>
       <x:c r="G8" s="67" t="n">
-        <x:v>7000</x:v>
+        <x:v>10900</x:v>
       </x:c>
       <x:c r="H8" s="47" t="str">
-        <x:v>인물 B 두 번째 아이템 공개</x:v>
+        <x:v>와이드 안무 C → 마지막 오버헤드 전환</x:v>
       </x:c>
       <x:c r="I8" s="47" t="str">
-        <x:v>MAGIC_REVEAL</x:v>
+        <x:v>DANCE_PHRASE_C</x:v>
       </x:c>
       <x:c r="J8" s="47" t="str">
-        <x:v>S03과 동일 포즈·구도에서 인물 B의 손에 다른 음료가 나타난 상태로 전환</x:v>
+        <x:v>세 번째 와이드 안무 프레이즈를 이어가고 카메라가 위쪽으로 이동하면서 마지막 포즈를 준비</x:v>
       </x:c>
       <x:c r="K8" s="47" t="str">
-        <x:v>5000ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 7000ms HARD_CUT</x:v>
+        <x:v>WIDE 7400–10200ms → OVERHEAD 10200–10900ms; speed=1.0; 흐름 삭제·재배열 금지</x:v>
       </x:c>
       <x:c r="L8" s="47"/>
       <x:c r="M8" s="47" t="str">
-        <x:v>promo.secondary,store.owner_face_allowed</x:v>
+        <x:v>store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N8" s="47" t="str">
-        <x:v>S03 마지막 프레임과 가장 일치하는 ITEM_PRESENT 프레임을 시작점으로 선택</x:v>
-      </x:c>
-      <x:c r="O8" s="47" t="str">
-        <x:v>sfx</x:v>
-      </x:c>
+        <x:v>매장 홍보는 촬영 배경과 출연 맥락으로 자연스럽게 드러내고 별도 홍보 컷을 삽입하지 않음</x:v>
+      </x:c>
+      <x:c r="O8" s="47"/>
       <x:c r="P8" s="49" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q8" s="48" t="n">
-        <x:v>46264.395833333336</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q8" s="48" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
       </x:c>
       <x:c r="R8" s="47" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S8" s="47" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T8" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
       </x:c>
       <x:c r="U8" s="47" t="str">
-        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V8" s="47" t="str">
-        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+        <x:v>미지원 피사체 추적·배경 합성 없이 실제 촬영 카메라 동선과 컷 연결만 사용.</x:v>
       </x:c>
       <x:c r="W8" s="47" t="str">
-        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="47" t="str">
-        <x:v>gts_jujutsu_v5_05</x:v>
+        <x:v>gts_otsukare_05</x:v>
       </x:c>
       <x:c r="B9" s="47" t="str">
-        <x:v>gt_jujutsu_transition_v5</x:v>
+        <x:v>gt_otsukare_summer_v2</x:v>
       </x:c>
       <x:c r="C9" s="47" t="str">
-        <x:v>jujutsu_transition</x:v>
+        <x:v>otsukare_summer_challenge</x:v>
       </x:c>
       <x:c r="D9" s="47" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E9" s="47" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F9" s="47" t="n">
-        <x:v>7000</x:v>
+        <x:v>10900</x:v>
       </x:c>
       <x:c r="G9" s="47" t="n">
-        <x:v>8500</x:v>
+        <x:v>11500</x:v>
       </x:c>
       <x:c r="H9" s="47" t="str">
-        <x:v>인물 A 새 빈손 포즈 셋업</x:v>
+        <x:v>오버헤드 근접 마지막 포즈</x:v>
       </x:c>
       <x:c r="I9" s="47" t="str">
-        <x:v>SETUP</x:v>
+        <x:v>DANCE_FINAL_POSE</x:v>
       </x:c>
       <x:c r="J9" s="47" t="str">
-        <x:v>인물 A가 다시 등장해 제품 공개 전 새 빈손 포즈를 안정적으로 유지</x:v>
+        <x:v>얼굴과 손동작이 가까워지는 오버헤드 포즈로 안무를 닫고 짧은 CTA를 안전 영역에 표시</x:v>
       </x:c>
       <x:c r="K9" s="47" t="str">
-        <x:v>POSE_HOLD_END_ANCHORED; S06과 정렬하고 8500ms SFX 직전에 종료</x:v>
-      </x:c>
-      <x:c r="L9" s="47"/>
+        <x:v>10900–11500ms; speed=1.0; CTA는 마지막 0.6초 안에서 한 줄만 사용</x:v>
+      </x:c>
+      <x:c r="L9" s="47" t="str">
+        <x:v>{{store.name}} · {{caption.cta}}</x:v>
+      </x:c>
       <x:c r="M9" s="47" t="str">
-        <x:v>promo.tertiary,store.owner_face_allowed</x:v>
+        <x:v>store.name,caption.cta,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N9" s="47" t="str">
-        <x:v>세 번째 실제 메뉴의 형태를 고려해 손과 테이블이 가리지 않는 포즈 선택</x:v>
+        <x:v>검증된 매장명과 짧은 CTA만 사용하고 얼굴·손을 가리지 않는 하단 세이프존에 배치</x:v>
       </x:c>
       <x:c r="O9" s="47" t="str">
-        <x:v>sfx</x:v>
+        <x:v>caption,text_2d,sfx</x:v>
       </x:c>
       <x:c r="P9" s="47" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="Q9" s="48" t="n">
-        <x:v>46264.395833333336</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q9" s="48" t="str">
+        <x:v>2026-08-24T22:00:00</x:v>
       </x:c>
       <x:c r="R9" s="47" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S9" s="47" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>SUPERSEDED</x:v>
       </x:c>
       <x:c r="T9" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
       </x:c>
       <x:c r="U9" s="47" t="str">
-        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V9" s="47" t="str">
-        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
+        <x:v>사용자는 앱에서 음원을 직접 추가하며 템플릿은 음원 제목·시작 위치만 최종 제공.</x:v>
       </x:c>
       <x:c r="W9" s="47" t="str">
-        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
+        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="47" t="str">
-        <x:v>gts_jujutsu_v5_06</x:v>
+        <x:v>gts_jujutsu_v5_01</x:v>
       </x:c>
       <x:c r="B10" s="47" t="str">
         <x:v>gt_jujutsu_transition_v5</x:v>
@@ -29451,32 +29698,32 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E10" s="47" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F10" s="47" t="n">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G10" s="47" t="n">
-        <x:v>10500</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="H10" s="47" t="str">
-        <x:v>인물 A 제품 공개</x:v>
+        <x:v>인물 A 빈손 포즈 훅</x:v>
       </x:c>
       <x:c r="I10" s="47" t="str">
-        <x:v>MAGIC_REVEAL</x:v>
+        <x:v>HOOK_SETUP</x:v>
       </x:c>
       <x:c r="J10" s="47" t="str">
-        <x:v>S05와 동일 포즈·구도에서 인물 A가 실제 제품을 든 상태로 시작</x:v>
+        <x:v>인물 A가 고정 미디엄 구도에서 빈손 시그니처 포즈에 진입해 안정적으로 유지</x:v>
       </x:c>
       <x:c r="K10" s="47" t="str">
-        <x:v>8500ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 아이템 전체가 보이는 결과 홀드</x:v>
+        <x:v>POSE_HOLD_END_ANCHORED; S02와 신체·손·배경 특징점을 정렬하고 1500ms SFX 직전에 종료</x:v>
       </x:c>
       <x:c r="L10" s="47"/>
       <x:c r="M10" s="47" t="str">
-        <x:v>promo.tertiary,store.owner_face_allowed</x:v>
+        <x:v>promo.primary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N10" s="47" t="str">
-        <x:v>실제 촬영된 제품/대표 상품으로 치환하고 S05 경계의 포즈 일치 우선</x:v>
+        <x:v>첫 공개 아이템은 실제 대표 메뉴/상품으로 정하고 동일 인물·구도·배경의 S02와 한 쌍으로 촬영</x:v>
       </x:c>
       <x:c r="O10" s="47" t="str">
         <x:v>sfx</x:v>
@@ -29508,7 +29755,7 @@
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="47" t="str">
-        <x:v>gts_jujutsu_v5_07</x:v>
+        <x:v>gts_jujutsu_v5_02</x:v>
       </x:c>
       <x:c r="B11" s="47" t="str">
         <x:v>gt_jujutsu_transition_v5</x:v>
@@ -29520,32 +29767,32 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="47" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="47" t="n">
-        <x:v>10500</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G11" s="47" t="n">
-        <x:v>12000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="H11" s="47" t="str">
-        <x:v>인물 B 마지막 빈손 포즈 셋업</x:v>
+        <x:v>인물 A 첫 아이템 공개</x:v>
       </x:c>
       <x:c r="I11" s="47" t="str">
-        <x:v>SETUP</x:v>
+        <x:v>MAGIC_REVEAL</x:v>
       </x:c>
       <x:c r="J11" s="47" t="str">
-        <x:v>인물 B가 마지막 공개를 위한 빈손 포즈를 취하고 배경·카메라를 고정</x:v>
+        <x:v>S01과 동일 포즈·구도에서 인물 A의 손에 실제 음료가 나타난 상태로 시작해 결과를 유지</x:v>
       </x:c>
       <x:c r="K11" s="47" t="str">
-        <x:v>POSE_HOLD_END_ANCHORED; S08과 정렬하고 12000ms SFX 직전에 종료</x:v>
+        <x:v>1500ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 디졸브·페이드 금지</x:v>
       </x:c>
       <x:c r="L11" s="47"/>
       <x:c r="M11" s="47" t="str">
-        <x:v>promo.quaternary,store.owner_face_allowed</x:v>
+        <x:v>promo.primary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N11" s="47" t="str">
-        <x:v>네 번째 실제 메뉴를 놓을 위치를 비워 두고 S08과 동일 인물·구도 유지</x:v>
+        <x:v>S01 마지막 프레임과 가장 일치하는 ITEM_PRESENT 프레임을 선택하고 실제 음료/상품만 노출</x:v>
       </x:c>
       <x:c r="O11" s="47" t="str">
         <x:v>sfx</x:v>
@@ -29577,7 +29824,7 @@
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
       <x:c r="A12" s="47" t="str">
-        <x:v>gts_jujutsu_v5_08</x:v>
+        <x:v>gts_jujutsu_v5_03</x:v>
       </x:c>
       <x:c r="B12" s="47" t="str">
         <x:v>gt_jujutsu_transition_v5</x:v>
@@ -29589,32 +29836,32 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="47" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F12" s="47" t="n">
-        <x:v>12000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G12" s="47" t="n">
-        <x:v>14000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="H12" s="47" t="str">
-        <x:v>인물 B 제품 최종 공개</x:v>
+        <x:v>인물 B 빈손 포즈 셋업</x:v>
       </x:c>
       <x:c r="I12" s="47" t="str">
-        <x:v>MAGIC_REVEAL</x:v>
+        <x:v>SETUP</x:v>
       </x:c>
       <x:c r="J12" s="47" t="str">
-        <x:v>S07과 동일 포즈·구도에서 실제 제품이 나타난 상태로 전환해 아웃트로 유지</x:v>
+        <x:v>인물 B가 같은 고정 카메라에서 새로운 빈손 포즈를 취하고 안정 구간을 유지</x:v>
       </x:c>
       <x:c r="K12" s="47" t="str">
-        <x:v>12000ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 14000ms까지 결과 홀드</x:v>
+        <x:v>POSE_HOLD_END_ANCHORED; S04와 포즈·배경을 정렬하고 5000ms SFX 직전에 종료</x:v>
       </x:c>
       <x:c r="L12" s="47"/>
       <x:c r="M12" s="47" t="str">
-        <x:v>promo.quaternary,store.owner_face_allowed</x:v>
+        <x:v>promo.secondary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N12" s="47" t="str">
-        <x:v>실제 촬영된 제품/상품을 명확히 보여주고 추가 전환 없이 종료</x:v>
+        <x:v>두 번째 출연자와 보조 메뉴를 사용하되 S04와 동일 인물·의상·배경 유지</x:v>
       </x:c>
       <x:c r="O12" s="47" t="str">
         <x:v>sfx</x:v>
@@ -29646,49 +29893,47 @@
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" s="47" t="str">
-        <x:v>gts_donggeurio_v1_01</x:v>
+        <x:v>gts_jujutsu_v5_04</x:v>
       </x:c>
       <x:c r="B13" s="47" t="str">
-        <x:v>gt_donggeurio_challenge_v1</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C13" s="47" t="str">
-        <x:v>donggeurio_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D13" s="47" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E13" s="47" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F13" s="47" t="n">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G13" s="47" t="n">
-        <x:v>1033</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="H13" s="47" t="str">
-        <x:v>감성 타이틀 훅</x:v>
+        <x:v>인물 B 두 번째 아이템 공개</x:v>
       </x:c>
       <x:c r="I13" s="47" t="str">
-        <x:v>HOOK</x:v>
+        <x:v>MAGIC_REVEAL</x:v>
       </x:c>
       <x:c r="J13" s="47" t="str">
-        <x:v>안정적인 벽면·공간 디테일을 고정 구도로 보여주고 중앙 프로젝트 타이틀 배치</x:v>
+        <x:v>S03과 동일 포즈·구도에서 인물 B의 손에 다른 음료가 나타난 상태로 전환</x:v>
       </x:c>
       <x:c r="K13" s="47" t="str">
-        <x:v>실측 0~1033ms; 안정 구간 중심 trim; speed 0.95~1.05; 1033ms HARD_CUT</x:v>
-      </x:c>
-      <x:c r="L13" s="47" t="str">
-        <x:v>{{project.title}}</x:v>
-      </x:c>
+        <x:v>5000ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 7000ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L13" s="47"/>
       <x:c r="M13" s="47" t="str">
-        <x:v>project.title,store.name</x:v>
+        <x:v>promo.secondary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N13" s="47" t="str">
-        <x:v>레퍼런스 상호·핸들은 복제하지 않고 검증된 프로젝트명/매장명으로 교체</x:v>
+        <x:v>S03 마지막 프레임과 가장 일치하는 ITEM_PRESENT 프레임을 시작점으로 선택</x:v>
       </x:c>
       <x:c r="O13" s="47" t="str">
-        <x:v>caption,text_2d</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P13" s="47" t="n">
         <x:v>30</x:v>
@@ -29703,63 +29948,61 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T13" s="47" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U13" s="47" t="str">
         <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V13" s="47" t="str">
-        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W13" s="47" t="str">
-        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
       <x:c r="A14" t="str">
-        <x:v>gts_donggeurio_v1_02</x:v>
+        <x:v>gts_jujutsu_v5_05</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>gt_donggeurio_challenge_v1</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>donggeurio_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D14" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E14" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F14" t="n">
-        <x:v>1033</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G14" t="n">
-        <x:v>3767</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="H14" t="str">
-        <x:v>메뉴 항공샷 공개</x:v>
+        <x:v>인물 A 새 빈손 포즈 셋업</x:v>
       </x:c>
       <x:c r="I14" t="str">
-        <x:v>REVEAL</x:v>
+        <x:v>SETUP</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>메뉴 전체가 보이는 탑다운/하이앵글 샷에 1.00→1.05 선형 줌인과 하단 보조 텍스트 적용</x:v>
+        <x:v>인물 A가 다시 등장해 제품 공개 전 새 빈손 포즈를 안정적으로 유지</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>실측 1033~3767ms; 구성 최적 구간 trim; speed 0.9~1.1; 3767ms HARD_CUT</x:v>
-      </x:c>
-      <x:c r="L14" t="str">
-        <x:v>{{store.location_or_context}}</x:v>
-      </x:c>
+        <x:v>POSE_HOLD_END_ANCHORED; S06과 정렬하고 8500ms SFX 직전에 종료</x:v>
+      </x:c>
+      <x:c r="L14"/>
       <x:c r="M14" t="str">
-        <x:v>store.location,store.context,promo.primary</x:v>
+        <x:v>promo.tertiary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>실제 메뉴와 검증된 장소/맥락만 사용하고 숫자·혜택을 임의 생성하지 않음</x:v>
+        <x:v>세 번째 실제 메뉴의 형태를 고려해 손과 테이블이 가리지 않는 포즈 선택</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>caption,text_2d,transform</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P14" t="n">
         <x:v>30</x:v>
@@ -29774,61 +30017,61 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T14" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U14" t="str">
         <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V14" t="str">
-        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W14" t="str">
-        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="62" customHeight="1">
       <x:c r="A15" t="str">
-        <x:v>gts_donggeurio_v1_03</x:v>
+        <x:v>gts_jujutsu_v5_06</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>gt_donggeurio_challenge_v1</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>donggeurio_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D15" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E15" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F15" t="n">
-        <x:v>3767</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G15" t="n">
-        <x:v>4700</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="H15" t="str">
-        <x:v>카페 공간 팬</x:v>
+        <x:v>인물 A 제품 공개</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>AMBIENCE</x:v>
+        <x:v>MAGIC_REVEAL</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>조명·좌석·인테리어를 보여주는 가장 매끄러운 우향 팬/측면 이동 구간 선택</x:v>
+        <x:v>S05와 동일 포즈·구도에서 인물 A가 실제 제품을 든 상태로 시작</x:v>
       </x:c>
       <x:c r="K15" t="str">
-        <x:v>실측 3767~4700ms; 모션 중심 trim; speed 0.9~1.35; 소스 팬 보존; 4700ms HARD_CUT</x:v>
+        <x:v>8500ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 아이템 전체가 보이는 결과 홀드</x:v>
       </x:c>
       <x:c r="L15"/>
       <x:c r="M15" t="str">
-        <x:v>store.interior</x:v>
+        <x:v>promo.tertiary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>실제 촬영된 공간 정보량이 높은 구간을 사용하고 긴 팬 전체를 강제 고배속하지 않음</x:v>
+        <x:v>실제 촬영된 제품/대표 상품으로 치환하고 S05 경계의 포즈 일치 우선</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>transform</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P15" t="n">
         <x:v>30</x:v>
@@ -29843,61 +30086,61 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T15" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U15" t="str">
         <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V15" t="str">
-        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W15" t="str">
-        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="62" customHeight="1">
       <x:c r="A16" t="str">
-        <x:v>gts_donggeurio_v1_04</x:v>
+        <x:v>gts_jujutsu_v5_07</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>gt_donggeurio_challenge_v1</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>donggeurio_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D16" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F16" t="n">
-        <x:v>4700</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G16" t="n">
-        <x:v>7000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="H16" t="str">
-        <x:v>메뉴 인터랙션 클로즈업</x:v>
+        <x:v>인물 B 마지막 빈손 포즈 셋업</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>ACTION</x:v>
+        <x:v>SETUP</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>손이나 도구가 음식에 개입하는 클로즈업에서 동작 시작·피크·종료를 보존</x:v>
+        <x:v>인물 B가 마지막 공개를 위한 빈손 포즈를 취하고 배경·카메라를 고정</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>실측 4700~7000ms; ACTION_PEAK를 슬롯 58% 부근에 배치; speed 0.9~1.1; 7000ms HARD_CUT</x:v>
+        <x:v>POSE_HOLD_END_ANCHORED; S08과 정렬하고 12000ms SFX 직전에 종료</x:v>
       </x:c>
       <x:c r="L16"/>
       <x:c r="M16" t="str">
-        <x:v>promo.primary.action</x:v>
+        <x:v>promo.quaternary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>실제 촬영된 섞기·집기·서빙 행동을 우선하며 없는 행동을 생성하지 않음</x:v>
+        <x:v>네 번째 실제 메뉴를 놓을 위치를 비워 두고 S08과 동일 인물·구도 유지</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>transform</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P16" t="n">
         <x:v>30</x:v>
@@ -29912,61 +30155,61 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T16" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U16" t="str">
         <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V16" t="str">
-        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W16" t="str">
-        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="62" customHeight="1">
       <x:c r="A17" t="str">
-        <x:v>gts_donggeurio_v1_05</x:v>
+        <x:v>gts_jujutsu_v5_08</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>gt_donggeurio_challenge_v1</x:v>
+        <x:v>gt_jujutsu_transition_v5</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>donggeurio_challenge</x:v>
+        <x:v>jujutsu_transition</x:v>
       </x:c>
       <x:c r="D17" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>7000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G17" t="n">
-        <x:v>8333</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="H17" t="str">
-        <x:v>음식 자르기 액션 하이라이트</x:v>
+        <x:v>인물 B 제품 최종 공개</x:v>
       </x:c>
       <x:c r="I17" t="str">
-        <x:v>ACTION_HIGHLIGHT</x:v>
+        <x:v>MAGIC_REVEAL</x:v>
       </x:c>
       <x:c r="J17" t="str">
-        <x:v>포크/나이프로 음식을 자르거나 분리하는 핵심 순간을 타이트한 클로즈업으로 강조</x:v>
+        <x:v>S07과 동일 포즈·구도에서 실제 제품이 나타난 상태로 전환해 아웃트로 유지</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>실측 7000~8333ms; ACTION_PEAK 중심 trim; speed 0.75~1.0, 0.8 선호; 8333ms HARD_CUT</x:v>
+        <x:v>12000ms SFX 타격점 HARD_CUT_MATCH; speed=1.0; 14000ms까지 결과 홀드</x:v>
       </x:c>
       <x:c r="L17"/>
       <x:c r="M17" t="str">
-        <x:v>promo.secondary.action</x:v>
+        <x:v>promo.quaternary,store.owner_face_allowed</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>자르기 장면이 없으면 다른 실제 메뉴 액션으로 대체하고 0.9배 수준까지 완화</x:v>
+        <x:v>실제 촬영된 제품/상품을 명확히 보여주고 추가 전환 없이 종료</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>transform</x:v>
+        <x:v>sfx</x:v>
       </x:c>
       <x:c r="P17" t="n">
         <x:v>30</x:v>
@@ -29981,21 +30224,21 @@
         <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T17" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$679:$G$692</x:v>
       </x:c>
       <x:c r="U17" t="str">
         <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V17" t="str">
-        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
+        <x:v>레퍼런스 오디오는 렌더링하지 않고 플랫폼에서 권리 확인된 음원을 추가. 자동 미세 정렬 수치는 서버 정책에서만 해결.</x:v>
       </x:c>
       <x:c r="W17" t="str">
-        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+        <x:v>05D8F5E6115DE5C5F237753D3B01AF60EC479E42C2DFA273F2210D6349435FD6</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="62" customHeight="1">
       <x:c r="A18" t="str">
-        <x:v>gts_donggeurio_v1_06</x:v>
+        <x:v>gts_donggeurio_v1_01</x:v>
       </x:c>
       <x:c r="B18" t="str">
         <x:v>gt_donggeurio_challenge_v1</x:v>
@@ -30007,35 +30250,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E18" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" t="n">
-        <x:v>8333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G18" t="n">
-        <x:v>9633</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="H18" t="str">
-        <x:v>매장 외관·위치 공개</x:v>
+        <x:v>감성 타이틀 훅</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>LOCATION</x:v>
+        <x:v>HOOK</x:v>
       </x:c>
       <x:c r="J18" t="str">
-        <x:v>매장 외관·간판·입구 등 장소를 식별할 수 있는 구도를 짧게 제시하고 지원될 때만 미세 줌</x:v>
+        <x:v>안정적인 벽면·공간 디테일을 고정 구도로 보여주고 중앙 프로젝트 타이틀 배치</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>실측 8333~9633ms; 구성 중심 trim; speed 0.9~1.1; 실제 경계는 HARD_CUT 우선</x:v>
-      </x:c>
-      <x:c r="L18"/>
+        <x:v>실측 0~1033ms; 안정 구간 중심 trim; speed 0.95~1.05; 1033ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L18" t="str">
+        <x:v>{{project.title}}</x:v>
+      </x:c>
       <x:c r="M18" t="str">
-        <x:v>store.name,store.location</x:v>
+        <x:v>project.title,store.name</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>검증된 매장 외관/위치만 사용하고 SLIDE_LEFT 느낌은 선택적 악센트로만 취급</x:v>
+        <x:v>레퍼런스 상호·핸들은 복제하지 않고 검증된 프로젝트명/매장명으로 교체</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>caption,text_2d,transform</x:v>
+        <x:v>caption,text_2d</x:v>
       </x:c>
       <x:c r="P18" t="n">
         <x:v>30</x:v>
@@ -30064,7 +30309,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>gts_donggeurio_v1_07</x:v>
+        <x:v>gts_donggeurio_v1_02</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>gt_donggeurio_challenge_v1</x:v>
@@ -30076,35 +30321,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E19" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F19" t="n">
-        <x:v>9633</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="G19" t="n">
-        <x:v>12067</x:v>
+        <x:v>3767</x:v>
       </x:c>
       <x:c r="H19" t="str">
-        <x:v>최종 메뉴 액션 아웃트로</x:v>
+        <x:v>메뉴 항공샷 공개</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>OUTRO</x:v>
+        <x:v>REVEAL</x:v>
       </x:c>
       <x:c r="J19" t="str">
-        <x:v>비비기·들어올리기·떠먹기 등 최종 음식 클로즈업에 1.05→1.00 ease-out 줌아웃</x:v>
+        <x:v>메뉴 전체가 보이는 탑다운/하이앵글 샷에 1.00→1.05 선형 줌인과 하단 보조 텍스트 적용</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>실측 9633~12067ms; ACTION_PEAK를 슬롯 48% 부근에 배치; speed 0.9~1.1; 정책값 해소 시에만 FADE_OUT</x:v>
-      </x:c>
-      <x:c r="L19"/>
+        <x:v>실측 1033~3767ms; 구성 최적 구간 trim; speed 0.9~1.1; 3767ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L19" t="str">
+        <x:v>{{store.location_or_context}}</x:v>
+      </x:c>
       <x:c r="M19" t="str">
-        <x:v>promo.primary,promo.secondary</x:v>
+        <x:v>store.location,store.context,promo.primary</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>가장 강한 실제 메뉴 액션을 사용하고 레퍼런스 브랜딩은 복제하지 않음</x:v>
+        <x:v>실제 메뉴와 검증된 장소/맥락만 사용하고 숫자·혜택을 임의 생성하지 않음</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>transform</x:v>
+        <x:v>caption,text_2d,transform</x:v>
       </x:c>
       <x:c r="P19" t="n">
         <x:v>30</x:v>
@@ -30133,345 +30380,554 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
-        <x:v>gts_otsukare_01</x:v>
+        <x:v>gts_donggeurio_v1_03</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_donggeurio_challenge_v1</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>donggeurio_challenge</x:v>
       </x:c>
       <x:c r="D20" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E20" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F20" t="n">
-        <x:v>0</x:v>
+        <x:v>3767</x:v>
       </x:c>
       <x:c r="G20" t="n">
-        <x:v>467</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="H20" t="str">
-        <x:v>오버헤드 V 포즈 훅</x:v>
+        <x:v>카페 공간 팬</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>DANCE_OVERHEAD_HOOK</x:v>
+        <x:v>AMBIENCE</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>한 명의 출연자가 오버헤드 근접 구도에서 V 포즈와 표정으로 시작하고 즉시 메인 안무로 연결</x:v>
+        <x:v>조명·좌석·인테리어를 보여주는 가장 매끄러운 우향 팬/측면 이동 구간 선택</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>0–467ms; speed=1.0; 다음 와이드 구간으로 동작이 끊기지 않게 연결</x:v>
-      </x:c>
-      <x:c r="L20" t="str">
-        <x:v>{{caption.hook}}</x:v>
-      </x:c>
+        <x:v>실측 3767~4700ms; 모션 중심 trim; speed 0.9~1.35; 소스 팬 보존; 4700ms HARD_CUT</x:v>
+      </x:c>
+      <x:c r="L20"/>
       <x:c r="M20" t="str">
-        <x:v>caption.hook,store.owner_face_allowed</x:v>
+        <x:v>store.interior</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>출연자는 촬영 동의된 매장 관계자만 사용하고 훅 자막은 얼굴·손을 가리지 않는 세이프존에 1줄로 표시</x:v>
+        <x:v>실제 촬영된 공간 정보량이 높은 구간을 사용하고 긴 팬 전체를 강제 고배속하지 않음</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>caption,text_2d</x:v>
+        <x:v>transform</x:v>
       </x:c>
       <x:c r="P20" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="Q20" t="str">
-        <x:v>2026-08-24T22:00:00</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q20" t="n">
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R20" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S20" t="str">
-        <x:v>SUPERSEDED</x:v>
+        <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T20" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
       </x:c>
       <x:c r="U20" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V20" t="str">
-        <x:v>원본 BGM은 합성하지 않고 플랫폼 UI를 복제하지 않음. 안무와 얼굴 가시성을 우선.</x:v>
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
       </x:c>
       <x:c r="W20" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
-        <x:v>gts_otsukare_02</x:v>
+        <x:v>gts_donggeurio_v1_04</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_donggeurio_challenge_v1</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>donggeurio_challenge</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E21" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F21" t="n">
-        <x:v>467</x:v>
+        <x:v>4700</x:v>
       </x:c>
       <x:c r="G21" t="n">
-        <x:v>3933</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="H21" t="str">
-        <x:v>와이드 안무 A → 오버헤드 포인트</x:v>
+        <x:v>메뉴 인터랙션 클로즈업</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>DANCE_PHRASE_A</x:v>
+        <x:v>ACTION</x:v>
       </x:c>
       <x:c r="J21" t="str">
-        <x:v>전신이 보이는 와이드 안무를 연속 수행한 뒤 같은 동작 흐름에서 카메라가 위쪽 가까운 포인트로 이동</x:v>
+        <x:v>손이나 도구가 음식에 개입하는 클로즈업에서 동작 시작·피크·종료를 보존</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>WIDE 467–3300ms → OVERHEAD 3300–3933ms; speed=1.0; 중간 홍보 컷 삽입 금지</x:v>
+        <x:v>실측 4700~7000ms; ACTION_PEAK를 슬롯 58% 부근에 배치; speed 0.9~1.1; 7000ms HARD_CUT</x:v>
       </x:c>
       <x:c r="L21"/>
       <x:c r="M21" t="str">
-        <x:v>store.owner_face_allowed</x:v>
+        <x:v>promo.primary.action</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>실제 촬영 장소와 동의된 출연자로 개인화하되 안무 프레이즈와 카메라 전환 순서를 유지</x:v>
-      </x:c>
-      <x:c r="O21"/>
+        <x:v>실제 촬영된 섞기·집기·서빙 행동을 우선하며 없는 행동을 생성하지 않음</x:v>
+      </x:c>
+      <x:c r="O21" t="str">
+        <x:v>transform</x:v>
+      </x:c>
       <x:c r="P21" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="Q21" t="str">
-        <x:v>2026-08-24T22:00:00</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q21" t="n">
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R21" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S21" t="str">
-        <x:v>SUPERSEDED</x:v>
+        <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T21" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
       </x:c>
       <x:c r="U21" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V21" t="str">
-        <x:v>가이드에 없는 메뉴 B-roll·생성 장면을 중간에 넣지 않음.</x:v>
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
       </x:c>
       <x:c r="W21" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
-        <x:v>gts_otsukare_03</x:v>
+        <x:v>gts_donggeurio_v1_05</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_donggeurio_challenge_v1</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>donggeurio_challenge</x:v>
       </x:c>
       <x:c r="D22" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E22" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F22" t="n">
-        <x:v>3933</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G22" t="n">
-        <x:v>7400</x:v>
+        <x:v>8333</x:v>
       </x:c>
       <x:c r="H22" t="str">
-        <x:v>와이드 안무 B → 오버헤드 포인트</x:v>
+        <x:v>음식 자르기 액션 하이라이트</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>DANCE_PHRASE_B</x:v>
+        <x:v>ACTION_HIGHLIGHT</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>전신 와이드 안무를 이어가며 팔과 상체 제스처를 보여준 뒤 두 번째 오버헤드 포인트로 연결</x:v>
+        <x:v>포크/나이프로 음식을 자르거나 분리하는 핵심 순간을 타이트한 클로즈업으로 강조</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>WIDE 3933–6733ms → OVERHEAD 6733–7400ms; speed=1.0; 앞뒤 동작 연속성 유지</x:v>
+        <x:v>실측 7000~8333ms; ACTION_PEAK 중심 trim; speed 0.75~1.0, 0.8 선호; 8333ms HARD_CUT</x:v>
       </x:c>
       <x:c r="L22"/>
       <x:c r="M22" t="str">
-        <x:v>store.owner_face_allowed</x:v>
+        <x:v>promo.secondary.action</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>의상·배경은 실제 촬영 맥락에 맞출 수 있으나 얼굴·손·몸동작을 이미지나 긴 자막으로 가리지 않음</x:v>
-      </x:c>
-      <x:c r="O22"/>
+        <x:v>자르기 장면이 없으면 다른 실제 메뉴 액션으로 대체하고 0.9배 수준까지 완화</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>transform</x:v>
+      </x:c>
       <x:c r="P22" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="Q22" t="str">
-        <x:v>2026-08-24T22:00:00</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q22" t="n">
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R22" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S22" t="str">
-        <x:v>SUPERSEDED</x:v>
+        <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T22" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
       </x:c>
       <x:c r="U22" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V22" t="str">
-        <x:v>춤 프레임을 메뉴 이미지로 교체하지 않으며 실제 안무 수행 영상을 유지.</x:v>
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
       </x:c>
       <x:c r="W22" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
-        <x:v>gts_otsukare_04</x:v>
+        <x:v>gts_donggeurio_v1_06</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_donggeurio_challenge_v1</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>donggeurio_challenge</x:v>
       </x:c>
       <x:c r="D23" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E23" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F23" t="n">
-        <x:v>7400</x:v>
+        <x:v>8333</x:v>
       </x:c>
       <x:c r="G23" t="n">
-        <x:v>10900</x:v>
+        <x:v>9633</x:v>
       </x:c>
       <x:c r="H23" t="str">
-        <x:v>와이드 안무 C → 마지막 오버헤드 전환</x:v>
+        <x:v>매장 외관·위치 공개</x:v>
       </x:c>
       <x:c r="I23" t="str">
-        <x:v>DANCE_PHRASE_C</x:v>
+        <x:v>LOCATION</x:v>
       </x:c>
       <x:c r="J23" t="str">
-        <x:v>세 번째 와이드 안무 프레이즈를 이어가고 카메라가 위쪽으로 이동하면서 마지막 포즈를 준비</x:v>
+        <x:v>매장 외관·간판·입구 등 장소를 식별할 수 있는 구도를 짧게 제시하고 지원될 때만 미세 줌</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>WIDE 7400–10200ms → OVERHEAD 10200–10900ms; speed=1.0; 흐름 삭제·재배열 금지</x:v>
+        <x:v>실측 8333~9633ms; 구성 중심 trim; speed 0.9~1.1; 실제 경계는 HARD_CUT 우선</x:v>
       </x:c>
       <x:c r="L23"/>
       <x:c r="M23" t="str">
-        <x:v>store.owner_face_allowed</x:v>
+        <x:v>store.name,store.location</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>매장 홍보는 촬영 배경과 출연 맥락으로 자연스럽게 드러내고 별도 홍보 컷을 삽입하지 않음</x:v>
-      </x:c>
-      <x:c r="O23"/>
+        <x:v>검증된 매장 외관/위치만 사용하고 SLIDE_LEFT 느낌은 선택적 악센트로만 취급</x:v>
+      </x:c>
+      <x:c r="O23" t="str">
+        <x:v>caption,text_2d,transform</x:v>
+      </x:c>
       <x:c r="P23" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="Q23" t="str">
-        <x:v>2026-08-24T22:00:00</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q23" t="n">
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R23" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S23" t="str">
-        <x:v>SUPERSEDED</x:v>
+        <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T23" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
       </x:c>
       <x:c r="U23" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V23" t="str">
-        <x:v>미지원 피사체 추적·배경 합성 없이 실제 촬영 카메라 동선과 컷 연결만 사용.</x:v>
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
       </x:c>
       <x:c r="W23" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
-        <x:v>gts_otsukare_05</x:v>
+        <x:v>gts_donggeurio_v1_07</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>gt_otsukare_summer_v2</x:v>
+        <x:v>gt_donggeurio_challenge_v1</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>otsukare_summer_challenge</x:v>
+        <x:v>donggeurio_challenge</x:v>
       </x:c>
       <x:c r="D24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E24" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F24" t="n">
-        <x:v>10900</x:v>
+        <x:v>9633</x:v>
       </x:c>
       <x:c r="G24" t="n">
-        <x:v>11500</x:v>
+        <x:v>12067</x:v>
       </x:c>
       <x:c r="H24" t="str">
-        <x:v>오버헤드 근접 마지막 포즈</x:v>
+        <x:v>최종 메뉴 액션 아웃트로</x:v>
       </x:c>
       <x:c r="I24" t="str">
-        <x:v>DANCE_FINAL_POSE</x:v>
+        <x:v>OUTRO</x:v>
       </x:c>
       <x:c r="J24" t="str">
-        <x:v>얼굴과 손동작이 가까워지는 오버헤드 포즈로 안무를 닫고 짧은 CTA를 안전 영역에 표시</x:v>
+        <x:v>비비기·들어올리기·떠먹기 등 최종 음식 클로즈업에 1.05→1.00 ease-out 줌아웃</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>10900–11500ms; speed=1.0; CTA는 마지막 0.6초 안에서 한 줄만 사용</x:v>
-      </x:c>
-      <x:c r="L24" t="str">
-        <x:v>{{store.name}} · {{caption.cta}}</x:v>
-      </x:c>
+        <x:v>실측 9633~12067ms; ACTION_PEAK를 슬롯 48% 부근에 배치; speed 0.9~1.1; 정책값 해소 시에만 FADE_OUT</x:v>
+      </x:c>
+      <x:c r="L24"/>
       <x:c r="M24" t="str">
-        <x:v>store.name,caption.cta,store.owner_face_allowed</x:v>
+        <x:v>promo.primary,promo.secondary</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>검증된 매장명과 짧은 CTA만 사용하고 얼굴·손을 가리지 않는 하단 세이프존에 배치</x:v>
+        <x:v>가장 강한 실제 메뉴 액션을 사용하고 레퍼런스 브랜딩은 복제하지 않음</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>caption,text_2d,sfx</x:v>
+        <x:v>transform</x:v>
       </x:c>
       <x:c r="P24" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="Q24" t="str">
-        <x:v>2026-08-24T22:00:00</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q24" t="n">
+        <x:v>46264.395833333336</x:v>
       </x:c>
       <x:c r="R24" t="str">
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="S24" t="str">
-        <x:v>SUPERSEDED</x:v>
+        <x:v>ACTIVE</x:v>
       </x:c>
       <x:c r="T24" t="str">
-        <x:v>'12_SOURCE_GUIDES'!$G$828:$G$846</x:v>
+        <x:v>'12_SOURCE_GUIDES'!$G$693:$G$706</x:v>
       </x:c>
       <x:c r="U24" t="str">
-        <x:v>VIDEO_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
       </x:c>
       <x:c r="V24" t="str">
-        <x:v>사용자는 앱에서 음원을 직접 추가하며 템플릿은 음원 제목·시작 위치만 최종 제공.</x:v>
+        <x:v>웜톤 수치·미세 줌·페이드 길이가 미해결이면 서버 정책값 또는 안전한 HARD_CUT/무변형으로 대체. 레퍼런스 브랜드 복제 금지.</x:v>
       </x:c>
       <x:c r="W24" t="str">
-        <x:v>B5BA6E95FE7BD0CD4F7A340EDC051E0BCCDF24D367ED1E60C495F1C96618A0B9</x:v>
+        <x:v>197EEB645CBCD97776AAD5D4337EA20074A6DE50BFB0ADDB6F704281A3ABFA5F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>gts_doma_bad_v1_01</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>정면 준비 동작 훅</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>HOOK_SETUP</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>고정 전신 구도에서 카메라를 바라보며 자연스러운 준비 동작을 이어가고 인물 전체를 프레임 안에 유지</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>0~4000ms 의미 구간; 원본 영상은 분할하지 않음; speed=1.0; 카메라 이동·디지털 줌·전환 없음</x:v>
+      </x:c>
+      <x:c r="L25"/>
+      <x:c r="M25" t="str">
+        <x:v>project.title,promo.context,store.context</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>레퍼런스 인원·복장·자막을 복제하지 않고 사용자 영상과 홍보 맥락에 맞춘 동작·텍스트만 사용</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>caption,text_2d</x:v>
+      </x:c>
+      <x:c r="P25" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q25" t="n">
+        <x:v>46264.99015046296</x:v>
+      </x:c>
+      <x:c r="R25" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S25" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T25" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$707:$G$716</x:v>
+      </x:c>
+      <x:c r="U25" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V25" t="str">
+        <x:v>단일 연속 영상은 분할·재배열·속도 변경·역재생·프리즈·합성 전환·애니메이션 변형을 금지. 외부 챌린지 음원이 없으면 오디오 재정렬을 생략하고 플랫폼에서 사용자가 권리 확인된 음원을 추가.</x:v>
+      </x:c>
+      <x:c r="W25" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>gts_doma_bad_v1_02</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="G26" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>드롭 직전 준비 동작</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>PRE_DROP_BUILDUP</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>같은 고정 전신 구도와 연속 동작을 유지하며 비트 드롭 직전의 짧은 준비·방향 전환 동작 수행</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>4000~5000ms 의미 구간; 5000ms 행동 반전 앵커를 준비하되 물리 컷을 만들지 않음; speed=1.0</x:v>
+      </x:c>
+      <x:c r="L26"/>
+      <x:c r="M26" t="str">
+        <x:v>project.title,promo.context,store.context</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>레퍼런스 인원·복장·자막을 복제하지 않고 사용자 영상과 홍보 맥락에 맞춘 동작·텍스트만 사용</x:v>
+      </x:c>
+      <x:c r="O26" t="str">
+        <x:v>caption,text_2d</x:v>
+      </x:c>
+      <x:c r="P26" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q26" t="n">
+        <x:v>46264.99015046296</x:v>
+      </x:c>
+      <x:c r="R26" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S26" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T26" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$707:$G$716</x:v>
+      </x:c>
+      <x:c r="U26" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V26" t="str">
+        <x:v>단일 연속 영상은 분할·재배열·속도 변경·역재생·프리즈·합성 전환·애니메이션 변형을 금지. 외부 챌린지 음원이 없으면 오디오 재정렬을 생략하고 플랫폼에서 사용자가 권리 확인된 음원을 추가.</x:v>
+      </x:c>
+      <x:c r="W26" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>gts_doma_bad_v1_03</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>gt_doma_bad_challenge_v1</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>doma_bad_challenge</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>반전 안무 클라이맥스</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>CLIMAX_DANCE</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>비트 드롭과 동시에 몸 또는 이동 방향을 크게 반전한 뒤 대비되는 안무를 끝까지 연속 수행</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>5000~11000ms 의미 구간; 5000ms 시각 행동 반전과 외부 음원 드롭을 가능할 때 ±1프레임 이내 정렬; 영상 분할 없음</x:v>
+      </x:c>
+      <x:c r="L27"/>
+      <x:c r="M27" t="str">
+        <x:v>project.title,promo.context,store.context</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>레퍼런스 인원·복장·자막을 복제하지 않고 사용자 영상과 홍보 맥락에 맞춘 동작·텍스트만 사용</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>caption,text_2d</x:v>
+      </x:c>
+      <x:c r="P27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q27" t="n">
+        <x:v>46264.99015046296</x:v>
+      </x:c>
+      <x:c r="R27" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="S27" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
+      <x:c r="T27" t="str">
+        <x:v>'12_SOURCE_GUIDES'!$G$707:$G$716</x:v>
+      </x:c>
+      <x:c r="U27" t="str">
+        <x:v>UPLOADED_JSON_ANALYSIS_IN_12_SOURCE_GUIDES</x:v>
+      </x:c>
+      <x:c r="V27" t="str">
+        <x:v>단일 연속 영상은 분할·재배열·속도 변경·역재생·프리즈·합성 전환·애니메이션 변형을 금지. 외부 챌린지 음원이 없으면 오디오 재정렬을 생략하고 플랫폼에서 사용자가 권리 확인된 음원을 추가.</x:v>
+      </x:c>
+      <x:c r="W27" t="str">
+        <x:v>B8C30708E56C22517FF97A1ECB76C173EE3A97D91E01175DF37759BFFAA8F78D</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
